--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karel\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karel\Downloads\draseis\draseis\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836229BF-DC36-4194-8E06-BC42E663002B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -894,27 +894,6 @@
     <xf numFmtId="0" fontId="6" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -945,6 +924,27 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1494,10 +1494,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
+      <c r="B1" s="57"/>
     </row>
     <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -1508,10 +1508,10 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="50"/>
+      <c r="B4" s="58"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
@@ -1544,166 +1544,166 @@
       </c>
     </row>
     <row r="10" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="64" t="s">
+      <c r="A10" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="65" t="s">
+      <c r="B10" s="56" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="55"/>
-      <c r="B11" s="55"/>
+      <c r="A11" s="46"/>
+      <c r="B11" s="46"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="B12" s="57"/>
+      <c r="B12" s="48"/>
     </row>
     <row r="13" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="59" t="s">
+      <c r="B13" s="50" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="58" t="s">
+      <c r="A14" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="50" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="58" t="s">
+      <c r="A15" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="59" t="s">
+      <c r="B15" s="50" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="B16" s="59" t="s">
+      <c r="B16" s="50" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="B17" s="59" t="s">
+      <c r="B17" s="50" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="58"/>
-      <c r="B18" s="59"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="50"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="56" t="s">
+      <c r="A19" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="57"/>
+      <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="58" t="s">
+      <c r="A20" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="50" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="58" t="s">
+      <c r="A21" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="59" t="s">
+      <c r="B21" s="50" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="58" t="s">
+      <c r="A22" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="B22" s="59" t="s">
+      <c r="B22" s="50" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="58" t="s">
+      <c r="A23" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="B23" s="59" t="s">
+      <c r="B23" s="50" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="58" t="s">
+      <c r="A24" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="B24" s="59" t="s">
+      <c r="B24" s="50" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="58" t="s">
+      <c r="A25" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="59" t="s">
+      <c r="B25" s="50" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="50" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="60" t="s">
+      <c r="A27" s="51" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="52" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="58"/>
-      <c r="B28" s="59"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="50"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="56" t="s">
+      <c r="A29" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="57"/>
+      <c r="B29" s="48"/>
     </row>
     <row r="30" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="58" t="s">
+      <c r="A30" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="59" t="s">
+      <c r="B30" s="50" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="62" t="s">
+      <c r="A31" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="54" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="55"/>
-      <c r="B32" s="55"/>
+      <c r="A32" s="46"/>
+      <c r="B32" s="46"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
@@ -10088,17 +10088,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
       <c r="K1" s="36" t="s">
         <v>82</v>
       </c>
@@ -10113,20 +10113,20 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="str">
+      <c r="A2" s="61" t="str">
         <f>$L$2&amp;" "&amp;$L$6</f>
         <v>ΟΚΤΩΒΡΙΟΣ 2026</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="F2" s="48" t="str">
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="F2" s="61" t="str">
         <f>$L$3&amp;" "&amp;$L$8</f>
         <v>ΝΟΕΜΒΡΙΟΣ 2026</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
       <c r="K2" s="34" t="s">
         <v>83</v>
       </c>
@@ -11346,59 +11346,59 @@
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
-      <c r="B37" s="46" t="s">
+      <c r="B37" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
       <c r="F37" s="12"/>
-      <c r="G37" s="46" t="s">
+      <c r="G37" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="H37" s="46"/>
-      <c r="I37" s="46"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
-      <c r="B38" s="46" t="s">
+      <c r="B38" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
       <c r="F38" s="13"/>
-      <c r="G38" s="46" t="s">
+      <c r="G38" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="H38" s="46"/>
-      <c r="I38" s="46"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
-      <c r="B39" s="46" t="s">
+      <c r="B39" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
       <c r="F39" s="14"/>
-      <c r="G39" s="46" t="s">
+      <c r="G39" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="H39" s="46"/>
-      <c r="I39" s="46"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="59"/>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
-      <c r="B40" s="46" t="s">
+      <c r="B40" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
       <c r="F40" s="15"/>
-      <c r="G40" s="46" t="s">
+      <c r="G40" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="H40" s="46"/>
-      <c r="I40" s="46"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -11501,12 +11501,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
       <c r="F1" s="36" t="s">
         <v>90</v>
       </c>
@@ -11522,13 +11522,13 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54" t="str">
+      <c r="A2" s="65" t="str">
         <f>$G$2&amp;" "&amp;$G$6</f>
         <v>ΝΟΕΜΒΡΙΟΣ 2026</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
       <c r="F2" s="34" t="s">
         <v>91</v>
       </c>
@@ -12251,35 +12251,35 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="40"/>
-      <c r="B41" s="51" t="s">
+      <c r="B41" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="52"/>
-      <c r="D41" s="52"/>
+      <c r="C41" s="63"/>
+      <c r="D41" s="63"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="31"/>
-      <c r="B42" s="51" t="s">
+      <c r="B42" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
+      <c r="C42" s="63"/>
+      <c r="D42" s="63"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="33"/>
-      <c r="B43" s="51" t="s">
+      <c r="B43" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="52"/>
-      <c r="D43" s="52"/>
+      <c r="C43" s="63"/>
+      <c r="D43" s="63"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="41"/>
-      <c r="B44" s="51" t="s">
+      <c r="B44" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karel\Downloads\draseis\draseis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836229BF-DC36-4194-8E06-BC42E663002B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A456699-72EF-43BF-B5DB-291A38801B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,10 +20,10 @@
     <sheet name="ΑΦΙΣΑ_1ΜΗΝΑΣ" sheetId="20" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ΔΡΑΣΕΙΣ!$A$1:$J$399</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ΔΡΑΣΕΙΣ!$A$1:$J$398</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">ΑΦΙΣΑ_1ΜΗΝΑΣ!$A$1:$D$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">ΑΦΙΣΑ_ΕΠΙΛΟΓΗΣ!$A$1:$I$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">ΔΡΑΣΕΙΣ!$A$1:$G$119</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">ΔΡΑΣΕΙΣ!$A$1:$G$118</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">ΑΦΙΣΑ_1ΜΗΝΑΣ!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">ΑΦΙΣΑ_ΕΠΙΛΟΓΗΣ!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">ΔΡΑΣΕΙΣ!$1:$1</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="127">
   <si>
     <t>3ο ΓΥΜΝΑΣΙΟ ΠΟΛΙΧΝΗΣ  ·  ΗΜΕΡΟΛΟΓΙΟ ΔΡΑΣΕΩΝ  ·  ΣΧΟΛΙΚΟ ΕΤΟΣ 2026-27</t>
   </si>
@@ -208,9 +208,6 @@
   </si>
   <si>
     <t>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</t>
-  </si>
-  <si>
-    <t>Επέτειος Πολυτεχνείου – Αργία</t>
   </si>
   <si>
     <t>Τελευταία ημέρα μαθημάτων πριν τις διακοπές</t>
@@ -950,7 +947,15 @@
   <cellStyles count="1">
     <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="37">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1532,7 +1537,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
@@ -1545,10 +1550,10 @@
     </row>
     <row r="10" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1557,48 +1562,48 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B12" s="48"/>
     </row>
     <row r="13" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="50" t="s">
         <v>95</v>
-      </c>
-      <c r="B13" s="50" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="50" t="s">
         <v>97</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="50" t="s">
         <v>99</v>
-      </c>
-      <c r="B15" s="50" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A16" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="50" t="s">
         <v>101</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="50" t="s">
         <v>103</v>
-      </c>
-      <c r="B17" s="50" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1607,72 +1612,72 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="50" t="s">
         <v>106</v>
-      </c>
-      <c r="B20" s="50" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A21" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="50" t="s">
         <v>108</v>
-      </c>
-      <c r="B21" s="50" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="B22" s="50" t="s">
         <v>110</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A23" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="50" t="s">
         <v>112</v>
-      </c>
-      <c r="B23" s="50" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A24" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="50" t="s">
         <v>114</v>
-      </c>
-      <c r="B24" s="50" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A25" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="50" t="s">
         <v>116</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A26" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="50" t="s">
         <v>118</v>
-      </c>
-      <c r="B26" s="50" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A27" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="52" t="s">
         <v>120</v>
-      </c>
-      <c r="B27" s="52" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1681,24 +1686,24 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="47" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B29" s="48"/>
     </row>
     <row r="30" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="50" t="s">
         <v>123</v>
-      </c>
-      <c r="B30" s="50" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="54" t="s">
         <v>125</v>
-      </c>
-      <c r="B31" s="54" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -1748,7 +1753,7 @@
         <v>18</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1925,7 +1930,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K399"/>
+  <dimension ref="A1:K398"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
@@ -1986,7 +1991,7 @@
       <c r="F2" s="21"/>
       <c r="G2" s="21"/>
       <c r="H2" s="22" t="str">
-        <f t="shared" ref="H2:H65" si="0">IF($A2="","",CHOOSE(WEEKDAY($A2,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" ref="H2:H64" si="0">IF($A2="","",CHOOSE(WEEKDAY($A2,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v>Παρ</v>
       </c>
       <c r="I2" s="23" t="str">
@@ -1994,7 +1999,7 @@
         <v>46276#1</v>
       </c>
       <c r="J2" s="23" t="str">
-        <f t="shared" ref="J2:J65" si="1">IF($A2="","",IF($B2="","",$B2&amp;"  ")&amp;$C2&amp;IF($E2="","","  ("&amp;$E2&amp;")"))</f>
+        <f t="shared" ref="J2:J64" si="1">IF($A2="","",IF($B2="","",$B2&amp;"  ")&amp;$C2&amp;IF($E2="","","  ("&amp;$E2&amp;")"))</f>
         <v>Αγιασμός – Έναρξη σχολικού έτους. Διαμοιρασμός σε τμήματα.</v>
       </c>
     </row>
@@ -2137,7 +2142,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="19">
-        <v>46342</v>
+        <v>46343</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="21" t="s">
@@ -2151,11 +2156,11 @@
       <c r="G8" s="21"/>
       <c r="H8" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Τρί</v>
       </c>
       <c r="I8" s="23" t="str">
         <f>IF($A8="","",$A8&amp;"#"&amp;COUNTIF($A$2:$A8,$A8))</f>
-        <v>46342#1</v>
+        <v>46343#1</v>
       </c>
       <c r="J8" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2164,65 +2169,65 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="19">
-        <v>46343</v>
+        <v>46379</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="21" t="s">
         <v>53</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E9" s="21"/>
       <c r="F9" s="21"/>
       <c r="G9" s="21"/>
       <c r="H9" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Τετ</v>
       </c>
       <c r="I9" s="23" t="str">
         <f>IF($A9="","",$A9&amp;"#"&amp;COUNTIF($A$2:$A9,$A9))</f>
-        <v>46343#1</v>
+        <v>46379#1</v>
       </c>
       <c r="J9" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Επέτειος Πολυτεχνείου – Αργία</v>
+        <v>Τελευταία ημέρα μαθημάτων πριν τις διακοπές</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="19">
-        <v>46379</v>
+        <v>46380</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="21" t="s">
         <v>54</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E10" s="21"/>
       <c r="F10" s="21"/>
       <c r="G10" s="21"/>
       <c r="H10" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I10" s="23" t="str">
         <f>IF($A10="","",$A10&amp;"#"&amp;COUNTIF($A$2:$A10,$A10))</f>
-        <v>46379#1</v>
+        <v>46380#1</v>
       </c>
       <c r="J10" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Τελευταία ημέρα μαθημάτων πριν τις διακοπές</v>
+        <v>Διακοπές Χριστουγέννων</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="19">
-        <v>46380</v>
+        <v>46381</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>25</v>
@@ -2232,11 +2237,11 @@
       <c r="G11" s="21"/>
       <c r="H11" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Παρ</v>
       </c>
       <c r="I11" s="23" t="str">
         <f>IF($A11="","",$A11&amp;"#"&amp;COUNTIF($A$2:$A11,$A11))</f>
-        <v>46380#1</v>
+        <v>46381#1</v>
       </c>
       <c r="J11" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2245,11 +2250,11 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="19">
-        <v>46381</v>
+        <v>46384</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>25</v>
@@ -2259,11 +2264,11 @@
       <c r="G12" s="21"/>
       <c r="H12" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Δευ</v>
       </c>
       <c r="I12" s="23" t="str">
         <f>IF($A12="","",$A12&amp;"#"&amp;COUNTIF($A$2:$A12,$A12))</f>
-        <v>46381#1</v>
+        <v>46384#1</v>
       </c>
       <c r="J12" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2272,11 +2277,11 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="19">
-        <v>46384</v>
+        <v>46385</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>25</v>
@@ -2286,11 +2291,11 @@
       <c r="G13" s="21"/>
       <c r="H13" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Τρί</v>
       </c>
       <c r="I13" s="23" t="str">
         <f>IF($A13="","",$A13&amp;"#"&amp;COUNTIF($A$2:$A13,$A13))</f>
-        <v>46384#1</v>
+        <v>46385#1</v>
       </c>
       <c r="J13" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2299,11 +2304,11 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="19">
-        <v>46385</v>
+        <v>46386</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>25</v>
@@ -2313,11 +2318,11 @@
       <c r="G14" s="21"/>
       <c r="H14" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Τετ</v>
       </c>
       <c r="I14" s="23" t="str">
         <f>IF($A14="","",$A14&amp;"#"&amp;COUNTIF($A$2:$A14,$A14))</f>
-        <v>46385#1</v>
+        <v>46386#1</v>
       </c>
       <c r="J14" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2326,11 +2331,11 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="19">
-        <v>46386</v>
+        <v>46387</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>25</v>
@@ -2340,11 +2345,11 @@
       <c r="G15" s="21"/>
       <c r="H15" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I15" s="23" t="str">
         <f>IF($A15="","",$A15&amp;"#"&amp;COUNTIF($A$2:$A15,$A15))</f>
-        <v>46386#1</v>
+        <v>46387#1</v>
       </c>
       <c r="J15" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2353,11 +2358,11 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="19">
-        <v>46387</v>
+        <v>46388</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>25</v>
@@ -2367,11 +2372,11 @@
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Παρ</v>
       </c>
       <c r="I16" s="23" t="str">
         <f>IF($A16="","",$A16&amp;"#"&amp;COUNTIF($A$2:$A16,$A16))</f>
-        <v>46387#1</v>
+        <v>46388#1</v>
       </c>
       <c r="J16" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2380,11 +2385,11 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="19">
-        <v>46388</v>
+        <v>46391</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>25</v>
@@ -2394,11 +2399,11 @@
       <c r="G17" s="21"/>
       <c r="H17" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Δευ</v>
       </c>
       <c r="I17" s="23" t="str">
         <f>IF($A17="","",$A17&amp;"#"&amp;COUNTIF($A$2:$A17,$A17))</f>
-        <v>46388#1</v>
+        <v>46391#1</v>
       </c>
       <c r="J17" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2407,11 +2412,11 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="19">
-        <v>46391</v>
+        <v>46392</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>25</v>
@@ -2421,11 +2426,11 @@
       <c r="G18" s="21"/>
       <c r="H18" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Τρί</v>
       </c>
       <c r="I18" s="23" t="str">
         <f>IF($A18="","",$A18&amp;"#"&amp;COUNTIF($A$2:$A18,$A18))</f>
-        <v>46391#1</v>
+        <v>46392#1</v>
       </c>
       <c r="J18" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2434,11 +2439,11 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="19">
-        <v>46392</v>
+        <v>46393</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>25</v>
@@ -2448,11 +2453,11 @@
       <c r="G19" s="21"/>
       <c r="H19" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Τετ</v>
       </c>
       <c r="I19" s="23" t="str">
         <f>IF($A19="","",$A19&amp;"#"&amp;COUNTIF($A$2:$A19,$A19))</f>
-        <v>46392#1</v>
+        <v>46393#1</v>
       </c>
       <c r="J19" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2461,11 +2466,11 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="19">
-        <v>46393</v>
+        <v>46394</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>25</v>
@@ -2475,11 +2480,11 @@
       <c r="G20" s="21"/>
       <c r="H20" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I20" s="23" t="str">
         <f>IF($A20="","",$A20&amp;"#"&amp;COUNTIF($A$2:$A20,$A20))</f>
-        <v>46393#1</v>
+        <v>46394#1</v>
       </c>
       <c r="J20" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2488,34 +2493,34 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="19">
-        <v>46394</v>
+        <v>46395</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="21" t="s">
         <v>55</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Παρ</v>
       </c>
       <c r="I21" s="23" t="str">
         <f>IF($A21="","",$A21&amp;"#"&amp;COUNTIF($A$2:$A21,$A21))</f>
-        <v>46394#1</v>
+        <v>46395#1</v>
       </c>
       <c r="J21" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Διακοπές Χριστουγέννων</v>
+        <v>Επαναλειτουργία σχολείου</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="19">
-        <v>46395</v>
+        <v>46407</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="21" t="s">
@@ -2529,128 +2534,128 @@
       <c r="G22" s="21"/>
       <c r="H22" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Τετ</v>
       </c>
       <c r="I22" s="23" t="str">
         <f>IF($A22="","",$A22&amp;"#"&amp;COUNTIF($A$2:$A22,$A22))</f>
-        <v>46395#1</v>
+        <v>46407#1</v>
       </c>
       <c r="J22" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Επαναλειτουργία σχολείου</v>
+        <v>Λήξη Α΄ τετραμήνου (εκτίμηση – εκκρεμεί εγκύκλιος)</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="19">
-        <v>46407</v>
+        <v>46417</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="21" t="s">
         <v>57</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
       <c r="G23" s="21"/>
       <c r="H23" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Σάβ</v>
       </c>
       <c r="I23" s="23" t="str">
         <f>IF($A23="","",$A23&amp;"#"&amp;COUNTIF($A$2:$A23,$A23))</f>
-        <v>46407#1</v>
+        <v>46417#1</v>
       </c>
       <c r="J23" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Λήξη Α΄ τετραμήνου (εκτίμηση – εκκρεμεί εγκύκλιος)</v>
+        <v>Εορτή Τριών Ιεραρχών (πέφτει Σάββατο)</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="19">
-        <v>46417</v>
+        <v>46461</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="21" t="s">
         <v>58</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
       <c r="G24" s="21"/>
       <c r="H24" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Σάβ</v>
+        <v>Δευ</v>
       </c>
       <c r="I24" s="23" t="str">
         <f>IF($A24="","",$A24&amp;"#"&amp;COUNTIF($A$2:$A24,$A24))</f>
-        <v>46417#1</v>
+        <v>46461#1</v>
       </c>
       <c r="J24" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Εορτή Τριών Ιεραρχών (πέφτει Σάββατο)</v>
+        <v>Καθαρά Δευτέρα – Αργία</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="19">
-        <v>46461</v>
+        <v>46470</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="21" t="s">
         <v>59</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
       <c r="G25" s="21"/>
       <c r="H25" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Τετ</v>
       </c>
       <c r="I25" s="23" t="str">
         <f>IF($A25="","",$A25&amp;"#"&amp;COUNTIF($A$2:$A25,$A25))</f>
-        <v>46461#1</v>
+        <v>46470#1</v>
       </c>
       <c r="J25" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Καθαρά Δευτέρα – Αργία</v>
+        <v>Σχολική εορτή για την 25η Μαρτίου</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="19">
-        <v>46470</v>
+        <v>46471</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="21" t="s">
         <v>60</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
       <c r="G26" s="21"/>
       <c r="H26" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I26" s="23" t="str">
         <f>IF($A26="","",$A26&amp;"#"&amp;COUNTIF($A$2:$A26,$A26))</f>
-        <v>46470#1</v>
+        <v>46471#1</v>
       </c>
       <c r="J26" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Σχολική εορτή για την 25η Μαρτίου</v>
+        <v>Εθνική επέτειος 25ης Μαρτίου – Αργία</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="19">
-        <v>46471</v>
+        <v>46503</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="21" t="s">
@@ -2664,24 +2669,24 @@
       <c r="G27" s="21"/>
       <c r="H27" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Δευ</v>
       </c>
       <c r="I27" s="23" t="str">
         <f>IF($A27="","",$A27&amp;"#"&amp;COUNTIF($A$2:$A27,$A27))</f>
-        <v>46471#1</v>
+        <v>46503#1</v>
       </c>
       <c r="J27" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Εθνική επέτειος 25ης Μαρτίου – Αργία</v>
+        <v>Διακοπές Πάσχα</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="19">
-        <v>46503</v>
+        <v>46504</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>25</v>
@@ -2691,11 +2696,11 @@
       <c r="G28" s="21"/>
       <c r="H28" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Τρί</v>
       </c>
       <c r="I28" s="23" t="str">
         <f>IF($A28="","",$A28&amp;"#"&amp;COUNTIF($A$2:$A28,$A28))</f>
-        <v>46503#1</v>
+        <v>46504#1</v>
       </c>
       <c r="J28" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2704,11 +2709,11 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="19">
-        <v>46504</v>
+        <v>46505</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>25</v>
@@ -2718,11 +2723,11 @@
       <c r="G29" s="21"/>
       <c r="H29" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Τετ</v>
       </c>
       <c r="I29" s="23" t="str">
         <f>IF($A29="","",$A29&amp;"#"&amp;COUNTIF($A$2:$A29,$A29))</f>
-        <v>46504#1</v>
+        <v>46505#1</v>
       </c>
       <c r="J29" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2731,11 +2736,11 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="19">
-        <v>46505</v>
+        <v>46506</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>25</v>
@@ -2745,11 +2750,11 @@
       <c r="G30" s="21"/>
       <c r="H30" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I30" s="23" t="str">
         <f>IF($A30="","",$A30&amp;"#"&amp;COUNTIF($A$2:$A30,$A30))</f>
-        <v>46505#1</v>
+        <v>46506#1</v>
       </c>
       <c r="J30" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2758,11 +2763,11 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="19">
-        <v>46506</v>
+        <v>46507</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D31" s="21" t="s">
         <v>25</v>
@@ -2772,11 +2777,11 @@
       <c r="G31" s="21"/>
       <c r="H31" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Παρ</v>
       </c>
       <c r="I31" s="23" t="str">
         <f>IF($A31="","",$A31&amp;"#"&amp;COUNTIF($A$2:$A31,$A31))</f>
-        <v>46506#1</v>
+        <v>46507#1</v>
       </c>
       <c r="J31" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2785,11 +2790,11 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="19">
-        <v>46507</v>
+        <v>46510</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D32" s="21" t="s">
         <v>25</v>
@@ -2799,11 +2804,11 @@
       <c r="G32" s="21"/>
       <c r="H32" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Δευ</v>
       </c>
       <c r="I32" s="23" t="str">
         <f>IF($A32="","",$A32&amp;"#"&amp;COUNTIF($A$2:$A32,$A32))</f>
-        <v>46507#1</v>
+        <v>46510#1</v>
       </c>
       <c r="J32" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2812,11 +2817,11 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="19">
-        <v>46510</v>
+        <v>46511</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D33" s="21" t="s">
         <v>25</v>
@@ -2826,11 +2831,11 @@
       <c r="G33" s="21"/>
       <c r="H33" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Τρί</v>
       </c>
       <c r="I33" s="23" t="str">
         <f>IF($A33="","",$A33&amp;"#"&amp;COUNTIF($A$2:$A33,$A33))</f>
-        <v>46510#1</v>
+        <v>46511#1</v>
       </c>
       <c r="J33" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2839,11 +2844,11 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="19">
-        <v>46511</v>
+        <v>46512</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D34" s="21" t="s">
         <v>25</v>
@@ -2853,11 +2858,11 @@
       <c r="G34" s="21"/>
       <c r="H34" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Τετ</v>
       </c>
       <c r="I34" s="23" t="str">
         <f>IF($A34="","",$A34&amp;"#"&amp;COUNTIF($A$2:$A34,$A34))</f>
-        <v>46511#1</v>
+        <v>46512#1</v>
       </c>
       <c r="J34" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2866,11 +2871,11 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="19">
-        <v>46512</v>
+        <v>46513</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D35" s="21" t="s">
         <v>25</v>
@@ -2880,11 +2885,11 @@
       <c r="G35" s="21"/>
       <c r="H35" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I35" s="23" t="str">
         <f>IF($A35="","",$A35&amp;"#"&amp;COUNTIF($A$2:$A35,$A35))</f>
-        <v>46512#1</v>
+        <v>46513#1</v>
       </c>
       <c r="J35" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2893,11 +2898,11 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="19">
-        <v>46513</v>
+        <v>46514</v>
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D36" s="21" t="s">
         <v>25</v>
@@ -2907,11 +2912,11 @@
       <c r="G36" s="21"/>
       <c r="H36" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Παρ</v>
       </c>
       <c r="I36" s="23" t="str">
         <f>IF($A36="","",$A36&amp;"#"&amp;COUNTIF($A$2:$A36,$A36))</f>
-        <v>46513#1</v>
+        <v>46514#1</v>
       </c>
       <c r="J36" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2920,41 +2925,41 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
-        <v>46514</v>
+        <v>46517</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="21" t="s">
         <v>62</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
       <c r="G37" s="21"/>
       <c r="H37" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Δευ</v>
       </c>
       <c r="I37" s="23" t="str">
         <f>IF($A37="","",$A37&amp;"#"&amp;COUNTIF($A$2:$A37,$A37))</f>
-        <v>46514#1</v>
+        <v>46517#1</v>
       </c>
       <c r="J37" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Διακοπές Πάσχα</v>
+        <v>Επαναλειτουργία σχολείου μετά το Πάσχα (εκτίμηση)</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="19">
-        <v>46517</v>
+        <v>46559</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
@@ -2965,65 +2970,59 @@
       </c>
       <c r="I38" s="23" t="str">
         <f>IF($A38="","",$A38&amp;"#"&amp;COUNTIF($A$2:$A38,$A38))</f>
-        <v>46517#1</v>
+        <v>46559#1</v>
       </c>
       <c r="J38" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Επαναλειτουργία σχολείου μετά το Πάσχα (εκτίμηση)</v>
+        <v>Αγίου Πνεύματος – Αργία</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="19">
-        <v>46559</v>
+        <v>46568</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="21" t="s">
         <v>64</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E39" s="21"/>
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
       <c r="H39" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Τετ</v>
       </c>
       <c r="I39" s="23" t="str">
         <f>IF($A39="","",$A39&amp;"#"&amp;COUNTIF($A$2:$A39,$A39))</f>
-        <v>46559#1</v>
+        <v>46568#1</v>
       </c>
       <c r="J39" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Αγίου Πνεύματος – Αργία</v>
+        <v>Λήξη διδακτικού έτους</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="19">
-        <v>46568</v>
-      </c>
+      <c r="A40" s="19"/>
       <c r="B40" s="20"/>
-      <c r="C40" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>30</v>
-      </c>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
       <c r="H40" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v/>
       </c>
       <c r="I40" s="23" t="str">
         <f>IF($A40="","",$A40&amp;"#"&amp;COUNTIF($A$2:$A40,$A40))</f>
-        <v>46568#1</v>
+        <v/>
       </c>
       <c r="J40" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Λήξη διδακτικού έτους</v>
+        <v/>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
@@ -3539,7 +3538,7 @@
       <c r="F65" s="21"/>
       <c r="G65" s="21"/>
       <c r="H65" s="22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H65:H128" si="2">IF($A65="","",CHOOSE(WEEKDAY($A65,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I65" s="23" t="str">
@@ -3547,7 +3546,7 @@
         <v/>
       </c>
       <c r="J65" s="23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J65:J128" si="3">IF($A65="","",IF($B65="","",$B65&amp;"  ")&amp;$C65&amp;IF($E65="","","  ("&amp;$E65&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -3560,7 +3559,7 @@
       <c r="F66" s="21"/>
       <c r="G66" s="21"/>
       <c r="H66" s="22" t="str">
-        <f t="shared" ref="H66:H129" si="2">IF($A66="","",CHOOSE(WEEKDAY($A66,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I66" s="23" t="str">
@@ -3568,7 +3567,7 @@
         <v/>
       </c>
       <c r="J66" s="23" t="str">
-        <f t="shared" ref="J66:J129" si="3">IF($A66="","",IF($B66="","",$B66&amp;"  ")&amp;$C66&amp;IF($E66="","","  ("&amp;$E66&amp;")"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4665,13 +4664,11 @@
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A119" s="19"/>
-      <c r="B119" s="20"/>
-      <c r="C119" s="21"/>
-      <c r="D119" s="21"/>
-      <c r="E119" s="21"/>
-      <c r="F119" s="21"/>
-      <c r="G119" s="21"/>
+      <c r="C119" s="44"/>
+      <c r="D119" s="44"/>
+      <c r="E119" s="44"/>
+      <c r="F119" s="44"/>
+      <c r="G119" s="44"/>
       <c r="H119" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4863,7 +4860,7 @@
       <c r="F129" s="44"/>
       <c r="G129" s="44"/>
       <c r="H129" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H129:H192" si="4">IF($A129="","",CHOOSE(WEEKDAY($A129,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I129" s="23" t="str">
@@ -4871,7 +4868,7 @@
         <v/>
       </c>
       <c r="J129" s="23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J129:J192" si="5">IF($A129="","",IF($B129="","",$B129&amp;"  ")&amp;$C129&amp;IF($E129="","","  ("&amp;$E129&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -4882,7 +4879,7 @@
       <c r="F130" s="44"/>
       <c r="G130" s="44"/>
       <c r="H130" s="22" t="str">
-        <f t="shared" ref="H130:H193" si="4">IF($A130="","",CHOOSE(WEEKDAY($A130,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I130" s="23" t="str">
@@ -4890,7 +4887,7 @@
         <v/>
       </c>
       <c r="J130" s="23" t="str">
-        <f t="shared" ref="J130:J193" si="5">IF($A130="","",IF($B130="","",$B130&amp;"  ")&amp;$C130&amp;IF($E130="","","  ("&amp;$E130&amp;")"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6079,7 +6076,7 @@
       <c r="F193" s="44"/>
       <c r="G193" s="44"/>
       <c r="H193" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="H193:H256" si="6">IF($A193="","",CHOOSE(WEEKDAY($A193,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I193" s="23" t="str">
@@ -6087,7 +6084,7 @@
         <v/>
       </c>
       <c r="J193" s="23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J193:J256" si="7">IF($A193="","",IF($B193="","",$B193&amp;"  ")&amp;$C193&amp;IF($E193="","","  ("&amp;$E193&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -6098,7 +6095,7 @@
       <c r="F194" s="44"/>
       <c r="G194" s="44"/>
       <c r="H194" s="22" t="str">
-        <f t="shared" ref="H194:H257" si="6">IF($A194="","",CHOOSE(WEEKDAY($A194,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I194" s="23" t="str">
@@ -6106,7 +6103,7 @@
         <v/>
       </c>
       <c r="J194" s="23" t="str">
-        <f t="shared" ref="J194:J257" si="7">IF($A194="","",IF($B194="","",$B194&amp;"  ")&amp;$C194&amp;IF($E194="","","  ("&amp;$E194&amp;")"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7295,7 +7292,7 @@
       <c r="F257" s="44"/>
       <c r="G257" s="44"/>
       <c r="H257" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="H257:H320" si="8">IF($A257="","",CHOOSE(WEEKDAY($A257,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I257" s="23" t="str">
@@ -7303,7 +7300,7 @@
         <v/>
       </c>
       <c r="J257" s="23" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J257:J320" si="9">IF($A257="","",IF($B257="","",$B257&amp;"  ")&amp;$C257&amp;IF($E257="","","  ("&amp;$E257&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -7314,7 +7311,7 @@
       <c r="F258" s="44"/>
       <c r="G258" s="44"/>
       <c r="H258" s="22" t="str">
-        <f t="shared" ref="H258:H321" si="8">IF($A258="","",CHOOSE(WEEKDAY($A258,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I258" s="23" t="str">
@@ -7322,7 +7319,7 @@
         <v/>
       </c>
       <c r="J258" s="23" t="str">
-        <f t="shared" ref="J258:J321" si="9">IF($A258="","",IF($B258="","",$B258&amp;"  ")&amp;$C258&amp;IF($E258="","","  ("&amp;$E258&amp;")"))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -8511,7 +8508,7 @@
       <c r="F321" s="44"/>
       <c r="G321" s="44"/>
       <c r="H321" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="H321:H384" si="10">IF($A321="","",CHOOSE(WEEKDAY($A321,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I321" s="23" t="str">
@@ -8519,7 +8516,7 @@
         <v/>
       </c>
       <c r="J321" s="23" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J321:J384" si="11">IF($A321="","",IF($B321="","",$B321&amp;"  ")&amp;$C321&amp;IF($E321="","","  ("&amp;$E321&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -8530,7 +8527,7 @@
       <c r="F322" s="44"/>
       <c r="G322" s="44"/>
       <c r="H322" s="22" t="str">
-        <f t="shared" ref="H322:H385" si="10">IF($A322="","",CHOOSE(WEEKDAY($A322,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="I322" s="23" t="str">
@@ -8538,7 +8535,7 @@
         <v/>
       </c>
       <c r="J322" s="23" t="str">
-        <f t="shared" ref="J322:J385" si="11">IF($A322="","",IF($B322="","",$B322&amp;"  ")&amp;$C322&amp;IF($E322="","","  ("&amp;$E322&amp;")"))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9727,7 +9724,7 @@
       <c r="F385" s="44"/>
       <c r="G385" s="44"/>
       <c r="H385" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="H385:H398" si="12">IF($A385="","",CHOOSE(WEEKDAY($A385,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I385" s="23" t="str">
@@ -9735,7 +9732,7 @@
         <v/>
       </c>
       <c r="J385" s="23" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J385:J398" si="13">IF($A385="","",IF($B385="","",$B385&amp;"  ")&amp;$C385&amp;IF($E385="","","  ("&amp;$E385&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -9746,7 +9743,7 @@
       <c r="F386" s="44"/>
       <c r="G386" s="44"/>
       <c r="H386" s="22" t="str">
-        <f t="shared" ref="H386:H399" si="12">IF($A386="","",CHOOSE(WEEKDAY($A386,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="I386" s="23" t="str">
@@ -9754,7 +9751,7 @@
         <v/>
       </c>
       <c r="J386" s="23" t="str">
-        <f t="shared" ref="J386:J399" si="13">IF($A386="","",IF($B386="","",$B386&amp;"  ")&amp;$C386&amp;IF($E386="","","  ("&amp;$E386&amp;")"))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -9986,65 +9983,51 @@
         <v/>
       </c>
     </row>
-    <row r="399" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C399" s="44"/>
-      <c r="D399" s="44"/>
-      <c r="E399" s="44"/>
-      <c r="F399" s="44"/>
-      <c r="G399" s="44"/>
-      <c r="H399" s="22" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="I399" s="23" t="str">
-        <f>IF($A399="","",$A399&amp;"#"&amp;COUNTIF($A$2:$A399,$A399))</f>
-        <v/>
-      </c>
-      <c r="J399" s="23" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J399" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J399">
-      <sortCondition ref="A1:A399"/>
+  <autoFilter ref="A1:J398" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J398">
+      <sortCondition ref="A1:A398"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="A2:G3 A5:G399">
-    <cfRule type="expression" dxfId="35" priority="10">
+  <conditionalFormatting sqref="A2:G3 A5:G8 A10:G398">
+    <cfRule type="expression" dxfId="36" priority="10">
       <formula>AND($A2="",$A1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:G399">
-    <cfRule type="expression" dxfId="34" priority="2">
+  <conditionalFormatting sqref="A2:G398">
+    <cfRule type="expression" dxfId="35" priority="2">
       <formula>$D2="Αργία / Διακοπές"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="3">
+    <cfRule type="expression" dxfId="34" priority="3">
       <formula>$D2="Εορτή / Εκκλησιασμός"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="4">
+    <cfRule type="expression" dxfId="33" priority="4">
       <formula>$D2="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="5">
+    <cfRule type="expression" dxfId="32" priority="5">
       <formula>$D2="Σύλλογος διδασκόντων"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="6">
+    <cfRule type="expression" dxfId="31" priority="6">
       <formula>$D2="Ενημέρωση γονέων / Έλεγχοι"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="7">
+    <cfRule type="expression" dxfId="30" priority="7">
       <formula>$D2="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="8">
+    <cfRule type="expression" dxfId="29" priority="8">
       <formula>$D2="Επιμόρφωση εκπαιδευτικών"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="9">
+    <cfRule type="expression" dxfId="28" priority="9">
       <formula>$D2="Δράση / Πρόγραμμα / Όμιλος"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A9:G9">
+    <cfRule type="expression" dxfId="0" priority="20">
+      <formula>AND($A9="",#REF!&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Τίτλος δράσης" prompt="Σύντομος τίτλος. Ώρες στη στήλη Β, τμήματα στη στήλη Ε." sqref="C2:C399" xr:uid="{0CD0AE7B-36D6-492A-8412-0F46B1D4BF63}"/>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Μη έγκυρη ημερομηνία" error="Γράψε πραγματική ημερομηνία στη μορφή 16/10/2026." promptTitle="Ημερομηνία" prompt="Γράψε την ημερομηνία, π.χ. 16/10/2026. Νέα δράση = πρώτη κενή (κίτρινη) γραμμή στο τέλος." sqref="A2:A399" xr:uid="{04C73EC8-C88D-4F69-A9AB-F63578E3CB50}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Τίτλος δράσης" prompt="Σύντομος τίτλος. Ώρες στη στήλη Β, τμήματα στη στήλη Ε." sqref="C2:C398" xr:uid="{0CD0AE7B-36D6-492A-8412-0F46B1D4BF63}"/>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Μη έγκυρη ημερομηνία" error="Γράψε πραγματική ημερομηνία στη μορφή 16/10/2026." promptTitle="Ημερομηνία" prompt="Γράψε την ημερομηνία, π.χ. 16/10/2026. Νέα δράση = πρώτη κενή (κίτρινη) γραμμή στο τέλος." sqref="A2:A398" xr:uid="{04C73EC8-C88D-4F69-A9AB-F63578E3CB50}">
       <formula1>OR($A2="",AND(ISNUMBER($A2),$A2&gt;36526))</formula1>
     </dataValidation>
   </dataValidations>
@@ -10060,7 +10043,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D399</xm:sqref>
+          <xm:sqref>D2:D398</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10100,16 +10083,16 @@
       <c r="H1" s="60"/>
       <c r="I1" s="60"/>
       <c r="K1" s="36" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" t="s">
         <v>69</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>70</v>
-      </c>
-      <c r="P1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -10128,13 +10111,13 @@
       <c r="H2" s="61"/>
       <c r="I2" s="61"/>
       <c r="K2" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L2" s="38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O2">
         <v>9</v>
@@ -10148,34 +10131,34 @@
         <v>42</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F3" s="24" t="s">
         <v>42</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3" s="24" t="s">
         <v>33</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K3" s="35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O3">
         <v>10</v>
@@ -10194,11 +10177,11 @@
         <v>46296</v>
       </c>
       <c r="C4" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="28" t="str">
-        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F4" s="25" t="str">
@@ -10210,16 +10193,16 @@
         <v>46327</v>
       </c>
       <c r="H4" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I4" s="28" t="str">
-        <f>IF($G4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="K4" s="34"/>
       <c r="N4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O4">
         <v>11</v>
@@ -10238,11 +10221,11 @@
         <v>46297</v>
       </c>
       <c r="C5" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="28" t="str">
-        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F5" s="25" t="str">
@@ -10254,22 +10237,22 @@
         <v>46328</v>
       </c>
       <c r="H5" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I5" s="28" t="str">
-        <f>IF($G5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="K5" s="34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L5">
         <f>INDEX($O$2:$O$11,MATCH($L$2,$N$2:$N$11,0))</f>
         <v>10</v>
       </c>
       <c r="N5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O5">
         <v>12</v>
@@ -10288,11 +10271,11 @@
         <v>46298</v>
       </c>
       <c r="C6" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="28" t="str">
-        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F6" s="25" t="str">
@@ -10304,22 +10287,22 @@
         <v>46329</v>
       </c>
       <c r="H6" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I6" s="28" t="str">
-        <f>IF($G6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="K6" s="34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L6">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($P$2:$P$11,MATCH($L$2,$N$2:$N$11,0))</f>
         <v>2026</v>
       </c>
       <c r="N6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -10338,11 +10321,11 @@
         <v>46299</v>
       </c>
       <c r="C7" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="28" t="str">
-        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F7" s="25" t="str">
@@ -10354,22 +10337,22 @@
         <v>46330</v>
       </c>
       <c r="H7" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v>Επιμόρφωση εκπαιδευτικών</v>
       </c>
       <c r="I7" s="28" t="str">
-        <f>IF($G7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives»</v>
       </c>
       <c r="K7" s="34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L7">
         <f>INDEX($O$2:$O$11,MATCH($L$3,$N$2:$N$11,0))</f>
         <v>11</v>
       </c>
       <c r="N7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O7">
         <v>2</v>
@@ -10388,11 +10371,11 @@
         <v>46300</v>
       </c>
       <c r="C8" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="28" t="str">
-        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F8" s="25" t="str">
@@ -10404,22 +10387,22 @@
         <v>46331</v>
       </c>
       <c r="H8" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I8" s="28" t="str">
-        <f>IF($G8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="K8" s="34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L8">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($P$2:$P$11,MATCH($L$3,$N$2:$N$11,0))</f>
         <v>2026</v>
       </c>
       <c r="N8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O8">
         <v>3</v>
@@ -10438,11 +10421,11 @@
         <v>46301</v>
       </c>
       <c r="C9" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="28" t="str">
-        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F9" s="25" t="str">
@@ -10454,15 +10437,15 @@
         <v>46332</v>
       </c>
       <c r="H9" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I9" s="28" t="str">
-        <f>IF($G9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O9">
         <v>4</v>
@@ -10481,11 +10464,11 @@
         <v>46302</v>
       </c>
       <c r="C10" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="28" t="str">
-        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F10" s="25" t="str">
@@ -10497,15 +10480,15 @@
         <v>46333</v>
       </c>
       <c r="H10" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I10" s="28" t="str">
-        <f>IF($G10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="N10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -10524,11 +10507,11 @@
         <v>46303</v>
       </c>
       <c r="C11" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="28" t="str">
-        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F11" s="25" t="str">
@@ -10540,15 +10523,15 @@
         <v>46334</v>
       </c>
       <c r="H11" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I11" s="28" t="str">
-        <f>IF($G11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="N11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -10567,11 +10550,11 @@
         <v>46304</v>
       </c>
       <c r="C12" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="28" t="str">
-        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F12" s="25" t="str">
@@ -10583,11 +10566,11 @@
         <v>46335</v>
       </c>
       <c r="H12" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I12" s="28" t="str">
-        <f>IF($G12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10601,11 +10584,11 @@
         <v>46305</v>
       </c>
       <c r="C13" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="28" t="str">
-        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F13" s="25" t="str">
@@ -10617,11 +10600,11 @@
         <v>46336</v>
       </c>
       <c r="H13" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I13" s="28" t="str">
-        <f>IF($G13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10635,11 +10618,11 @@
         <v>46306</v>
       </c>
       <c r="C14" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="28" t="str">
-        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F14" s="25" t="str">
@@ -10651,11 +10634,11 @@
         <v>46337</v>
       </c>
       <c r="H14" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I14" s="28" t="str">
-        <f>IF($G14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10669,11 +10652,11 @@
         <v>46307</v>
       </c>
       <c r="C15" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="28" t="str">
-        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F15" s="25" t="str">
@@ -10685,11 +10668,11 @@
         <v>46338</v>
       </c>
       <c r="H15" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I15" s="28" t="str">
-        <f>IF($G15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10703,11 +10686,11 @@
         <v>46308</v>
       </c>
       <c r="C16" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="28" t="str">
-        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F16" s="25" t="str">
@@ -10719,11 +10702,11 @@
         <v>46339</v>
       </c>
       <c r="H16" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I16" s="28" t="str">
-        <f>IF($G16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10737,11 +10720,11 @@
         <v>46309</v>
       </c>
       <c r="C17" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="28" t="str">
-        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F17" s="25" t="str">
@@ -10753,11 +10736,11 @@
         <v>46340</v>
       </c>
       <c r="H17" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I17" s="28" t="str">
-        <f>IF($G17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10771,11 +10754,11 @@
         <v>46310</v>
       </c>
       <c r="C18" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="28" t="str">
-        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F18" s="25" t="str">
@@ -10787,11 +10770,11 @@
         <v>46341</v>
       </c>
       <c r="H18" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I18" s="28" t="str">
-        <f>IF($G18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10805,11 +10788,11 @@
         <v>46311</v>
       </c>
       <c r="C19" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="28" t="str">
-        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F19" s="25" t="str">
@@ -10821,12 +10804,12 @@
         <v>46342</v>
       </c>
       <c r="H19" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
-        <v>Εορτή / Εκκλησιασμός</v>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <v/>
       </c>
       <c r="I19" s="28" t="str">
-        <f>IF($G19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
-        <v>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</v>
+        <f>IF($G19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -10839,11 +10822,11 @@
         <v>46312</v>
       </c>
       <c r="C20" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="28" t="str">
-        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F20" s="25" t="str">
@@ -10855,12 +10838,12 @@
         <v>46343</v>
       </c>
       <c r="H20" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
-        <v>Αργία / Διακοπές</v>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <v>Εορτή / Εκκλησιασμός</v>
       </c>
       <c r="I20" s="28" t="str">
-        <f>IF($G20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
-        <v>Επέτειος Πολυτεχνείου – Αργία</v>
+        <f>IF($G20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <v>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -10873,11 +10856,11 @@
         <v>46313</v>
       </c>
       <c r="C21" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="28" t="str">
-        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F21" s="25" t="str">
@@ -10889,11 +10872,11 @@
         <v>46344</v>
       </c>
       <c r="H21" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I21" s="28" t="str">
-        <f>IF($G21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10907,11 +10890,11 @@
         <v>46314</v>
       </c>
       <c r="C22" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="28" t="str">
-        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F22" s="25" t="str">
@@ -10923,11 +10906,11 @@
         <v>46345</v>
       </c>
       <c r="H22" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I22" s="28" t="str">
-        <f>IF($G22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10941,11 +10924,11 @@
         <v>46315</v>
       </c>
       <c r="C23" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F23" s="25" t="str">
@@ -10957,11 +10940,11 @@
         <v>46346</v>
       </c>
       <c r="H23" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I23" s="28" t="str">
-        <f>IF($G23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10975,11 +10958,11 @@
         <v>46316</v>
       </c>
       <c r="C24" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="28" t="str">
-        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F24" s="25" t="str">
@@ -10991,11 +10974,11 @@
         <v>46347</v>
       </c>
       <c r="H24" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I24" s="28" t="str">
-        <f>IF($G24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11009,11 +10992,11 @@
         <v>46317</v>
       </c>
       <c r="C25" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="28" t="str">
-        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F25" s="25" t="str">
@@ -11025,11 +11008,11 @@
         <v>46348</v>
       </c>
       <c r="H25" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I25" s="28" t="str">
-        <f>IF($G25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11043,11 +11026,11 @@
         <v>46318</v>
       </c>
       <c r="C26" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="28" t="str">
-        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F26" s="25" t="str">
@@ -11059,11 +11042,11 @@
         <v>46349</v>
       </c>
       <c r="H26" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I26" s="28" t="str">
-        <f>IF($G26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11077,11 +11060,11 @@
         <v>46319</v>
       </c>
       <c r="C27" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="28" t="str">
-        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F27" s="25" t="str">
@@ -11093,11 +11076,11 @@
         <v>46350</v>
       </c>
       <c r="H27" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I27" s="28" t="str">
-        <f>IF($G27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11111,11 +11094,11 @@
         <v>46320</v>
       </c>
       <c r="C28" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F28" s="25" t="str">
@@ -11127,11 +11110,11 @@
         <v>46351</v>
       </c>
       <c r="H28" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I28" s="28" t="str">
-        <f>IF($G28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11145,11 +11128,11 @@
         <v>46321</v>
       </c>
       <c r="C29" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v>Αργία / Διακοπές</v>
       </c>
       <c r="D29" s="28" t="str">
-        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v>Αγίου Δημητρίου – Ελευθέρια Θεσσαλονίκης (τοπική αργία)</v>
       </c>
       <c r="F29" s="25" t="str">
@@ -11161,11 +11144,11 @@
         <v>46352</v>
       </c>
       <c r="H29" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I29" s="28" t="str">
-        <f>IF($G29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11179,11 +11162,11 @@
         <v>46322</v>
       </c>
       <c r="C30" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v>Εορτή / Εκκλησιασμός</v>
       </c>
       <c r="D30" s="28" t="str">
-        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου (χωρίς μάθημα)</v>
       </c>
       <c r="F30" s="25" t="str">
@@ -11195,11 +11178,11 @@
         <v>46353</v>
       </c>
       <c r="H30" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I30" s="28" t="str">
-        <f>IF($G30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11213,11 +11196,11 @@
         <v>46323</v>
       </c>
       <c r="C31" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v>Αργία / Διακοπές</v>
       </c>
       <c r="D31" s="28" t="str">
-        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v>Εθνική επέτειος 28ης Οκτωβρίου – Αργία</v>
       </c>
       <c r="F31" s="25" t="str">
@@ -11229,11 +11212,11 @@
         <v>46354</v>
       </c>
       <c r="H31" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I31" s="28" t="str">
-        <f>IF($G31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11247,11 +11230,11 @@
         <v>46324</v>
       </c>
       <c r="C32" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="28" t="str">
-        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F32" s="25" t="str">
@@ -11263,11 +11246,11 @@
         <v>46355</v>
       </c>
       <c r="H32" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I32" s="28" t="str">
-        <f>IF($G32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11281,11 +11264,11 @@
         <v>46325</v>
       </c>
       <c r="C33" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="28" t="str">
-        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F33" s="25" t="str">
@@ -11297,11 +11280,11 @@
         <v>46356</v>
       </c>
       <c r="H33" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I33" s="28" t="str">
-        <f>IF($G33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11315,11 +11298,11 @@
         <v>46326</v>
       </c>
       <c r="C34" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="28" t="str">
-        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F34" s="25" t="str">
@@ -11331,17 +11314,17 @@
         <v/>
       </c>
       <c r="H34" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="I34" s="28" t="str">
-        <f>IF($G34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($G34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -11415,60 +11398,60 @@
     <mergeCell ref="G38:I38"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:D34">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>$C4="Αργία / Διακοπές"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="2">
+    <cfRule type="expression" dxfId="26" priority="2">
       <formula>$C4="Εορτή / Εκκλησιασμός"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="3">
+    <cfRule type="expression" dxfId="25" priority="3">
       <formula>$C4="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="4">
+    <cfRule type="expression" dxfId="24" priority="4">
       <formula>$C4="Σύλλογος διδασκόντων"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="5">
+    <cfRule type="expression" dxfId="23" priority="5">
       <formula>$C4="Ενημέρωση γονέων / Έλεγχοι"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="6">
+    <cfRule type="expression" dxfId="22" priority="6">
       <formula>$C4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="7">
+    <cfRule type="expression" dxfId="21" priority="7">
       <formula>$C4="Επιμόρφωση εκπαιδευτικών"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="8">
+    <cfRule type="expression" dxfId="20" priority="8">
       <formula>$C4="Δράση / Πρόγραμμα / Όμιλος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="9">
+    <cfRule type="expression" dxfId="19" priority="9">
       <formula>IF($B4="",0,WEEKDAY($B4,2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:I34">
-    <cfRule type="expression" dxfId="17" priority="10">
+    <cfRule type="expression" dxfId="18" priority="10">
       <formula>$H4="Αργία / Διακοπές"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="11">
+    <cfRule type="expression" dxfId="17" priority="11">
       <formula>$H4="Εορτή / Εκκλησιασμός"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="12">
+    <cfRule type="expression" dxfId="16" priority="12">
       <formula>$H4="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="13">
+    <cfRule type="expression" dxfId="15" priority="13">
       <formula>$H4="Σύλλογος διδασκόντων"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="14" priority="14">
       <formula>$H4="Ενημέρωση γονέων / Έλεγχοι"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="15">
+    <cfRule type="expression" dxfId="13" priority="15">
       <formula>$H4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="16">
+    <cfRule type="expression" dxfId="12" priority="16">
       <formula>$H4="Επιμόρφωση εκπαιδευτικών"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="17">
+    <cfRule type="expression" dxfId="11" priority="17">
       <formula>$H4="Δράση / Πρόγραμμα / Όμιλος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="18">
+    <cfRule type="expression" dxfId="10" priority="18">
       <formula>IF($G4="",0,WEEKDAY($G4,2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11508,17 +11491,17 @@
       <c r="C1" s="60"/>
       <c r="D1" s="60"/>
       <c r="F1" s="36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G1" s="34"/>
       <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
         <v>69</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>70</v>
-      </c>
-      <c r="K1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -11530,13 +11513,13 @@
       <c r="C2" s="61"/>
       <c r="D2" s="61"/>
       <c r="F2" s="34" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J2">
         <v>9</v>
@@ -11550,18 +11533,18 @@
         <v>42</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F3" s="34"/>
       <c r="G3" s="34"/>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J3">
         <v>10</v>
@@ -11580,17 +11563,17 @@
         <v>46327</v>
       </c>
       <c r="C4" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="28" t="str">
-        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F4" s="34"/>
       <c r="G4" s="34"/>
       <c r="I4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J4">
         <v>11</v>
@@ -11609,22 +11592,22 @@
         <v>46328</v>
       </c>
       <c r="C5" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="28" t="str">
-        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F5" s="34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G5" s="34">
         <f>INDEX($J$2:$J$11,MATCH($G$2,$I$2:$I$11,0))</f>
         <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -11643,22 +11626,22 @@
         <v>46329</v>
       </c>
       <c r="C6" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="28" t="str">
-        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F6" s="34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G6" s="34">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($K$2:$K$11,MATCH($G$2,$I$2:$I$11,0))</f>
         <v>2026</v>
       </c>
       <c r="I6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -11677,17 +11660,17 @@
         <v>46330</v>
       </c>
       <c r="C7" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v>Επιμόρφωση εκπαιδευτικών</v>
       </c>
       <c r="D7" s="28" t="str">
-        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives»</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34"/>
       <c r="I7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -11706,17 +11689,17 @@
         <v>46331</v>
       </c>
       <c r="C8" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="28" t="str">
-        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J8">
         <v>3</v>
@@ -11735,15 +11718,15 @@
         <v>46332</v>
       </c>
       <c r="C9" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="28" t="str">
-        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -11762,15 +11745,15 @@
         <v>46333</v>
       </c>
       <c r="C10" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="28" t="str">
-        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -11789,15 +11772,15 @@
         <v>46334</v>
       </c>
       <c r="C11" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="28" t="str">
-        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
       <c r="I11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -11816,11 +11799,11 @@
         <v>46335</v>
       </c>
       <c r="C12" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="28" t="str">
-        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11834,11 +11817,11 @@
         <v>46336</v>
       </c>
       <c r="C13" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="28" t="str">
-        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11852,11 +11835,11 @@
         <v>46337</v>
       </c>
       <c r="C14" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="28" t="str">
-        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11870,11 +11853,11 @@
         <v>46338</v>
       </c>
       <c r="C15" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="28" t="str">
-        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11888,11 +11871,11 @@
         <v>46339</v>
       </c>
       <c r="C16" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="28" t="str">
-        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11906,11 +11889,11 @@
         <v>46340</v>
       </c>
       <c r="C17" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="28" t="str">
-        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11924,11 +11907,11 @@
         <v>46341</v>
       </c>
       <c r="C18" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="28" t="str">
-        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11942,12 +11925,12 @@
         <v>46342</v>
       </c>
       <c r="C19" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
-        <v>Εορτή / Εκκλησιασμός</v>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <v/>
       </c>
       <c r="D19" s="28" t="str">
-        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
-        <v>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</v>
+        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -11960,12 +11943,12 @@
         <v>46343</v>
       </c>
       <c r="C20" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
-        <v>Αργία / Διακοπές</v>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <v>Εορτή / Εκκλησιασμός</v>
       </c>
       <c r="D20" s="28" t="str">
-        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
-        <v>Επέτειος Πολυτεχνείου – Αργία</v>
+        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <v>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -11978,11 +11961,11 @@
         <v>46344</v>
       </c>
       <c r="C21" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="28" t="str">
-        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11996,11 +11979,11 @@
         <v>46345</v>
       </c>
       <c r="C22" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="28" t="str">
-        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12014,11 +11997,11 @@
         <v>46346</v>
       </c>
       <c r="C23" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12032,11 +12015,11 @@
         <v>46347</v>
       </c>
       <c r="C24" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="28" t="str">
-        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12050,11 +12033,11 @@
         <v>46348</v>
       </c>
       <c r="C25" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="28" t="str">
-        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12068,11 +12051,11 @@
         <v>46349</v>
       </c>
       <c r="C26" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="28" t="str">
-        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12086,11 +12069,11 @@
         <v>46350</v>
       </c>
       <c r="C27" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="28" t="str">
-        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12104,11 +12087,11 @@
         <v>46351</v>
       </c>
       <c r="C28" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12122,11 +12105,11 @@
         <v>46352</v>
       </c>
       <c r="C29" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="28" t="str">
-        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12140,11 +12123,11 @@
         <v>46353</v>
       </c>
       <c r="C30" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="28" t="str">
-        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12158,11 +12141,11 @@
         <v>46354</v>
       </c>
       <c r="C31" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="28" t="str">
-        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12176,11 +12159,11 @@
         <v>46355</v>
       </c>
       <c r="C32" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="28" t="str">
-        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12194,11 +12177,11 @@
         <v>46356</v>
       </c>
       <c r="C33" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="28" t="str">
-        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12212,17 +12195,17 @@
         <v/>
       </c>
       <c r="C34" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="28" t="str">
-        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -12291,31 +12274,31 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:D34">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$C4="Αργία / Διακοπές"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>$C4="Εορτή / Εκκλησιασμός"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$C4="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>$C4="Σύλλογος διδασκόντων"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$C4="Ενημέρωση γονέων / Έλεγχοι"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>$C4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="7">
+    <cfRule type="expression" dxfId="3" priority="7">
       <formula>$C4="Επιμόρφωση εκπαιδευτικών"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="8">
+    <cfRule type="expression" dxfId="2" priority="8">
       <formula>$C4="Δράση / Πρόγραμμα / Όμιλος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="1" priority="9">
       <formula>IF($B4="",0,WEEKDAY($B4,2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karel\Downloads\draseis\draseis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A456699-72EF-43BF-B5DB-291A38801B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F88E49D-0FE6-4CAB-AA8C-227585E98107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -186,27 +186,15 @@
     <t>ΕΜΦΑΝΙΣΗ</t>
   </si>
   <si>
-    <t>Αγιασμός – Έναρξη σχολικού έτους. Διαμοιρασμός σε τμήματα.</t>
-  </si>
-  <si>
     <t>Έναρξη μαθημάτων</t>
   </si>
   <si>
-    <t>Αγίου Δημητρίου – Ελευθέρια Θεσσαλονίκης (τοπική αργία)</t>
-  </si>
-  <si>
-    <t>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου (χωρίς μάθημα)</t>
-  </si>
-  <si>
     <t>Εθνική επέτειος 28ης Οκτωβρίου – Αργία</t>
   </si>
   <si>
     <t>08:45-11:15</t>
   </si>
   <si>
-    <t>Διαδικτυακή εκπαίδευση «Kids Save Lives»</t>
-  </si>
-  <si>
     <t>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</t>
   </si>
   <si>
@@ -430,6 +418,18 @@
   </si>
   <si>
     <t>Νέα δράση: γράψε την στην κίτρινη (πρώτη κενή) γραμμή στο τέλος – αναλυτικά βήμα–βήμα πιο κάτω.</t>
+  </si>
+  <si>
+    <t>Αγιασμός – Έναρξη σχολικού έτους</t>
+  </si>
+  <si>
+    <t>Αγίου Δημητρίου</t>
+  </si>
+  <si>
+    <t>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου</t>
+  </si>
+  <si>
+    <t>Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμόρφωση μαθητών και εκπαιδευτικών</t>
   </si>
 </sst>
 </file>
@@ -950,14 +950,6 @@
   <dxfs count="37">
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill>
           <bgColor rgb="FFE4E4E4"/>
         </patternFill>
@@ -1142,6 +1134,14 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF4B6B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1537,7 +1537,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
@@ -1550,10 +1550,10 @@
     </row>
     <row r="10" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="55" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1562,48 +1562,48 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B12" s="48"/>
     </row>
     <row r="13" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="49" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="49" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="49" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A16" s="49" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="49" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1612,72 +1612,72 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" s="49" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A21" s="49" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" s="49" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A23" s="49" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A24" s="49" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A25" s="49" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A26" s="49" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A27" s="51" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1686,24 +1686,24 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="47" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B29" s="48"/>
     </row>
     <row r="30" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="49" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B30" s="50" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="53" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B31" s="54" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -1753,7 +1753,7 @@
         <v>18</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1976,13 +1976,13 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="19">
         <v>46276</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="21" t="s">
-        <v>45</v>
+        <v>123</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>26</v>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="J2" s="23" t="str">
         <f t="shared" ref="J2:J64" si="1">IF($A2="","",IF($B2="","",$B2&amp;"  ")&amp;$C2&amp;IF($E2="","","  ("&amp;$E2&amp;")"))</f>
-        <v>Αγιασμός – Έναρξη σχολικού έτους. Διαμοιρασμός σε τμήματα.</v>
+        <v>Αγιασμός – Έναρξη σχολικού έτους</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>30</v>
@@ -2030,13 +2030,13 @@
         <v>Έναρξη μαθημάτων</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>46321</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="21" t="s">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>25</v>
@@ -2054,16 +2054,16 @@
       </c>
       <c r="J4" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Αγίου Δημητρίου – Ελευθέρια Θεσσαλονίκης (τοπική αργία)</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+        <v>Αγίου Δημητρίου</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="19">
         <v>46322</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="21" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>26</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="J5" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου (χωρίς μάθημα)</v>
+        <v>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>25</v>
@@ -2111,15 +2111,15 @@
         <v>Εθνική επέτειος 28ης Οκτωβρίου – Αργία</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="19">
         <v>46330</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>31</v>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="J7" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives»</v>
+        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμόρφωση μαθητών και εκπαιδευτικών</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="21" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>26</v>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="21" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>30</v>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D10" s="21" t="s">
         <v>25</v>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>25</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D12" s="21" t="s">
         <v>25</v>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>25</v>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>25</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D15" s="21" t="s">
         <v>25</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>25</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D17" s="21" t="s">
         <v>25</v>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D18" s="21" t="s">
         <v>25</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>25</v>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D20" s="21" t="s">
         <v>25</v>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="21" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D21" s="21" t="s">
         <v>30</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="21" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D22" s="21" t="s">
         <v>30</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="21" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D23" s="21" t="s">
         <v>26</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D24" s="21" t="s">
         <v>25</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="21" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>26</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="21" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D26" s="21" t="s">
         <v>25</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D27" s="21" t="s">
         <v>25</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D28" s="21" t="s">
         <v>25</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>25</v>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>25</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D31" s="21" t="s">
         <v>25</v>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D32" s="21" t="s">
         <v>25</v>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D33" s="21" t="s">
         <v>25</v>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D34" s="21" t="s">
         <v>25</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D35" s="21" t="s">
         <v>25</v>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D36" s="21" t="s">
         <v>25</v>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="21" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D37" s="21" t="s">
         <v>30</v>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="21" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D38" s="21" t="s">
         <v>25</v>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="21" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D39" s="21" t="s">
         <v>30</v>
@@ -10021,7 +10021,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:G9">
-    <cfRule type="expression" dxfId="0" priority="20">
+    <cfRule type="expression" dxfId="27" priority="20">
       <formula>AND($A9="",#REF!&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10083,16 +10083,16 @@
       <c r="H1" s="60"/>
       <c r="I1" s="60"/>
       <c r="K1" s="36" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="O1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -10111,13 +10111,13 @@
       <c r="H2" s="61"/>
       <c r="I2" s="61"/>
       <c r="K2" s="34" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L2" s="38" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="N2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="O2">
         <v>9</v>
@@ -10131,34 +10131,34 @@
         <v>42</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C3" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F3" s="24" t="s">
         <v>42</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H3" s="24" t="s">
         <v>33</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K3" s="35" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="O3">
         <v>10</v>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="K4" s="34"/>
       <c r="N4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="O4">
         <v>11</v>
@@ -10245,14 +10245,14 @@
         <v/>
       </c>
       <c r="K5" s="34" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="L5">
         <f>INDEX($O$2:$O$11,MATCH($L$2,$N$2:$N$11,0))</f>
         <v>10</v>
       </c>
       <c r="N5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="O5">
         <v>12</v>
@@ -10295,14 +10295,14 @@
         <v/>
       </c>
       <c r="K6" s="34" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L6">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($P$2:$P$11,MATCH($L$2,$N$2:$N$11,0))</f>
         <v>2026</v>
       </c>
       <c r="N6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -10342,17 +10342,17 @@
       </c>
       <c r="I7" s="28" t="str">
         <f>IF($G7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
-        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives»</v>
+        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμόρφωση μαθητών και εκπαιδευτικών</v>
       </c>
       <c r="K7" s="34" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L7">
         <f>INDEX($O$2:$O$11,MATCH($L$3,$N$2:$N$11,0))</f>
         <v>11</v>
       </c>
       <c r="N7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="O7">
         <v>2</v>
@@ -10395,14 +10395,14 @@
         <v/>
       </c>
       <c r="K8" s="34" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L8">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($P$2:$P$11,MATCH($L$3,$N$2:$N$11,0))</f>
         <v>2026</v>
       </c>
       <c r="N8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="O8">
         <v>3</v>
@@ -10445,7 +10445,7 @@
         <v/>
       </c>
       <c r="N9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="O9">
         <v>4</v>
@@ -10488,7 +10488,7 @@
         <v/>
       </c>
       <c r="N10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -10531,7 +10531,7 @@
         <v/>
       </c>
       <c r="N11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -11133,7 +11133,7 @@
       </c>
       <c r="D29" s="28" t="str">
         <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
-        <v>Αγίου Δημητρίου – Ελευθέρια Θεσσαλονίκης (τοπική αργία)</v>
+        <v>Αγίου Δημητρίου</v>
       </c>
       <c r="F29" s="25" t="str">
         <f t="shared" si="2"/>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="D30" s="28" t="str">
         <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
-        <v>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου (χωρίς μάθημα)</v>
+        <v>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου</v>
       </c>
       <c r="F30" s="25" t="str">
         <f t="shared" si="2"/>
@@ -11324,7 +11324,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -11398,60 +11398,60 @@
     <mergeCell ref="G38:I38"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:D34">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>$C4="Αργία / Διακοπές"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="2">
+    <cfRule type="expression" dxfId="25" priority="2">
       <formula>$C4="Εορτή / Εκκλησιασμός"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="3">
+    <cfRule type="expression" dxfId="24" priority="3">
       <formula>$C4="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="4">
+    <cfRule type="expression" dxfId="23" priority="4">
       <formula>$C4="Σύλλογος διδασκόντων"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="5">
+    <cfRule type="expression" dxfId="22" priority="5">
       <formula>$C4="Ενημέρωση γονέων / Έλεγχοι"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="6">
+    <cfRule type="expression" dxfId="21" priority="6">
       <formula>$C4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="7">
+    <cfRule type="expression" dxfId="20" priority="7">
       <formula>$C4="Επιμόρφωση εκπαιδευτικών"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="8">
+    <cfRule type="expression" dxfId="19" priority="8">
       <formula>$C4="Δράση / Πρόγραμμα / Όμιλος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="9">
+    <cfRule type="expression" dxfId="18" priority="9">
       <formula>IF($B4="",0,WEEKDAY($B4,2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:I34">
-    <cfRule type="expression" dxfId="18" priority="10">
+    <cfRule type="expression" dxfId="17" priority="10">
       <formula>$H4="Αργία / Διακοπές"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="11">
+    <cfRule type="expression" dxfId="16" priority="11">
       <formula>$H4="Εορτή / Εκκλησιασμός"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="12">
+    <cfRule type="expression" dxfId="15" priority="12">
       <formula>$H4="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="13">
+    <cfRule type="expression" dxfId="14" priority="13">
       <formula>$H4="Σύλλογος διδασκόντων"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>$H4="Ενημέρωση γονέων / Έλεγχοι"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="12" priority="15">
       <formula>$H4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16">
+    <cfRule type="expression" dxfId="11" priority="16">
       <formula>$H4="Επιμόρφωση εκπαιδευτικών"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="17">
+    <cfRule type="expression" dxfId="10" priority="17">
       <formula>$H4="Δράση / Πρόγραμμα / Όμιλος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="18">
+    <cfRule type="expression" dxfId="9" priority="18">
       <formula>IF($G4="",0,WEEKDAY($G4,2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11491,17 +11491,17 @@
       <c r="C1" s="60"/>
       <c r="D1" s="60"/>
       <c r="F1" s="36" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G1" s="34"/>
       <c r="I1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="K1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -11513,13 +11513,13 @@
       <c r="C2" s="61"/>
       <c r="D2" s="61"/>
       <c r="F2" s="34" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J2">
         <v>9</v>
@@ -11533,18 +11533,18 @@
         <v>42</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C3" s="24" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F3" s="34"/>
       <c r="G3" s="34"/>
       <c r="I3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J3">
         <v>10</v>
@@ -11573,7 +11573,7 @@
       <c r="F4" s="34"/>
       <c r="G4" s="34"/>
       <c r="I4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="J4">
         <v>11</v>
@@ -11600,14 +11600,14 @@
         <v/>
       </c>
       <c r="F5" s="34" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G5" s="34">
         <f>INDEX($J$2:$J$11,MATCH($G$2,$I$2:$I$11,0))</f>
         <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -11634,14 +11634,14 @@
         <v/>
       </c>
       <c r="F6" s="34" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G6" s="34">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($K$2:$K$11,MATCH($G$2,$I$2:$I$11,0))</f>
         <v>2026</v>
       </c>
       <c r="I6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -11665,12 +11665,12 @@
       </c>
       <c r="D7" s="28" t="str">
         <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
-        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives»</v>
+        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμόρφωση μαθητών και εκπαιδευτικών</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34"/>
       <c r="I7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -11699,7 +11699,7 @@
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
       <c r="I8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J8">
         <v>3</v>
@@ -11726,7 +11726,7 @@
         <v/>
       </c>
       <c r="I9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -11753,7 +11753,7 @@
         <v/>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -11780,7 +11780,7 @@
         <v/>
       </c>
       <c r="I11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -12205,7 +12205,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -12274,31 +12274,31 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:D34">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$C4="Αργία / Διακοπές"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>$C4="Εορτή / Εκκλησιασμός"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>$C4="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>$C4="Σύλλογος διδασκόντων"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>$C4="Ενημέρωση γονέων / Έλεγχοι"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>$C4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="2" priority="7">
       <formula>$C4="Επιμόρφωση εκπαιδευτικών"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="8">
+    <cfRule type="expression" dxfId="1" priority="8">
       <formula>$C4="Δράση / Πρόγραμμα / Όμιλος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="9">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>IF($B4="",0,WEEKDAY($B4,2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karel\Downloads\draseis\draseis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F88E49D-0FE6-4CAB-AA8C-227585E98107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A84F33-6EB6-4B04-AE56-785711F7D057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -429,7 +429,7 @@
     <t>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου</t>
   </si>
   <si>
-    <t>Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμόρφωση μαθητών και εκπαιδευτικών</t>
+    <t>Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</t>
   </si>
 </sst>
 </file>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="J7" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμόρφωση μαθητών και εκπαιδευτικών</v>
+        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="I7" s="28" t="str">
         <f>IF($G7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
-        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμόρφωση μαθητών και εκπαιδευτικών</v>
+        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</v>
       </c>
       <c r="K7" s="34" t="s">
         <v>82</v>
@@ -11118,7 +11118,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Δευ</v>
@@ -11152,7 +11152,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Τρί</v>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="D7" s="28" t="str">
         <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
-        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμόρφωση μαθητών και εκπαιδευτικών</v>
+        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34"/>

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -144,7 +144,7 @@
     <t>Ορόσημο / Εξετάσεις</t>
   </si>
   <si>
-    <t>Επιμόρφωση εκπαιδευτικών</t>
+    <t>Δράση</t>
   </si>
   <si>
     <t>Δράση / Πρόγραμμα / Όμιλος</t>
@@ -10014,7 +10014,7 @@
       <formula>$D2="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="29" priority="8">
-      <formula>$D2="Επιμόρφωση εκπαιδευτικών"</formula>
+      <formula>$D2="Δράση"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="28" priority="9">
       <formula>$D2="Δράση / Πρόγραμμα / Όμιλος"</formula>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="H7" s="27" t="str">
         <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
-        <v>Επιμόρφωση εκπαιδευτικών</v>
+        <v>Δράση</v>
       </c>
       <c r="I7" s="28" t="str">
         <f>IF($G7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
@@ -11417,7 +11417,7 @@
       <formula>$C4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="7">
-      <formula>$C4="Επιμόρφωση εκπαιδευτικών"</formula>
+      <formula>$C4="Δράση"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="8">
       <formula>$C4="Δράση / Πρόγραμμα / Όμιλος"</formula>
@@ -11446,7 +11446,7 @@
       <formula>$H4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="16">
-      <formula>$H4="Επιμόρφωση εκπαιδευτικών"</formula>
+      <formula>$H4="Δράση"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="17">
       <formula>$H4="Δράση / Πρόγραμμα / Όμιλος"</formula>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="C7" s="27" t="str">
         <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
-        <v>Επιμόρφωση εκπαιδευτικών</v>
+        <v>Δράση</v>
       </c>
       <c r="D7" s="28" t="str">
         <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
@@ -12293,7 +12293,7 @@
       <formula>$C4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="7">
-      <formula>$C4="Επιμόρφωση εκπαιδευτικών"</formula>
+      <formula>$C4="Δράση"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="8">
       <formula>$C4="Δράση / Πρόγραμμα / Όμιλος"</formula>

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karel\Downloads\draseis\draseis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A84F33-6EB6-4B04-AE56-785711F7D057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F16BF0-6EB1-4454-8AF7-D78160817342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,10 +20,10 @@
     <sheet name="ΑΦΙΣΑ_1ΜΗΝΑΣ" sheetId="20" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ΔΡΑΣΕΙΣ!$A$1:$J$398</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ΔΡΑΣΕΙΣ!$A$1:$J$402</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">ΑΦΙΣΑ_1ΜΗΝΑΣ!$A$1:$D$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">ΑΦΙΣΑ_ΕΠΙΛΟΓΗΣ!$A$1:$I$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">ΔΡΑΣΕΙΣ!$A$1:$G$118</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">ΔΡΑΣΕΙΣ!$A$1:$G$122</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">ΑΦΙΣΑ_1ΜΗΝΑΣ!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">ΑΦΙΣΑ_ΕΠΙΛΟΓΗΣ!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">ΔΡΑΣΕΙΣ!$1:$1</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="127">
   <si>
     <t>3ο ΓΥΜΝΑΣΙΟ ΠΟΛΙΧΝΗΣ  ·  ΗΜΕΡΟΛΟΓΙΟ ΔΡΑΣΕΩΝ  ·  ΣΧΟΛΙΚΟ ΕΤΟΣ 2026-27</t>
   </si>
@@ -117,9 +117,6 @@
     <t>ΠΡΟΣΩΡΙΝΕΣ ΗΜΕΡΟΜΗΝΙΕΣ</t>
   </si>
   <si>
-    <t>Λήξη Α΄ τετραμήνου, επιστροφή μετά το Πάσχα και λήξη μαθημάτων Γυμνασίου</t>
-  </si>
-  <si>
     <t>οριστικοποιούνται με εγκύκλιο του Υπουργείου. Είναι σημειωμένες ως εκτίμηση.</t>
   </si>
   <si>
@@ -225,9 +222,6 @@
     <t>Διακοπές Πάσχα</t>
   </si>
   <si>
-    <t>Επαναλειτουργία σχολείου μετά το Πάσχα (εκτίμηση)</t>
-  </si>
-  <si>
     <t>Αγίου Πνεύματος – Αργία</t>
   </si>
   <si>
@@ -430,6 +424,12 @@
   </si>
   <si>
     <t>Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</t>
+  </si>
+  <si>
+    <t>Επαναλειτουργία σχολείου μετά το Πάσχα</t>
+  </si>
+  <si>
+    <t>Λήξη Α΄ τετραμήνου και λήξη μαθημάτων Γυμνασίου</t>
   </si>
 </sst>
 </file>
@@ -947,7 +947,7 @@
   <cellStyles count="1">
     <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="39">
     <dxf>
       <fill>
         <patternFill>
@@ -1134,6 +1134,22 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF4B6B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1537,7 +1553,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
@@ -1550,10 +1566,10 @@
     </row>
     <row r="10" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="55" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1562,48 +1578,48 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B12" s="48"/>
     </row>
     <row r="13" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="49" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="49" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="49" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A16" s="49" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="49" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1612,72 +1628,72 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" s="49" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A21" s="49" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" s="49" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A23" s="49" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A24" s="49" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A25" s="49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A26" s="49" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A27" s="51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1686,24 +1702,24 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="47" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B29" s="48"/>
     </row>
     <row r="30" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="49" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B30" s="50" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B31" s="54" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -1753,7 +1769,7 @@
         <v>18</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1777,66 +1793,66 @@
         <v>21</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="7"/>
       <c r="B46" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
       <c r="B47" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="10"/>
       <c r="B48" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="11"/>
       <c r="B49" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="12"/>
       <c r="B50" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="14"/>
       <c r="B52" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="15"/>
       <c r="B53" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1860,63 +1876,63 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>33</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="9"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="10"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="12"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="13"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="14"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="15"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1930,7 +1946,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K398"/>
+  <dimension ref="A1:K402"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
@@ -1946,34 +1962,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="C1" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="D1" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="I1" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="J1" s="45" t="s">
         <v>43</v>
-      </c>
-      <c r="J1" s="45" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1982,16 +1998,16 @@
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="21"/>
       <c r="G2" s="21"/>
       <c r="H2" s="22" t="str">
-        <f t="shared" ref="H2:H64" si="0">IF($A2="","",CHOOSE(WEEKDAY($A2,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" ref="H2:H68" si="0">IF($A2="","",CHOOSE(WEEKDAY($A2,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v>Παρ</v>
       </c>
       <c r="I2" s="23" t="str">
@@ -1999,7 +2015,7 @@
         <v>46276#1</v>
       </c>
       <c r="J2" s="23" t="str">
-        <f t="shared" ref="J2:J64" si="1">IF($A2="","",IF($B2="","",$B2&amp;"  ")&amp;$C2&amp;IF($E2="","","  ("&amp;$E2&amp;")"))</f>
+        <f t="shared" ref="J2:J68" si="1">IF($A2="","",IF($B2="","",$B2&amp;"  ")&amp;$C2&amp;IF($E2="","","  ("&amp;$E2&amp;")"))</f>
         <v>Αγιασμός – Έναρξη σχολικού έτους</v>
       </c>
     </row>
@@ -2009,10 +2025,10 @@
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
@@ -2036,10 +2052,10 @@
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4" s="21"/>
@@ -2063,10 +2079,10 @@
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
@@ -2090,10 +2106,10 @@
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
@@ -2116,13 +2132,13 @@
         <v>46330</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -2146,10 +2162,10 @@
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
@@ -2173,10 +2189,10 @@
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" s="21"/>
       <c r="F9" s="21"/>
@@ -2200,10 +2216,10 @@
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" s="21"/>
       <c r="F10" s="21"/>
@@ -2227,10 +2243,10 @@
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="21"/>
       <c r="F11" s="21"/>
@@ -2254,10 +2270,10 @@
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="21"/>
       <c r="F12" s="21"/>
@@ -2281,10 +2297,10 @@
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
@@ -2308,10 +2324,10 @@
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
@@ -2335,10 +2351,10 @@
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
@@ -2362,10 +2378,10 @@
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
@@ -2389,10 +2405,10 @@
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
@@ -2416,10 +2432,10 @@
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
@@ -2443,10 +2459,10 @@
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
@@ -2470,10 +2486,10 @@
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
@@ -2497,10 +2513,10 @@
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
@@ -2524,10 +2540,10 @@
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" s="21"/>
       <c r="F22" s="21"/>
@@ -2551,10 +2567,10 @@
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
@@ -2578,10 +2594,10 @@
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
@@ -2605,10 +2621,10 @@
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
@@ -2632,10 +2648,10 @@
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
@@ -2659,10 +2675,10 @@
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
@@ -2686,10 +2702,10 @@
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
@@ -2713,10 +2729,10 @@
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
@@ -2740,10 +2756,10 @@
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E30" s="21"/>
       <c r="F30" s="21"/>
@@ -2767,10 +2783,10 @@
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
@@ -2790,25 +2806,25 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="19">
-        <v>46510</v>
+        <v>46508</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
       <c r="G32" s="21"/>
       <c r="H32" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Σάβ</v>
       </c>
       <c r="I32" s="23" t="str">
         <f>IF($A32="","",$A32&amp;"#"&amp;COUNTIF($A$2:$A32,$A32))</f>
-        <v>46510#1</v>
+        <v>46508#1</v>
       </c>
       <c r="J32" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2817,25 +2833,25 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="19">
-        <v>46511</v>
+        <v>46509</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E33" s="21"/>
       <c r="F33" s="21"/>
       <c r="G33" s="21"/>
       <c r="H33" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Κυρ</v>
       </c>
       <c r="I33" s="23" t="str">
         <f>IF($A33="","",$A33&amp;"#"&amp;COUNTIF($A$2:$A33,$A33))</f>
-        <v>46511#1</v>
+        <v>46509#1</v>
       </c>
       <c r="J33" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2844,25 +2860,25 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="19">
-        <v>46512</v>
+        <v>46510</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E34" s="21"/>
       <c r="F34" s="21"/>
       <c r="G34" s="21"/>
       <c r="H34" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Δευ</v>
       </c>
       <c r="I34" s="23" t="str">
         <f>IF($A34="","",$A34&amp;"#"&amp;COUNTIF($A$2:$A34,$A34))</f>
-        <v>46512#1</v>
+        <v>46510#1</v>
       </c>
       <c r="J34" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2871,25 +2887,25 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="19">
-        <v>46513</v>
+        <v>46511</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
       <c r="G35" s="21"/>
       <c r="H35" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Τρί</v>
       </c>
       <c r="I35" s="23" t="str">
         <f>IF($A35="","",$A35&amp;"#"&amp;COUNTIF($A$2:$A35,$A35))</f>
-        <v>46513#1</v>
+        <v>46511#1</v>
       </c>
       <c r="J35" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2898,25 +2914,25 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="19">
-        <v>46514</v>
+        <v>46512</v>
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
       <c r="G36" s="21"/>
       <c r="H36" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Τετ</v>
       </c>
       <c r="I36" s="23" t="str">
         <f>IF($A36="","",$A36&amp;"#"&amp;COUNTIF($A$2:$A36,$A36))</f>
-        <v>46514#1</v>
+        <v>46512#1</v>
       </c>
       <c r="J36" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2925,167 +2941,191 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
-        <v>46517</v>
+        <v>46513</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
       <c r="G37" s="21"/>
       <c r="H37" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I37" s="23" t="str">
         <f>IF($A37="","",$A37&amp;"#"&amp;COUNTIF($A$2:$A37,$A37))</f>
-        <v>46517#1</v>
+        <v>46513#1</v>
       </c>
       <c r="J37" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Επαναλειτουργία σχολείου μετά το Πάσχα (εκτίμηση)</v>
+        <v>Διακοπές Πάσχα</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="19">
-        <v>46559</v>
+        <v>46514</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
       <c r="H38" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Παρ</v>
       </c>
       <c r="I38" s="23" t="str">
         <f>IF($A38="","",$A38&amp;"#"&amp;COUNTIF($A$2:$A38,$A38))</f>
-        <v>46559#1</v>
+        <v>46514#1</v>
       </c>
       <c r="J38" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Αγίου Πνεύματος – Αργία</v>
+        <v>Διακοπές Πάσχα</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="19">
-        <v>46568</v>
+        <v>46515</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="21" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E39" s="21"/>
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
       <c r="H39" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Σάβ</v>
       </c>
       <c r="I39" s="23" t="str">
         <f>IF($A39="","",$A39&amp;"#"&amp;COUNTIF($A$2:$A39,$A39))</f>
-        <v>46568#1</v>
+        <v>46515#1</v>
       </c>
       <c r="J39" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Λήξη διδακτικού έτους</v>
+        <v>Διακοπές Πάσχα</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="19"/>
+      <c r="A40" s="19">
+        <v>46516</v>
+      </c>
       <c r="B40" s="20"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
+      <c r="C40" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>24</v>
+      </c>
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
       <c r="H40" s="22" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Κυρ</v>
       </c>
       <c r="I40" s="23" t="str">
         <f>IF($A40="","",$A40&amp;"#"&amp;COUNTIF($A$2:$A40,$A40))</f>
-        <v/>
+        <v>46516#1</v>
       </c>
       <c r="J40" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Διακοπές Πάσχα</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
+      <c r="A41" s="19">
+        <v>46517</v>
+      </c>
       <c r="B41" s="20"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
+      <c r="C41" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>29</v>
+      </c>
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="22" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Δευ</v>
       </c>
       <c r="I41" s="23" t="str">
         <f>IF($A41="","",$A41&amp;"#"&amp;COUNTIF($A$2:$A41,$A41))</f>
-        <v/>
+        <v>46517#1</v>
       </c>
       <c r="J41" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Επαναλειτουργία σχολείου μετά το Πάσχα</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="19"/>
+      <c r="A42" s="19">
+        <v>46559</v>
+      </c>
       <c r="B42" s="20"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
+      <c r="C42" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>24</v>
+      </c>
       <c r="E42" s="21"/>
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
       <c r="H42" s="22" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Δευ</v>
       </c>
       <c r="I42" s="23" t="str">
         <f>IF($A42="","",$A42&amp;"#"&amp;COUNTIF($A$2:$A42,$A42))</f>
-        <v/>
+        <v>46559#1</v>
       </c>
       <c r="J42" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Αγίου Πνεύματος – Αργία</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
+      <c r="A43" s="19">
+        <v>46568</v>
+      </c>
       <c r="B43" s="20"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
+      <c r="C43" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>29</v>
+      </c>
       <c r="E43" s="21"/>
       <c r="F43" s="21"/>
       <c r="G43" s="21"/>
       <c r="H43" s="22" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Τετ</v>
       </c>
       <c r="I43" s="23" t="str">
         <f>IF($A43="","",$A43&amp;"#"&amp;COUNTIF($A$2:$A43,$A43))</f>
-        <v/>
+        <v>46568#1</v>
       </c>
       <c r="J43" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Λήξη διδακτικού έτους</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -3538,7 +3578,7 @@
       <c r="F65" s="21"/>
       <c r="G65" s="21"/>
       <c r="H65" s="22" t="str">
-        <f t="shared" ref="H65:H128" si="2">IF($A65="","",CHOOSE(WEEKDAY($A65,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I65" s="23" t="str">
@@ -3546,7 +3586,7 @@
         <v/>
       </c>
       <c r="J65" s="23" t="str">
-        <f t="shared" ref="J65:J128" si="3">IF($A65="","",IF($B65="","",$B65&amp;"  ")&amp;$C65&amp;IF($E65="","","  ("&amp;$E65&amp;")"))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3559,7 +3599,7 @@
       <c r="F66" s="21"/>
       <c r="G66" s="21"/>
       <c r="H66" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I66" s="23" t="str">
@@ -3567,7 +3607,7 @@
         <v/>
       </c>
       <c r="J66" s="23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3580,7 +3620,7 @@
       <c r="F67" s="21"/>
       <c r="G67" s="21"/>
       <c r="H67" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I67" s="23" t="str">
@@ -3588,7 +3628,7 @@
         <v/>
       </c>
       <c r="J67" s="23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3601,7 +3641,7 @@
       <c r="F68" s="21"/>
       <c r="G68" s="21"/>
       <c r="H68" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I68" s="23" t="str">
@@ -3609,7 +3649,7 @@
         <v/>
       </c>
       <c r="J68" s="23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -3622,7 +3662,7 @@
       <c r="F69" s="21"/>
       <c r="G69" s="21"/>
       <c r="H69" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H69:H132" si="2">IF($A69="","",CHOOSE(WEEKDAY($A69,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I69" s="23" t="str">
@@ -3630,7 +3670,7 @@
         <v/>
       </c>
       <c r="J69" s="23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J69:J132" si="3">IF($A69="","",IF($B69="","",$B69&amp;"  ")&amp;$C69&amp;IF($E69="","","  ("&amp;$E69&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -4664,11 +4704,13 @@
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C119" s="44"/>
-      <c r="D119" s="44"/>
-      <c r="E119" s="44"/>
-      <c r="F119" s="44"/>
-      <c r="G119" s="44"/>
+      <c r="A119" s="19"/>
+      <c r="B119" s="20"/>
+      <c r="C119" s="21"/>
+      <c r="D119" s="21"/>
+      <c r="E119" s="21"/>
+      <c r="F119" s="21"/>
+      <c r="G119" s="21"/>
       <c r="H119" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4683,11 +4725,13 @@
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C120" s="44"/>
-      <c r="D120" s="44"/>
-      <c r="E120" s="44"/>
-      <c r="F120" s="44"/>
-      <c r="G120" s="44"/>
+      <c r="A120" s="19"/>
+      <c r="B120" s="20"/>
+      <c r="C120" s="21"/>
+      <c r="D120" s="21"/>
+      <c r="E120" s="21"/>
+      <c r="F120" s="21"/>
+      <c r="G120" s="21"/>
       <c r="H120" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4702,11 +4746,13 @@
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C121" s="44"/>
-      <c r="D121" s="44"/>
-      <c r="E121" s="44"/>
-      <c r="F121" s="44"/>
-      <c r="G121" s="44"/>
+      <c r="A121" s="19"/>
+      <c r="B121" s="20"/>
+      <c r="C121" s="21"/>
+      <c r="D121" s="21"/>
+      <c r="E121" s="21"/>
+      <c r="F121" s="21"/>
+      <c r="G121" s="21"/>
       <c r="H121" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4721,11 +4767,13 @@
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C122" s="44"/>
-      <c r="D122" s="44"/>
-      <c r="E122" s="44"/>
-      <c r="F122" s="44"/>
-      <c r="G122" s="44"/>
+      <c r="A122" s="19"/>
+      <c r="B122" s="20"/>
+      <c r="C122" s="21"/>
+      <c r="D122" s="21"/>
+      <c r="E122" s="21"/>
+      <c r="F122" s="21"/>
+      <c r="G122" s="21"/>
       <c r="H122" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4860,7 +4908,7 @@
       <c r="F129" s="44"/>
       <c r="G129" s="44"/>
       <c r="H129" s="22" t="str">
-        <f t="shared" ref="H129:H192" si="4">IF($A129="","",CHOOSE(WEEKDAY($A129,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I129" s="23" t="str">
@@ -4868,7 +4916,7 @@
         <v/>
       </c>
       <c r="J129" s="23" t="str">
-        <f t="shared" ref="J129:J192" si="5">IF($A129="","",IF($B129="","",$B129&amp;"  ")&amp;$C129&amp;IF($E129="","","  ("&amp;$E129&amp;")"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4879,7 +4927,7 @@
       <c r="F130" s="44"/>
       <c r="G130" s="44"/>
       <c r="H130" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I130" s="23" t="str">
@@ -4887,7 +4935,7 @@
         <v/>
       </c>
       <c r="J130" s="23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4898,7 +4946,7 @@
       <c r="F131" s="44"/>
       <c r="G131" s="44"/>
       <c r="H131" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I131" s="23" t="str">
@@ -4906,7 +4954,7 @@
         <v/>
       </c>
       <c r="J131" s="23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4917,7 +4965,7 @@
       <c r="F132" s="44"/>
       <c r="G132" s="44"/>
       <c r="H132" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I132" s="23" t="str">
@@ -4925,7 +4973,7 @@
         <v/>
       </c>
       <c r="J132" s="23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4936,7 +4984,7 @@
       <c r="F133" s="44"/>
       <c r="G133" s="44"/>
       <c r="H133" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="H133:H196" si="4">IF($A133="","",CHOOSE(WEEKDAY($A133,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I133" s="23" t="str">
@@ -4944,7 +4992,7 @@
         <v/>
       </c>
       <c r="J133" s="23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J133:J196" si="5">IF($A133="","",IF($B133="","",$B133&amp;"  ")&amp;$C133&amp;IF($E133="","","  ("&amp;$E133&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -6076,7 +6124,7 @@
       <c r="F193" s="44"/>
       <c r="G193" s="44"/>
       <c r="H193" s="22" t="str">
-        <f t="shared" ref="H193:H256" si="6">IF($A193="","",CHOOSE(WEEKDAY($A193,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I193" s="23" t="str">
@@ -6084,7 +6132,7 @@
         <v/>
       </c>
       <c r="J193" s="23" t="str">
-        <f t="shared" ref="J193:J256" si="7">IF($A193="","",IF($B193="","",$B193&amp;"  ")&amp;$C193&amp;IF($E193="","","  ("&amp;$E193&amp;")"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6095,7 +6143,7 @@
       <c r="F194" s="44"/>
       <c r="G194" s="44"/>
       <c r="H194" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I194" s="23" t="str">
@@ -6103,7 +6151,7 @@
         <v/>
       </c>
       <c r="J194" s="23" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6114,7 +6162,7 @@
       <c r="F195" s="44"/>
       <c r="G195" s="44"/>
       <c r="H195" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I195" s="23" t="str">
@@ -6122,7 +6170,7 @@
         <v/>
       </c>
       <c r="J195" s="23" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6133,7 +6181,7 @@
       <c r="F196" s="44"/>
       <c r="G196" s="44"/>
       <c r="H196" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I196" s="23" t="str">
@@ -6141,7 +6189,7 @@
         <v/>
       </c>
       <c r="J196" s="23" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6152,7 +6200,7 @@
       <c r="F197" s="44"/>
       <c r="G197" s="44"/>
       <c r="H197" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="H197:H260" si="6">IF($A197="","",CHOOSE(WEEKDAY($A197,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I197" s="23" t="str">
@@ -6160,7 +6208,7 @@
         <v/>
       </c>
       <c r="J197" s="23" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J197:J260" si="7">IF($A197="","",IF($B197="","",$B197&amp;"  ")&amp;$C197&amp;IF($E197="","","  ("&amp;$E197&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -7292,7 +7340,7 @@
       <c r="F257" s="44"/>
       <c r="G257" s="44"/>
       <c r="H257" s="22" t="str">
-        <f t="shared" ref="H257:H320" si="8">IF($A257="","",CHOOSE(WEEKDAY($A257,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I257" s="23" t="str">
@@ -7300,7 +7348,7 @@
         <v/>
       </c>
       <c r="J257" s="23" t="str">
-        <f t="shared" ref="J257:J320" si="9">IF($A257="","",IF($B257="","",$B257&amp;"  ")&amp;$C257&amp;IF($E257="","","  ("&amp;$E257&amp;")"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7311,7 +7359,7 @@
       <c r="F258" s="44"/>
       <c r="G258" s="44"/>
       <c r="H258" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I258" s="23" t="str">
@@ -7319,7 +7367,7 @@
         <v/>
       </c>
       <c r="J258" s="23" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7330,7 +7378,7 @@
       <c r="F259" s="44"/>
       <c r="G259" s="44"/>
       <c r="H259" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I259" s="23" t="str">
@@ -7338,7 +7386,7 @@
         <v/>
       </c>
       <c r="J259" s="23" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7349,7 +7397,7 @@
       <c r="F260" s="44"/>
       <c r="G260" s="44"/>
       <c r="H260" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I260" s="23" t="str">
@@ -7357,7 +7405,7 @@
         <v/>
       </c>
       <c r="J260" s="23" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7368,7 +7416,7 @@
       <c r="F261" s="44"/>
       <c r="G261" s="44"/>
       <c r="H261" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="H261:H324" si="8">IF($A261="","",CHOOSE(WEEKDAY($A261,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I261" s="23" t="str">
@@ -7376,7 +7424,7 @@
         <v/>
       </c>
       <c r="J261" s="23" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J261:J324" si="9">IF($A261="","",IF($B261="","",$B261&amp;"  ")&amp;$C261&amp;IF($E261="","","  ("&amp;$E261&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -8508,7 +8556,7 @@
       <c r="F321" s="44"/>
       <c r="G321" s="44"/>
       <c r="H321" s="22" t="str">
-        <f t="shared" ref="H321:H384" si="10">IF($A321="","",CHOOSE(WEEKDAY($A321,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I321" s="23" t="str">
@@ -8516,7 +8564,7 @@
         <v/>
       </c>
       <c r="J321" s="23" t="str">
-        <f t="shared" ref="J321:J384" si="11">IF($A321="","",IF($B321="","",$B321&amp;"  ")&amp;$C321&amp;IF($E321="","","  ("&amp;$E321&amp;")"))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -8527,7 +8575,7 @@
       <c r="F322" s="44"/>
       <c r="G322" s="44"/>
       <c r="H322" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I322" s="23" t="str">
@@ -8535,7 +8583,7 @@
         <v/>
       </c>
       <c r="J322" s="23" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -8546,7 +8594,7 @@
       <c r="F323" s="44"/>
       <c r="G323" s="44"/>
       <c r="H323" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I323" s="23" t="str">
@@ -8554,7 +8602,7 @@
         <v/>
       </c>
       <c r="J323" s="23" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -8565,7 +8613,7 @@
       <c r="F324" s="44"/>
       <c r="G324" s="44"/>
       <c r="H324" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I324" s="23" t="str">
@@ -8573,7 +8621,7 @@
         <v/>
       </c>
       <c r="J324" s="23" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -8584,7 +8632,7 @@
       <c r="F325" s="44"/>
       <c r="G325" s="44"/>
       <c r="H325" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="H325:H388" si="10">IF($A325="","",CHOOSE(WEEKDAY($A325,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I325" s="23" t="str">
@@ -8592,7 +8640,7 @@
         <v/>
       </c>
       <c r="J325" s="23" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J325:J388" si="11">IF($A325="","",IF($B325="","",$B325&amp;"  ")&amp;$C325&amp;IF($E325="","","  ("&amp;$E325&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -9724,7 +9772,7 @@
       <c r="F385" s="44"/>
       <c r="G385" s="44"/>
       <c r="H385" s="22" t="str">
-        <f t="shared" ref="H385:H398" si="12">IF($A385="","",CHOOSE(WEEKDAY($A385,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="I385" s="23" t="str">
@@ -9732,7 +9780,7 @@
         <v/>
       </c>
       <c r="J385" s="23" t="str">
-        <f t="shared" ref="J385:J398" si="13">IF($A385="","",IF($B385="","",$B385&amp;"  ")&amp;$C385&amp;IF($E385="","","  ("&amp;$E385&amp;")"))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9743,7 +9791,7 @@
       <c r="F386" s="44"/>
       <c r="G386" s="44"/>
       <c r="H386" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="I386" s="23" t="str">
@@ -9751,7 +9799,7 @@
         <v/>
       </c>
       <c r="J386" s="23" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9762,7 +9810,7 @@
       <c r="F387" s="44"/>
       <c r="G387" s="44"/>
       <c r="H387" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="I387" s="23" t="str">
@@ -9770,7 +9818,7 @@
         <v/>
       </c>
       <c r="J387" s="23" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9781,7 +9829,7 @@
       <c r="F388" s="44"/>
       <c r="G388" s="44"/>
       <c r="H388" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="I388" s="23" t="str">
@@ -9789,7 +9837,7 @@
         <v/>
       </c>
       <c r="J388" s="23" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9800,7 +9848,7 @@
       <c r="F389" s="44"/>
       <c r="G389" s="44"/>
       <c r="H389" s="22" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="H389:H402" si="12">IF($A389="","",CHOOSE(WEEKDAY($A389,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I389" s="23" t="str">
@@ -9808,7 +9856,7 @@
         <v/>
       </c>
       <c r="J389" s="23" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J389:J402" si="13">IF($A389="","",IF($B389="","",$B389&amp;"  ")&amp;$C389&amp;IF($E389="","","  ("&amp;$E389&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -9983,51 +10031,137 @@
         <v/>
       </c>
     </row>
+    <row r="399" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C399" s="44"/>
+      <c r="D399" s="44"/>
+      <c r="E399" s="44"/>
+      <c r="F399" s="44"/>
+      <c r="G399" s="44"/>
+      <c r="H399" s="22" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I399" s="23" t="str">
+        <f>IF($A399="","",$A399&amp;"#"&amp;COUNTIF($A$2:$A399,$A399))</f>
+        <v/>
+      </c>
+      <c r="J399" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="400" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C400" s="44"/>
+      <c r="D400" s="44"/>
+      <c r="E400" s="44"/>
+      <c r="F400" s="44"/>
+      <c r="G400" s="44"/>
+      <c r="H400" s="22" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I400" s="23" t="str">
+        <f>IF($A400="","",$A400&amp;"#"&amp;COUNTIF($A$2:$A400,$A400))</f>
+        <v/>
+      </c>
+      <c r="J400" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="401" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C401" s="44"/>
+      <c r="D401" s="44"/>
+      <c r="E401" s="44"/>
+      <c r="F401" s="44"/>
+      <c r="G401" s="44"/>
+      <c r="H401" s="22" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I401" s="23" t="str">
+        <f>IF($A401="","",$A401&amp;"#"&amp;COUNTIF($A$2:$A401,$A401))</f>
+        <v/>
+      </c>
+      <c r="J401" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="402" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C402" s="44"/>
+      <c r="D402" s="44"/>
+      <c r="E402" s="44"/>
+      <c r="F402" s="44"/>
+      <c r="G402" s="44"/>
+      <c r="H402" s="22" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="I402" s="23" t="str">
+        <f>IF($A402="","",$A402&amp;"#"&amp;COUNTIF($A$2:$A402,$A402))</f>
+        <v/>
+      </c>
+      <c r="J402" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J398" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J398">
-      <sortCondition ref="A1:A398"/>
+  <autoFilter ref="A1:J402" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J402">
+      <sortCondition ref="A1:A402"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="A2:G3 A5:G8 A10:G398">
-    <cfRule type="expression" dxfId="36" priority="10">
+  <conditionalFormatting sqref="A2:G3 A5:G8 A10:G33 A42:G402 A35:G40">
+    <cfRule type="expression" dxfId="38" priority="10">
       <formula>AND($A2="",$A1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:G398">
-    <cfRule type="expression" dxfId="35" priority="2">
+  <conditionalFormatting sqref="A2:G402">
+    <cfRule type="expression" dxfId="37" priority="2">
       <formula>$D2="Αργία / Διακοπές"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="3">
+    <cfRule type="expression" dxfId="36" priority="3">
       <formula>$D2="Εορτή / Εκκλησιασμός"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="4">
+    <cfRule type="expression" dxfId="35" priority="4">
       <formula>$D2="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="5">
+    <cfRule type="expression" dxfId="34" priority="5">
       <formula>$D2="Σύλλογος διδασκόντων"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="6">
+    <cfRule type="expression" dxfId="33" priority="6">
       <formula>$D2="Ενημέρωση γονέων / Έλεγχοι"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="7">
+    <cfRule type="expression" dxfId="32" priority="7">
       <formula>$D2="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="8">
+    <cfRule type="expression" dxfId="31" priority="8">
       <formula>$D2="Δράση"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="9">
+    <cfRule type="expression" dxfId="30" priority="9">
       <formula>$D2="Δράση / Πρόγραμμα / Όμιλος"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:G9">
-    <cfRule type="expression" dxfId="27" priority="20">
+    <cfRule type="expression" dxfId="29" priority="20">
       <formula>AND($A9="",#REF!&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A34:G34">
+    <cfRule type="expression" dxfId="28" priority="22">
+      <formula>AND($A34="",$A31&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A41:G41">
+    <cfRule type="expression" dxfId="27" priority="24">
+      <formula>AND($A41="",$A38&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Τίτλος δράσης" prompt="Σύντομος τίτλος. Ώρες στη στήλη Β, τμήματα στη στήλη Ε." sqref="C2:C398" xr:uid="{0CD0AE7B-36D6-492A-8412-0F46B1D4BF63}"/>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Μη έγκυρη ημερομηνία" error="Γράψε πραγματική ημερομηνία στη μορφή 16/10/2026." promptTitle="Ημερομηνία" prompt="Γράψε την ημερομηνία, π.χ. 16/10/2026. Νέα δράση = πρώτη κενή (κίτρινη) γραμμή στο τέλος." sqref="A2:A398" xr:uid="{04C73EC8-C88D-4F69-A9AB-F63578E3CB50}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Τίτλος δράσης" prompt="Σύντομος τίτλος. Ώρες στη στήλη Β, τμήματα στη στήλη Ε." sqref="C2:C402" xr:uid="{0CD0AE7B-36D6-492A-8412-0F46B1D4BF63}"/>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Μη έγκυρη ημερομηνία" error="Γράψε πραγματική ημερομηνία στη μορφή 16/10/2026." promptTitle="Ημερομηνία" prompt="Γράψε την ημερομηνία, π.χ. 16/10/2026. Νέα δράση = πρώτη κενή (κίτρινη) γραμμή στο τέλος." sqref="A2:A402" xr:uid="{04C73EC8-C88D-4F69-A9AB-F63578E3CB50}">
       <formula1>OR($A2="",AND(ISNUMBER($A2),$A2&gt;36526))</formula1>
     </dataValidation>
   </dataValidations>
@@ -10043,7 +10177,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D398</xm:sqref>
+          <xm:sqref>D2:D402</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10083,16 +10217,16 @@
       <c r="H1" s="60"/>
       <c r="I1" s="60"/>
       <c r="K1" s="36" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" t="s">
         <v>64</v>
-      </c>
-      <c r="O1" t="s">
-        <v>65</v>
-      </c>
-      <c r="P1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -10111,13 +10245,13 @@
       <c r="H2" s="61"/>
       <c r="I2" s="61"/>
       <c r="K2" s="34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L2" s="38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O2">
         <v>9</v>
@@ -10128,37 +10262,37 @@
     </row>
     <row r="3" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K3" s="35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O3">
         <v>10</v>
@@ -10177,11 +10311,11 @@
         <v>46296</v>
       </c>
       <c r="C4" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="28" t="str">
-        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F4" s="25" t="str">
@@ -10193,16 +10327,16 @@
         <v>46327</v>
       </c>
       <c r="H4" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I4" s="28" t="str">
-        <f>IF($G4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="K4" s="34"/>
       <c r="N4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O4">
         <v>11</v>
@@ -10221,11 +10355,11 @@
         <v>46297</v>
       </c>
       <c r="C5" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="28" t="str">
-        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F5" s="25" t="str">
@@ -10237,22 +10371,22 @@
         <v>46328</v>
       </c>
       <c r="H5" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I5" s="28" t="str">
-        <f>IF($G5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="K5" s="34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L5">
         <f>INDEX($O$2:$O$11,MATCH($L$2,$N$2:$N$11,0))</f>
         <v>10</v>
       </c>
       <c r="N5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O5">
         <v>12</v>
@@ -10271,11 +10405,11 @@
         <v>46298</v>
       </c>
       <c r="C6" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="28" t="str">
-        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F6" s="25" t="str">
@@ -10287,22 +10421,22 @@
         <v>46329</v>
       </c>
       <c r="H6" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I6" s="28" t="str">
-        <f>IF($G6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="K6" s="34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L6">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($P$2:$P$11,MATCH($L$2,$N$2:$N$11,0))</f>
         <v>2026</v>
       </c>
       <c r="N6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -10311,7 +10445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Κυρ</v>
@@ -10321,11 +10455,11 @@
         <v>46299</v>
       </c>
       <c r="C7" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="28" t="str">
-        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F7" s="25" t="str">
@@ -10337,22 +10471,22 @@
         <v>46330</v>
       </c>
       <c r="H7" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v>Δράση</v>
       </c>
       <c r="I7" s="28" t="str">
-        <f>IF($G7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</v>
       </c>
       <c r="K7" s="34" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L7">
         <f>INDEX($O$2:$O$11,MATCH($L$3,$N$2:$N$11,0))</f>
         <v>11</v>
       </c>
       <c r="N7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O7">
         <v>2</v>
@@ -10371,11 +10505,11 @@
         <v>46300</v>
       </c>
       <c r="C8" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="28" t="str">
-        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F8" s="25" t="str">
@@ -10387,22 +10521,22 @@
         <v>46331</v>
       </c>
       <c r="H8" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I8" s="28" t="str">
-        <f>IF($G8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="K8" s="34" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="L8">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($P$2:$P$11,MATCH($L$3,$N$2:$N$11,0))</f>
         <v>2026</v>
       </c>
       <c r="N8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O8">
         <v>3</v>
@@ -10421,11 +10555,11 @@
         <v>46301</v>
       </c>
       <c r="C9" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="28" t="str">
-        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F9" s="25" t="str">
@@ -10437,15 +10571,15 @@
         <v>46332</v>
       </c>
       <c r="H9" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I9" s="28" t="str">
-        <f>IF($G9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="N9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O9">
         <v>4</v>
@@ -10464,11 +10598,11 @@
         <v>46302</v>
       </c>
       <c r="C10" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="28" t="str">
-        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F10" s="25" t="str">
@@ -10480,15 +10614,15 @@
         <v>46333</v>
       </c>
       <c r="H10" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I10" s="28" t="str">
-        <f>IF($G10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="N10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -10507,11 +10641,11 @@
         <v>46303</v>
       </c>
       <c r="C11" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="28" t="str">
-        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F11" s="25" t="str">
@@ -10523,15 +10657,15 @@
         <v>46334</v>
       </c>
       <c r="H11" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I11" s="28" t="str">
-        <f>IF($G11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="N11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -10550,11 +10684,11 @@
         <v>46304</v>
       </c>
       <c r="C12" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="28" t="str">
-        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F12" s="25" t="str">
@@ -10566,11 +10700,11 @@
         <v>46335</v>
       </c>
       <c r="H12" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I12" s="28" t="str">
-        <f>IF($G12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10584,11 +10718,11 @@
         <v>46305</v>
       </c>
       <c r="C13" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="28" t="str">
-        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F13" s="25" t="str">
@@ -10600,11 +10734,11 @@
         <v>46336</v>
       </c>
       <c r="H13" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I13" s="28" t="str">
-        <f>IF($G13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10618,11 +10752,11 @@
         <v>46306</v>
       </c>
       <c r="C14" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="28" t="str">
-        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F14" s="25" t="str">
@@ -10634,11 +10768,11 @@
         <v>46337</v>
       </c>
       <c r="H14" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I14" s="28" t="str">
-        <f>IF($G14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10652,11 +10786,11 @@
         <v>46307</v>
       </c>
       <c r="C15" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="28" t="str">
-        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F15" s="25" t="str">
@@ -10668,11 +10802,11 @@
         <v>46338</v>
       </c>
       <c r="H15" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I15" s="28" t="str">
-        <f>IF($G15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10686,11 +10820,11 @@
         <v>46308</v>
       </c>
       <c r="C16" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="28" t="str">
-        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F16" s="25" t="str">
@@ -10702,11 +10836,11 @@
         <v>46339</v>
       </c>
       <c r="H16" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I16" s="28" t="str">
-        <f>IF($G16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10720,11 +10854,11 @@
         <v>46309</v>
       </c>
       <c r="C17" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="28" t="str">
-        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F17" s="25" t="str">
@@ -10736,11 +10870,11 @@
         <v>46340</v>
       </c>
       <c r="H17" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I17" s="28" t="str">
-        <f>IF($G17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10754,11 +10888,11 @@
         <v>46310</v>
       </c>
       <c r="C18" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="28" t="str">
-        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F18" s="25" t="str">
@@ -10770,11 +10904,11 @@
         <v>46341</v>
       </c>
       <c r="H18" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I18" s="28" t="str">
-        <f>IF($G18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10788,11 +10922,11 @@
         <v>46311</v>
       </c>
       <c r="C19" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="28" t="str">
-        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F19" s="25" t="str">
@@ -10804,11 +10938,11 @@
         <v>46342</v>
       </c>
       <c r="H19" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I19" s="28" t="str">
-        <f>IF($G19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10822,11 +10956,11 @@
         <v>46312</v>
       </c>
       <c r="C20" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="28" t="str">
-        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F20" s="25" t="str">
@@ -10838,11 +10972,11 @@
         <v>46343</v>
       </c>
       <c r="H20" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v>Εορτή / Εκκλησιασμός</v>
       </c>
       <c r="I20" s="28" t="str">
-        <f>IF($G20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</v>
       </c>
     </row>
@@ -10856,11 +10990,11 @@
         <v>46313</v>
       </c>
       <c r="C21" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="28" t="str">
-        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F21" s="25" t="str">
@@ -10872,11 +11006,11 @@
         <v>46344</v>
       </c>
       <c r="H21" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I21" s="28" t="str">
-        <f>IF($G21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10890,11 +11024,11 @@
         <v>46314</v>
       </c>
       <c r="C22" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="28" t="str">
-        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F22" s="25" t="str">
@@ -10906,11 +11040,11 @@
         <v>46345</v>
       </c>
       <c r="H22" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I22" s="28" t="str">
-        <f>IF($G22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10924,11 +11058,11 @@
         <v>46315</v>
       </c>
       <c r="C23" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F23" s="25" t="str">
@@ -10940,11 +11074,11 @@
         <v>46346</v>
       </c>
       <c r="H23" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I23" s="28" t="str">
-        <f>IF($G23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10958,11 +11092,11 @@
         <v>46316</v>
       </c>
       <c r="C24" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="28" t="str">
-        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F24" s="25" t="str">
@@ -10974,11 +11108,11 @@
         <v>46347</v>
       </c>
       <c r="H24" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I24" s="28" t="str">
-        <f>IF($G24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10992,11 +11126,11 @@
         <v>46317</v>
       </c>
       <c r="C25" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="28" t="str">
-        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F25" s="25" t="str">
@@ -11008,11 +11142,11 @@
         <v>46348</v>
       </c>
       <c r="H25" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I25" s="28" t="str">
-        <f>IF($G25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11026,11 +11160,11 @@
         <v>46318</v>
       </c>
       <c r="C26" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="28" t="str">
-        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F26" s="25" t="str">
@@ -11042,11 +11176,11 @@
         <v>46349</v>
       </c>
       <c r="H26" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I26" s="28" t="str">
-        <f>IF($G26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11060,11 +11194,11 @@
         <v>46319</v>
       </c>
       <c r="C27" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="28" t="str">
-        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F27" s="25" t="str">
@@ -11076,11 +11210,11 @@
         <v>46350</v>
       </c>
       <c r="H27" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I27" s="28" t="str">
-        <f>IF($G27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11094,11 +11228,11 @@
         <v>46320</v>
       </c>
       <c r="C28" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F28" s="25" t="str">
@@ -11110,11 +11244,11 @@
         <v>46351</v>
       </c>
       <c r="H28" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I28" s="28" t="str">
-        <f>IF($G28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11128,11 +11262,11 @@
         <v>46321</v>
       </c>
       <c r="C29" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v>Αργία / Διακοπές</v>
       </c>
       <c r="D29" s="28" t="str">
-        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v>Αγίου Δημητρίου</v>
       </c>
       <c r="F29" s="25" t="str">
@@ -11144,11 +11278,11 @@
         <v>46352</v>
       </c>
       <c r="H29" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I29" s="28" t="str">
-        <f>IF($G29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11162,11 +11296,11 @@
         <v>46322</v>
       </c>
       <c r="C30" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v>Εορτή / Εκκλησιασμός</v>
       </c>
       <c r="D30" s="28" t="str">
-        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου</v>
       </c>
       <c r="F30" s="25" t="str">
@@ -11178,11 +11312,11 @@
         <v>46353</v>
       </c>
       <c r="H30" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I30" s="28" t="str">
-        <f>IF($G30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11196,11 +11330,11 @@
         <v>46323</v>
       </c>
       <c r="C31" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v>Αργία / Διακοπές</v>
       </c>
       <c r="D31" s="28" t="str">
-        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v>Εθνική επέτειος 28ης Οκτωβρίου – Αργία</v>
       </c>
       <c r="F31" s="25" t="str">
@@ -11212,11 +11346,11 @@
         <v>46354</v>
       </c>
       <c r="H31" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I31" s="28" t="str">
-        <f>IF($G31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11230,11 +11364,11 @@
         <v>46324</v>
       </c>
       <c r="C32" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="28" t="str">
-        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F32" s="25" t="str">
@@ -11246,11 +11380,11 @@
         <v>46355</v>
       </c>
       <c r="H32" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I32" s="28" t="str">
-        <f>IF($G32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11264,11 +11398,11 @@
         <v>46325</v>
       </c>
       <c r="C33" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="28" t="str">
-        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F33" s="25" t="str">
@@ -11280,11 +11414,11 @@
         <v>46356</v>
       </c>
       <c r="H33" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I33" s="28" t="str">
-        <f>IF($G33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11298,11 +11432,11 @@
         <v>46326</v>
       </c>
       <c r="C34" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="28" t="str">
-        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F34" s="25" t="str">
@@ -11314,29 +11448,29 @@
         <v/>
       </c>
       <c r="H34" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="I34" s="28" t="str">
-        <f>IF($G34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($G34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($G34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
       <c r="B37" s="59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="59"/>
       <c r="F37" s="12"/>
       <c r="G37" s="59" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H37" s="59"/>
       <c r="I37" s="59"/>
@@ -11344,13 +11478,13 @@
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="59"/>
       <c r="F38" s="13"/>
       <c r="G38" s="59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H38" s="59"/>
       <c r="I38" s="59"/>
@@ -11358,13 +11492,13 @@
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
       <c r="B39" s="59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" s="59"/>
       <c r="D39" s="59"/>
       <c r="F39" s="14"/>
       <c r="G39" s="59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H39" s="59"/>
       <c r="I39" s="59"/>
@@ -11372,13 +11506,13 @@
     <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
       <c r="B40" s="59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C40" s="59"/>
       <c r="D40" s="59"/>
       <c r="F40" s="15"/>
       <c r="G40" s="59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H40" s="59"/>
       <c r="I40" s="59"/>
@@ -11491,17 +11625,17 @@
       <c r="C1" s="60"/>
       <c r="D1" s="60"/>
       <c r="F1" s="36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G1" s="34"/>
       <c r="I1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" t="s">
         <v>64</v>
-      </c>
-      <c r="J1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -11513,13 +11647,13 @@
       <c r="C2" s="61"/>
       <c r="D2" s="61"/>
       <c r="F2" s="34" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J2">
         <v>9</v>
@@ -11530,21 +11664,21 @@
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F3" s="34"/>
       <c r="G3" s="34"/>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J3">
         <v>10</v>
@@ -11563,17 +11697,17 @@
         <v>46327</v>
       </c>
       <c r="C4" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="28" t="str">
-        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F4" s="34"/>
       <c r="G4" s="34"/>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J4">
         <v>11</v>
@@ -11592,22 +11726,22 @@
         <v>46328</v>
       </c>
       <c r="C5" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="28" t="str">
-        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F5" s="34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G5" s="34">
         <f>INDEX($J$2:$J$11,MATCH($G$2,$I$2:$I$11,0))</f>
         <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -11626,22 +11760,22 @@
         <v>46329</v>
       </c>
       <c r="C6" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="28" t="str">
-        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F6" s="34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G6" s="34">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($K$2:$K$11,MATCH($G$2,$I$2:$I$11,0))</f>
         <v>2026</v>
       </c>
       <c r="I6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -11650,7 +11784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Τετ</v>
@@ -11660,17 +11794,17 @@
         <v>46330</v>
       </c>
       <c r="C7" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v>Δράση</v>
       </c>
       <c r="D7" s="28" t="str">
-        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34"/>
       <c r="I7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -11689,17 +11823,17 @@
         <v>46331</v>
       </c>
       <c r="C8" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="28" t="str">
-        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
       <c r="I8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J8">
         <v>3</v>
@@ -11718,15 +11852,15 @@
         <v>46332</v>
       </c>
       <c r="C9" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="28" t="str">
-        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="I9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -11745,15 +11879,15 @@
         <v>46333</v>
       </c>
       <c r="C10" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="28" t="str">
-        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="I10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -11772,15 +11906,15 @@
         <v>46334</v>
       </c>
       <c r="C11" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="28" t="str">
-        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
       <c r="I11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -11799,11 +11933,11 @@
         <v>46335</v>
       </c>
       <c r="C12" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="28" t="str">
-        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11817,11 +11951,11 @@
         <v>46336</v>
       </c>
       <c r="C13" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="28" t="str">
-        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11835,11 +11969,11 @@
         <v>46337</v>
       </c>
       <c r="C14" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="28" t="str">
-        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11853,11 +11987,11 @@
         <v>46338</v>
       </c>
       <c r="C15" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="28" t="str">
-        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11871,11 +12005,11 @@
         <v>46339</v>
       </c>
       <c r="C16" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="28" t="str">
-        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11889,11 +12023,11 @@
         <v>46340</v>
       </c>
       <c r="C17" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="28" t="str">
-        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11907,11 +12041,11 @@
         <v>46341</v>
       </c>
       <c r="C18" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="28" t="str">
-        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11925,11 +12059,11 @@
         <v>46342</v>
       </c>
       <c r="C19" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="28" t="str">
-        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11943,11 +12077,11 @@
         <v>46343</v>
       </c>
       <c r="C20" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v>Εορτή / Εκκλησιασμός</v>
       </c>
       <c r="D20" s="28" t="str">
-        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</v>
       </c>
     </row>
@@ -11961,11 +12095,11 @@
         <v>46344</v>
       </c>
       <c r="C21" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="28" t="str">
-        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11979,11 +12113,11 @@
         <v>46345</v>
       </c>
       <c r="C22" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="28" t="str">
-        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11997,11 +12131,11 @@
         <v>46346</v>
       </c>
       <c r="C23" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12015,11 +12149,11 @@
         <v>46347</v>
       </c>
       <c r="C24" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="28" t="str">
-        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12033,11 +12167,11 @@
         <v>46348</v>
       </c>
       <c r="C25" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="28" t="str">
-        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12051,11 +12185,11 @@
         <v>46349</v>
       </c>
       <c r="C26" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="28" t="str">
-        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12069,11 +12203,11 @@
         <v>46350</v>
       </c>
       <c r="C27" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="28" t="str">
-        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12087,11 +12221,11 @@
         <v>46351</v>
       </c>
       <c r="C28" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12105,11 +12239,11 @@
         <v>46352</v>
       </c>
       <c r="C29" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="28" t="str">
-        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12123,11 +12257,11 @@
         <v>46353</v>
       </c>
       <c r="C30" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="28" t="str">
-        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12141,11 +12275,11 @@
         <v>46354</v>
       </c>
       <c r="C31" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="28" t="str">
-        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12159,11 +12293,11 @@
         <v>46355</v>
       </c>
       <c r="C32" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="28" t="str">
-        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12177,11 +12311,11 @@
         <v>46356</v>
       </c>
       <c r="C33" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="28" t="str">
-        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12195,47 +12329,47 @@
         <v/>
       </c>
       <c r="C34" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$398,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="28" t="str">
-        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$398,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$398,0)),""))</f>
+        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="32"/>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="30"/>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="42"/>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="43"/>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="40"/>
       <c r="B41" s="62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C41" s="63"/>
       <c r="D41" s="63"/>
@@ -12243,7 +12377,7 @@
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="31"/>
       <c r="B42" s="62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C42" s="63"/>
       <c r="D42" s="63"/>
@@ -12251,7 +12385,7 @@
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="33"/>
       <c r="B43" s="62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C43" s="63"/>
       <c r="D43" s="63"/>
@@ -12259,7 +12393,7 @@
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="41"/>
       <c r="B44" s="62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C44" s="62"/>
       <c r="D44" s="62"/>

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30515"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karel\Downloads\draseis\draseis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F16BF0-6EB1-4454-8AF7-D78160817342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20BEE76-92A1-480A-8166-EA025F69A7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ΟΔΗΓΙΕΣ" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,16 @@
     <sheet name="ΔΡΑΣΕΙΣ" sheetId="3" r:id="rId3"/>
     <sheet name="ΑΦΙΣΑ_ΕΠΙΛΟΓΗΣ" sheetId="19" r:id="rId4"/>
     <sheet name="ΑΦΙΣΑ_1ΜΗΝΑΣ" sheetId="20" r:id="rId5"/>
+    <sheet name="ΑΦΙΣΑ_1ΜΗΝΑΣ_λίστα" sheetId="21" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ΔΡΑΣΕΙΣ!$A$1:$J$402</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">ΑΦΙΣΑ_1ΜΗΝΑΣ!$A$1:$D$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ΔΡΑΣΕΙΣ!$A$1:$J$399</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">ΑΦΙΣΑ_1ΜΗΝΑΣ!$A$1:$G$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">ΑΦΙΣΑ_1ΜΗΝΑΣ_λίστα!$A$1:$D$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">ΑΦΙΣΑ_ΕΠΙΛΟΓΗΣ!$A$1:$I$40</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">ΔΡΑΣΕΙΣ!$A$1:$G$122</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">ΔΡΑΣΕΙΣ!$A$1:$G$119</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">ΑΦΙΣΑ_1ΜΗΝΑΣ!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">ΑΦΙΣΑ_1ΜΗΝΑΣ_λίστα!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">ΑΦΙΣΑ_ΕΠΙΛΟΓΗΣ!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">ΔΡΑΣΕΙΣ!$1:$1</definedName>
   </definedNames>
@@ -49,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="140">
   <si>
     <t>3ο ΓΥΜΝΑΣΙΟ ΠΟΛΙΧΝΗΣ  ·  ΗΜΕΡΟΛΟΓΙΟ ΔΡΑΣΕΩΝ  ·  ΣΧΟΛΙΚΟ ΕΤΟΣ 2026-27</t>
   </si>
@@ -117,6 +120,9 @@
     <t>ΠΡΟΣΩΡΙΝΕΣ ΗΜΕΡΟΜΗΝΙΕΣ</t>
   </si>
   <si>
+    <t>Λήξη Α΄ τετραμήνου, επιστροφή μετά το Πάσχα και λήξη μαθημάτων Γυμνασίου</t>
+  </si>
+  <si>
     <t>οριστικοποιούνται με εγκύκλιο του Υπουργείου. Είναι σημειωμένες ως εκτίμηση.</t>
   </si>
   <si>
@@ -141,7 +147,7 @@
     <t>Ορόσημο / Εξετάσεις</t>
   </si>
   <si>
-    <t>Δράση</t>
+    <t>Επιμόρφωση εκπαιδευτικών</t>
   </si>
   <si>
     <t>Δράση / Πρόγραμμα / Όμιλος</t>
@@ -183,13 +189,25 @@
     <t>ΕΜΦΑΝΙΣΗ</t>
   </si>
   <si>
+    <t>Αγιασμός – Έναρξη σχολικού έτους. Διαμοιρασμός σε τμήματα.</t>
+  </si>
+  <si>
     <t>Έναρξη μαθημάτων</t>
+  </si>
+  <si>
+    <t>Αγίου Δημητρίου – Ελευθέρια Θεσσαλονίκης (τοπική αργία)</t>
+  </si>
+  <si>
+    <t>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου (χωρίς μάθημα)</t>
   </si>
   <si>
     <t>Εθνική επέτειος 28ης Οκτωβρίου – Αργία</t>
   </si>
   <si>
     <t>08:45-11:15</t>
+  </si>
+  <si>
+    <t>Διαδικτυακή εκπαίδευση «Kids Save Lives»</t>
   </si>
   <si>
     <t>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</t>
@@ -220,6 +238,9 @@
   </si>
   <si>
     <t>Διακοπές Πάσχα</t>
+  </si>
+  <si>
+    <t>Επαναλειτουργία σχολείου μετά το Πάσχα (εκτίμηση)</t>
   </si>
   <si>
     <t>Αγίου Πνεύματος – Αργία</t>
@@ -304,9 +325,6 @@
   </si>
   <si>
     <t>Μήνας:</t>
-  </si>
-  <si>
-    <t>ΑΦΙΣΑ_ΕΠΙΛΟΓΗΣ: δύο μήνες (L2, L3) → Α3 οριζόντια. ΑΦΙΣΑ_1ΜΗΝΑΣ: ένας μήνας (G2) → Α4 κατακόρυφα.</t>
   </si>
   <si>
     <t>4.</t>
@@ -414,33 +432,58 @@
     <t>Νέα δράση: γράψε την στην κίτρινη (πρώτη κενή) γραμμή στο τέλος – αναλυτικά βήμα–βήμα πιο κάτω.</t>
   </si>
   <si>
-    <t>Αγιασμός – Έναρξη σχολικού έτους</t>
+    <t>αρ. μήνα</t>
   </si>
   <si>
-    <t>Αγίου Δημητρίου</t>
+    <t>έτος</t>
   </si>
   <si>
-    <t>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου</t>
+    <t>1η μέρα πλέγματος</t>
   </si>
   <si>
-    <t>Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</t>
+    <t>ΔΕΥΤΕΡΑ</t>
   </si>
   <si>
-    <t>Επαναλειτουργία σχολείου μετά το Πάσχα</t>
+    <t>ΤΡΙΤΗ</t>
   </si>
   <si>
-    <t>Λήξη Α΄ τετραμήνου και λήξη μαθημάτων Γυμνασίου</t>
+    <t>ΤΕΤΑΡΤΗ</t>
+  </si>
+  <si>
+    <t>ΠΕΜΠΤΗ</t>
+  </si>
+  <si>
+    <t>ΠΑΡΑΣΚΕΥΗ</t>
+  </si>
+  <si>
+    <t>ΣΑΒΒΑΤΟ</t>
+  </si>
+  <si>
+    <t>ΚΥΡΙΑΚΗ</t>
+  </si>
+  <si>
+    <t>ΣΗΜΕΙΩΣΕΙΣ ΜΗΝΑ</t>
+  </si>
+  <si>
+    <t>ΑΦΙΣΑ_ΕΠΙΛΟΓΗΣ: δύο μήνες (L2, L3) → Α3 οριζόντια. ΑΦΙΣΑ_1ΜΗΝΑΣ: ημερολόγιο-πλέγμα ενός μήνα με χώρο για χειρόγραφες σημειώσεις (μήνας στο L2) → Α3 οριζόντια.</t>
+  </si>
+  <si>
+    <t>09:00-12.30</t>
+  </si>
+  <si>
+    <t>Μουσείο Μακεδονικού Αγώνα</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="dd/mm"/>
+    <numFmt numFmtId="166" formatCode="d"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -599,8 +642,57 @@
       <family val="2"/>
       <charset val="161"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="30">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -745,8 +837,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4E4E4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E5496"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F7F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -804,11 +926,191 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F3864"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F3864"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F3864"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F3864"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F3864"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F3864"/>
+      </right>
+      <top style="dotted">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F3864"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F3864"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF1F3864"/>
+      </top>
+      <bottom style="dotted">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF1F3864"/>
+      </top>
+      <bottom style="dotted">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF1F3864"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F3864"/>
+      </top>
+      <bottom style="dotted">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F3864"/>
+      </left>
+      <right/>
+      <top style="dotted">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF1F3864"/>
+      </right>
+      <top style="dotted">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -922,6 +1224,70 @@
     <xf numFmtId="0" fontId="24" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -935,19 +1301,101 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="45">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC4B5DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF9FD8CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFA9CDEB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF9C08A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFD0CECE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFB7DE9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFE08A"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF4B6B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -957,15 +1405,17 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FF9FD8CE"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC4B5DC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFC4B5DC"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF9FD8CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1020,15 +1470,17 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FF9FD8CE"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC4B5DC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFC4B5DC"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF9FD8CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1083,15 +1535,17 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FF9FD8CE"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFC4B5DC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFC4B5DC"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF9FD8CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1141,7 +1595,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFC4B5DC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1149,29 +1603,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF9FD8CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC4B5DC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1214,14 +1646,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF4B6B6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1485,7 +1909,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="2">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="3">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1515,10 +1939,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
+      <c r="B1" s="91"/>
     </row>
     <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -1529,10 +1953,10 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="58"/>
+      <c r="B4" s="92"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
@@ -1553,7 +1977,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
@@ -1566,10 +1990,10 @@
     </row>
     <row r="10" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="55" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -1578,48 +2002,48 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B12" s="48"/>
     </row>
     <row r="13" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="49" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="49" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="49" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A16" s="49" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A17" s="49" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -1628,72 +2052,72 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B19" s="48"/>
     </row>
     <row r="20" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" s="49" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A21" s="49" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" s="49" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A23" s="49" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A24" s="49" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A25" s="49" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A26" s="49" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A27" s="51" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1702,24 +2126,24 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="47" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B29" s="48"/>
     </row>
     <row r="30" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="49" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B30" s="50" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="53" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B31" s="54" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -1764,12 +2188,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1793,66 +2217,66 @@
         <v>21</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>126</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="7"/>
       <c r="B46" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
       <c r="B47" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="10"/>
       <c r="B48" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="11"/>
       <c r="B49" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="12"/>
       <c r="B50" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="14"/>
       <c r="B52" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="15"/>
       <c r="B53" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1876,63 +2300,63 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="7"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="9"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="10"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="12"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B7" s="13"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="14"/>
+        <v>31</v>
+      </c>
+      <c r="B8" s="100"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="15"/>
+        <v>32</v>
+      </c>
+      <c r="B9" s="101"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1946,7 +2370,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K402"/>
+  <dimension ref="A1:K399"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
@@ -1962,52 +2386,52 @@
   <sheetData>
     <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H1" s="45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1" s="45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="19">
         <v>46276</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="21" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="21"/>
       <c r="F2" s="21"/>
       <c r="G2" s="21"/>
       <c r="H2" s="22" t="str">
-        <f t="shared" ref="H2:H68" si="0">IF($A2="","",CHOOSE(WEEKDAY($A2,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" ref="H2:H65" si="0">IF($A2="","",CHOOSE(WEEKDAY($A2,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v>Παρ</v>
       </c>
       <c r="I2" s="23" t="str">
@@ -2015,8 +2439,8 @@
         <v>46276#1</v>
       </c>
       <c r="J2" s="23" t="str">
-        <f t="shared" ref="J2:J68" si="1">IF($A2="","",IF($B2="","",$B2&amp;"  ")&amp;$C2&amp;IF($E2="","","  ("&amp;$E2&amp;")"))</f>
-        <v>Αγιασμός – Έναρξη σχολικού έτους</v>
+        <f t="shared" ref="J2:J65" si="1">IF($A2="","",IF($B2="","",$B2&amp;"  ")&amp;$C2&amp;IF($E2="","","  ("&amp;$E2&amp;")"))</f>
+        <v>Αγιασμός – Έναρξη σχολικού έτους. Διαμοιρασμός σε τμήματα.</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -2025,10 +2449,10 @@
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3" s="21"/>
       <c r="F3" s="21"/>
@@ -2046,16 +2470,16 @@
         <v>Έναρξη μαθημάτων</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>46321</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="21" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4" s="21"/>
@@ -2070,19 +2494,19 @@
       </c>
       <c r="J4" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Αγίου Δημητρίου</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>Αγίου Δημητρίου – Ελευθέρια Θεσσαλονίκης (τοπική αργία)</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="19">
         <v>46322</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="21" t="s">
-        <v>123</v>
+        <v>48</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5" s="21"/>
@@ -2097,7 +2521,7 @@
       </c>
       <c r="J5" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου</v>
+        <v>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου (χωρίς μάθημα)</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2106,10 +2530,10 @@
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="21" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="21"/>
       <c r="F6" s="21"/>
@@ -2127,18 +2551,18 @@
         <v>Εθνική επέτειος 28ης Οκτωβρίου – Αργία</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="19">
         <v>46330</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="21"/>
@@ -2153,7 +2577,7 @@
       </c>
       <c r="J7" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</v>
+        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives»</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2162,10 +2586,10 @@
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="21" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
@@ -2185,79 +2609,81 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="19">
-        <v>46379</v>
-      </c>
-      <c r="B9" s="20"/>
+        <v>46356</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>138</v>
+      </c>
       <c r="C9" s="21" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E9" s="21"/>
       <c r="F9" s="21"/>
       <c r="G9" s="21"/>
       <c r="H9" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Δευ</v>
       </c>
       <c r="I9" s="23" t="str">
         <f>IF($A9="","",$A9&amp;"#"&amp;COUNTIF($A$2:$A9,$A9))</f>
-        <v>46379#1</v>
+        <v>46356#1</v>
       </c>
       <c r="J9" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Τελευταία ημέρα μαθημάτων πριν τις διακοπές</v>
+        <v>09:00-12.30  Μουσείο Μακεδονικού Αγώνα</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="19">
-        <v>46380</v>
+        <v>46379</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="21" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E10" s="21"/>
       <c r="F10" s="21"/>
       <c r="G10" s="21"/>
       <c r="H10" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Τετ</v>
       </c>
       <c r="I10" s="23" t="str">
         <f>IF($A10="","",$A10&amp;"#"&amp;COUNTIF($A$2:$A10,$A10))</f>
-        <v>46380#1</v>
+        <v>46379#1</v>
       </c>
       <c r="J10" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Διακοπές Χριστουγέννων</v>
+        <v>Τελευταία ημέρα μαθημάτων πριν τις διακοπές</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="19">
-        <v>46381</v>
+        <v>46380</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E11" s="21"/>
       <c r="F11" s="21"/>
       <c r="G11" s="21"/>
       <c r="H11" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I11" s="23" t="str">
         <f>IF($A11="","",$A11&amp;"#"&amp;COUNTIF($A$2:$A11,$A11))</f>
-        <v>46381#1</v>
+        <v>46380#1</v>
       </c>
       <c r="J11" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2266,25 +2692,25 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="19">
-        <v>46384</v>
+        <v>46381</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" s="21"/>
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
       <c r="H12" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Παρ</v>
       </c>
       <c r="I12" s="23" t="str">
         <f>IF($A12="","",$A12&amp;"#"&amp;COUNTIF($A$2:$A12,$A12))</f>
-        <v>46384#1</v>
+        <v>46381#1</v>
       </c>
       <c r="J12" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2293,25 +2719,25 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="19">
-        <v>46385</v>
+        <v>46384</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
       <c r="G13" s="21"/>
       <c r="H13" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Δευ</v>
       </c>
       <c r="I13" s="23" t="str">
         <f>IF($A13="","",$A13&amp;"#"&amp;COUNTIF($A$2:$A13,$A13))</f>
-        <v>46385#1</v>
+        <v>46384#1</v>
       </c>
       <c r="J13" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2320,25 +2746,25 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="19">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
       <c r="H14" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Τρί</v>
       </c>
       <c r="I14" s="23" t="str">
         <f>IF($A14="","",$A14&amp;"#"&amp;COUNTIF($A$2:$A14,$A14))</f>
-        <v>46386#1</v>
+        <v>46385#1</v>
       </c>
       <c r="J14" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2347,25 +2773,25 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="19">
-        <v>46387</v>
+        <v>46386</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
       <c r="G15" s="21"/>
       <c r="H15" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Τετ</v>
       </c>
       <c r="I15" s="23" t="str">
         <f>IF($A15="","",$A15&amp;"#"&amp;COUNTIF($A$2:$A15,$A15))</f>
-        <v>46387#1</v>
+        <v>46386#1</v>
       </c>
       <c r="J15" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2374,25 +2800,25 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="19">
-        <v>46388</v>
+        <v>46387</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16" s="21"/>
       <c r="G16" s="21"/>
       <c r="H16" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I16" s="23" t="str">
         <f>IF($A16="","",$A16&amp;"#"&amp;COUNTIF($A$2:$A16,$A16))</f>
-        <v>46388#1</v>
+        <v>46387#1</v>
       </c>
       <c r="J16" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2401,25 +2827,25 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="19">
-        <v>46391</v>
+        <v>46388</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="21"/>
       <c r="F17" s="21"/>
       <c r="G17" s="21"/>
       <c r="H17" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Παρ</v>
       </c>
       <c r="I17" s="23" t="str">
         <f>IF($A17="","",$A17&amp;"#"&amp;COUNTIF($A$2:$A17,$A17))</f>
-        <v>46391#1</v>
+        <v>46388#1</v>
       </c>
       <c r="J17" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2428,25 +2854,25 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="19">
-        <v>46392</v>
+        <v>46391</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
       <c r="G18" s="21"/>
       <c r="H18" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Δευ</v>
       </c>
       <c r="I18" s="23" t="str">
         <f>IF($A18="","",$A18&amp;"#"&amp;COUNTIF($A$2:$A18,$A18))</f>
-        <v>46392#1</v>
+        <v>46391#1</v>
       </c>
       <c r="J18" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2455,25 +2881,25 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="19">
-        <v>46393</v>
+        <v>46392</v>
       </c>
       <c r="B19" s="20"/>
       <c r="C19" s="21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
       <c r="G19" s="21"/>
       <c r="H19" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Τρί</v>
       </c>
       <c r="I19" s="23" t="str">
         <f>IF($A19="","",$A19&amp;"#"&amp;COUNTIF($A$2:$A19,$A19))</f>
-        <v>46393#1</v>
+        <v>46392#1</v>
       </c>
       <c r="J19" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2482,25 +2908,25 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="19">
-        <v>46394</v>
+        <v>46393</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="21" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" s="21"/>
       <c r="F20" s="21"/>
       <c r="G20" s="21"/>
       <c r="H20" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Τετ</v>
       </c>
       <c r="I20" s="23" t="str">
         <f>IF($A20="","",$A20&amp;"#"&amp;COUNTIF($A$2:$A20,$A20))</f>
-        <v>46394#1</v>
+        <v>46393#1</v>
       </c>
       <c r="J20" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2509,119 +2935,119 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="19">
-        <v>46395</v>
+        <v>46394</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="21" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E21" s="21"/>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
       <c r="H21" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I21" s="23" t="str">
         <f>IF($A21="","",$A21&amp;"#"&amp;COUNTIF($A$2:$A21,$A21))</f>
-        <v>46395#1</v>
+        <v>46394#1</v>
       </c>
       <c r="J21" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Επαναλειτουργία σχολείου</v>
+        <v>Διακοπές Χριστουγέννων</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="19">
-        <v>46407</v>
+        <v>46395</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="21" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="21"/>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
       <c r="H22" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Παρ</v>
       </c>
       <c r="I22" s="23" t="str">
         <f>IF($A22="","",$A22&amp;"#"&amp;COUNTIF($A$2:$A22,$A22))</f>
-        <v>46407#1</v>
+        <v>46395#1</v>
       </c>
       <c r="J22" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Λήξη Α΄ τετραμήνου (εκτίμηση – εκκρεμεί εγκύκλιος)</v>
+        <v>Επαναλειτουργία σχολείου</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="19">
-        <v>46417</v>
+        <v>46407</v>
       </c>
       <c r="B23" s="20"/>
       <c r="C23" s="21" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
       <c r="G23" s="21"/>
       <c r="H23" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Σάβ</v>
+        <v>Τετ</v>
       </c>
       <c r="I23" s="23" t="str">
         <f>IF($A23="","",$A23&amp;"#"&amp;COUNTIF($A$2:$A23,$A23))</f>
-        <v>46417#1</v>
+        <v>46407#1</v>
       </c>
       <c r="J23" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Εορτή Τριών Ιεραρχών (πέφτει Σάββατο)</v>
+        <v>Λήξη Α΄ τετραμήνου (εκτίμηση – εκκρεμεί εγκύκλιος)</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="19">
-        <v>46461</v>
+        <v>46417</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="21" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
       <c r="G24" s="21"/>
       <c r="H24" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Σάβ</v>
       </c>
       <c r="I24" s="23" t="str">
         <f>IF($A24="","",$A24&amp;"#"&amp;COUNTIF($A$2:$A24,$A24))</f>
-        <v>46461#1</v>
+        <v>46417#1</v>
       </c>
       <c r="J24" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Καθαρά Δευτέρα – Αργία</v>
+        <v>Εορτή Τριών Ιεραρχών (πέφτει Σάββατο)</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="19">
-        <v>46470</v>
+        <v>46461</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="21" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D25" s="21" t="s">
         <v>25</v>
@@ -2631,92 +3057,92 @@
       <c r="G25" s="21"/>
       <c r="H25" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Δευ</v>
       </c>
       <c r="I25" s="23" t="str">
         <f>IF($A25="","",$A25&amp;"#"&amp;COUNTIF($A$2:$A25,$A25))</f>
-        <v>46470#1</v>
+        <v>46461#1</v>
       </c>
       <c r="J25" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Σχολική εορτή για την 25η Μαρτίου</v>
+        <v>Καθαρά Δευτέρα – Αργία</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="19">
-        <v>46471</v>
+        <v>46470</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="21" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
       <c r="G26" s="21"/>
       <c r="H26" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Τετ</v>
       </c>
       <c r="I26" s="23" t="str">
         <f>IF($A26="","",$A26&amp;"#"&amp;COUNTIF($A$2:$A26,$A26))</f>
-        <v>46471#1</v>
+        <v>46470#1</v>
       </c>
       <c r="J26" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Εθνική επέτειος 25ης Μαρτίου – Αργία</v>
+        <v>Σχολική εορτή για την 25η Μαρτίου</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="19">
-        <v>46503</v>
+        <v>46471</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="21" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
       <c r="G27" s="21"/>
       <c r="H27" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I27" s="23" t="str">
         <f>IF($A27="","",$A27&amp;"#"&amp;COUNTIF($A$2:$A27,$A27))</f>
-        <v>46503#1</v>
+        <v>46471#1</v>
       </c>
       <c r="J27" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Διακοπές Πάσχα</v>
+        <v>Εθνική επέτειος 25ης Μαρτίου – Αργία</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="19">
-        <v>46504</v>
+        <v>46503</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E28" s="21"/>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
       <c r="H28" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Δευ</v>
       </c>
       <c r="I28" s="23" t="str">
         <f>IF($A28="","",$A28&amp;"#"&amp;COUNTIF($A$2:$A28,$A28))</f>
-        <v>46504#1</v>
+        <v>46503#1</v>
       </c>
       <c r="J28" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2725,25 +3151,25 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="19">
-        <v>46505</v>
+        <v>46504</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E29" s="21"/>
       <c r="F29" s="21"/>
       <c r="G29" s="21"/>
       <c r="H29" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Τρί</v>
       </c>
       <c r="I29" s="23" t="str">
         <f>IF($A29="","",$A29&amp;"#"&amp;COUNTIF($A$2:$A29,$A29))</f>
-        <v>46505#1</v>
+        <v>46504#1</v>
       </c>
       <c r="J29" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2752,25 +3178,25 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="19">
-        <v>46506</v>
+        <v>46505</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E30" s="21"/>
       <c r="F30" s="21"/>
       <c r="G30" s="21"/>
       <c r="H30" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Τετ</v>
       </c>
       <c r="I30" s="23" t="str">
         <f>IF($A30="","",$A30&amp;"#"&amp;COUNTIF($A$2:$A30,$A30))</f>
-        <v>46506#1</v>
+        <v>46505#1</v>
       </c>
       <c r="J30" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2779,25 +3205,25 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="19">
-        <v>46507</v>
+        <v>46506</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E31" s="21"/>
       <c r="F31" s="21"/>
       <c r="G31" s="21"/>
       <c r="H31" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I31" s="23" t="str">
         <f>IF($A31="","",$A31&amp;"#"&amp;COUNTIF($A$2:$A31,$A31))</f>
-        <v>46507#1</v>
+        <v>46506#1</v>
       </c>
       <c r="J31" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2806,25 +3232,25 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="19">
-        <v>46508</v>
+        <v>46507</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E32" s="21"/>
       <c r="F32" s="21"/>
       <c r="G32" s="21"/>
       <c r="H32" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Σάβ</v>
+        <v>Παρ</v>
       </c>
       <c r="I32" s="23" t="str">
         <f>IF($A32="","",$A32&amp;"#"&amp;COUNTIF($A$2:$A32,$A32))</f>
-        <v>46508#1</v>
+        <v>46507#1</v>
       </c>
       <c r="J32" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2833,25 +3259,25 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="19">
-        <v>46509</v>
+        <v>46510</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E33" s="21"/>
       <c r="F33" s="21"/>
       <c r="G33" s="21"/>
       <c r="H33" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Κυρ</v>
+        <v>Δευ</v>
       </c>
       <c r="I33" s="23" t="str">
         <f>IF($A33="","",$A33&amp;"#"&amp;COUNTIF($A$2:$A33,$A33))</f>
-        <v>46509#1</v>
+        <v>46510#1</v>
       </c>
       <c r="J33" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2860,25 +3286,25 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="19">
-        <v>46510</v>
+        <v>46511</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E34" s="21"/>
       <c r="F34" s="21"/>
       <c r="G34" s="21"/>
       <c r="H34" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Τρί</v>
       </c>
       <c r="I34" s="23" t="str">
         <f>IF($A34="","",$A34&amp;"#"&amp;COUNTIF($A$2:$A34,$A34))</f>
-        <v>46510#1</v>
+        <v>46511#1</v>
       </c>
       <c r="J34" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2887,25 +3313,25 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="19">
-        <v>46511</v>
+        <v>46512</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E35" s="21"/>
       <c r="F35" s="21"/>
       <c r="G35" s="21"/>
       <c r="H35" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Τετ</v>
       </c>
       <c r="I35" s="23" t="str">
         <f>IF($A35="","",$A35&amp;"#"&amp;COUNTIF($A$2:$A35,$A35))</f>
-        <v>46511#1</v>
+        <v>46512#1</v>
       </c>
       <c r="J35" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2914,25 +3340,25 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="19">
-        <v>46512</v>
+        <v>46513</v>
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E36" s="21"/>
       <c r="F36" s="21"/>
       <c r="G36" s="21"/>
       <c r="H36" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I36" s="23" t="str">
         <f>IF($A36="","",$A36&amp;"#"&amp;COUNTIF($A$2:$A36,$A36))</f>
-        <v>46512#1</v>
+        <v>46513#1</v>
       </c>
       <c r="J36" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2941,25 +3367,25 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
-        <v>46513</v>
+        <v>46514</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E37" s="21"/>
       <c r="F37" s="21"/>
       <c r="G37" s="21"/>
       <c r="H37" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Παρ</v>
       </c>
       <c r="I37" s="23" t="str">
         <f>IF($A37="","",$A37&amp;"#"&amp;COUNTIF($A$2:$A37,$A37))</f>
-        <v>46513#1</v>
+        <v>46514#1</v>
       </c>
       <c r="J37" s="23" t="str">
         <f t="shared" si="1"/>
@@ -2968,164 +3394,146 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="19">
-        <v>46514</v>
+        <v>46517</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="21" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
       <c r="H38" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Δευ</v>
       </c>
       <c r="I38" s="23" t="str">
         <f>IF($A38="","",$A38&amp;"#"&amp;COUNTIF($A$2:$A38,$A38))</f>
-        <v>46514#1</v>
+        <v>46517#1</v>
       </c>
       <c r="J38" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Διακοπές Πάσχα</v>
+        <v>Επαναλειτουργία σχολείου μετά το Πάσχα (εκτίμηση)</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="19">
-        <v>46515</v>
+        <v>46559</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="21" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E39" s="21"/>
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
       <c r="H39" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Σάβ</v>
+        <v>Δευ</v>
       </c>
       <c r="I39" s="23" t="str">
         <f>IF($A39="","",$A39&amp;"#"&amp;COUNTIF($A$2:$A39,$A39))</f>
-        <v>46515#1</v>
+        <v>46559#1</v>
       </c>
       <c r="J39" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Διακοπές Πάσχα</v>
+        <v>Αγίου Πνεύματος – Αργία</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="19">
-        <v>46516</v>
+        <v>46568</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="21" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
       <c r="G40" s="21"/>
       <c r="H40" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Κυρ</v>
+        <v>Τετ</v>
       </c>
       <c r="I40" s="23" t="str">
         <f>IF($A40="","",$A40&amp;"#"&amp;COUNTIF($A$2:$A40,$A40))</f>
-        <v>46516#1</v>
+        <v>46568#1</v>
       </c>
       <c r="J40" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Διακοπές Πάσχα</v>
+        <v>Λήξη διδακτικού έτους</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="19">
-        <v>46517</v>
-      </c>
+      <c r="A41" s="19"/>
       <c r="B41" s="20"/>
-      <c r="C41" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>29</v>
-      </c>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v/>
       </c>
       <c r="I41" s="23" t="str">
         <f>IF($A41="","",$A41&amp;"#"&amp;COUNTIF($A$2:$A41,$A41))</f>
-        <v>46517#1</v>
+        <v/>
       </c>
       <c r="J41" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Επαναλειτουργία σχολείου μετά το Πάσχα</v>
+        <v/>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="19">
-        <v>46559</v>
-      </c>
+      <c r="A42" s="19"/>
       <c r="B42" s="20"/>
-      <c r="C42" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>24</v>
-      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="21"/>
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
       <c r="H42" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v/>
       </c>
       <c r="I42" s="23" t="str">
         <f>IF($A42="","",$A42&amp;"#"&amp;COUNTIF($A$2:$A42,$A42))</f>
-        <v>46559#1</v>
+        <v/>
       </c>
       <c r="J42" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Αγίου Πνεύματος – Αργία</v>
+        <v/>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="19">
-        <v>46568</v>
-      </c>
+      <c r="A43" s="19"/>
       <c r="B43" s="20"/>
-      <c r="C43" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>29</v>
-      </c>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="21"/>
       <c r="F43" s="21"/>
       <c r="G43" s="21"/>
       <c r="H43" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v/>
       </c>
       <c r="I43" s="23" t="str">
         <f>IF($A43="","",$A43&amp;"#"&amp;COUNTIF($A$2:$A43,$A43))</f>
-        <v>46568#1</v>
+        <v/>
       </c>
       <c r="J43" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Λήξη διδακτικού έτους</v>
+        <v/>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
@@ -3599,7 +4007,7 @@
       <c r="F66" s="21"/>
       <c r="G66" s="21"/>
       <c r="H66" s="22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H66:H129" si="2">IF($A66="","",CHOOSE(WEEKDAY($A66,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I66" s="23" t="str">
@@ -3607,7 +4015,7 @@
         <v/>
       </c>
       <c r="J66" s="23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J66:J129" si="3">IF($A66="","",IF($B66="","",$B66&amp;"  ")&amp;$C66&amp;IF($E66="","","  ("&amp;$E66&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -3620,7 +4028,7 @@
       <c r="F67" s="21"/>
       <c r="G67" s="21"/>
       <c r="H67" s="22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I67" s="23" t="str">
@@ -3628,7 +4036,7 @@
         <v/>
       </c>
       <c r="J67" s="23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3641,7 +4049,7 @@
       <c r="F68" s="21"/>
       <c r="G68" s="21"/>
       <c r="H68" s="22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I68" s="23" t="str">
@@ -3649,7 +4057,7 @@
         <v/>
       </c>
       <c r="J68" s="23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -3662,7 +4070,7 @@
       <c r="F69" s="21"/>
       <c r="G69" s="21"/>
       <c r="H69" s="22" t="str">
-        <f t="shared" ref="H69:H132" si="2">IF($A69="","",CHOOSE(WEEKDAY($A69,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I69" s="23" t="str">
@@ -3670,7 +4078,7 @@
         <v/>
       </c>
       <c r="J69" s="23" t="str">
-        <f t="shared" ref="J69:J132" si="3">IF($A69="","",IF($B69="","",$B69&amp;"  ")&amp;$C69&amp;IF($E69="","","  ("&amp;$E69&amp;")"))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4725,13 +5133,11 @@
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A120" s="19"/>
-      <c r="B120" s="20"/>
-      <c r="C120" s="21"/>
-      <c r="D120" s="21"/>
-      <c r="E120" s="21"/>
-      <c r="F120" s="21"/>
-      <c r="G120" s="21"/>
+      <c r="C120" s="44"/>
+      <c r="D120" s="44"/>
+      <c r="E120" s="44"/>
+      <c r="F120" s="44"/>
+      <c r="G120" s="44"/>
       <c r="H120" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4746,13 +5152,11 @@
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A121" s="19"/>
-      <c r="B121" s="20"/>
-      <c r="C121" s="21"/>
-      <c r="D121" s="21"/>
-      <c r="E121" s="21"/>
-      <c r="F121" s="21"/>
-      <c r="G121" s="21"/>
+      <c r="C121" s="44"/>
+      <c r="D121" s="44"/>
+      <c r="E121" s="44"/>
+      <c r="F121" s="44"/>
+      <c r="G121" s="44"/>
       <c r="H121" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4767,13 +5171,11 @@
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A122" s="19"/>
-      <c r="B122" s="20"/>
-      <c r="C122" s="21"/>
-      <c r="D122" s="21"/>
-      <c r="E122" s="21"/>
-      <c r="F122" s="21"/>
-      <c r="G122" s="21"/>
+      <c r="C122" s="44"/>
+      <c r="D122" s="44"/>
+      <c r="E122" s="44"/>
+      <c r="F122" s="44"/>
+      <c r="G122" s="44"/>
       <c r="H122" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4927,7 +5329,7 @@
       <c r="F130" s="44"/>
       <c r="G130" s="44"/>
       <c r="H130" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="H130:H193" si="4">IF($A130="","",CHOOSE(WEEKDAY($A130,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I130" s="23" t="str">
@@ -4935,7 +5337,7 @@
         <v/>
       </c>
       <c r="J130" s="23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J130:J193" si="5">IF($A130="","",IF($B130="","",$B130&amp;"  ")&amp;$C130&amp;IF($E130="","","  ("&amp;$E130&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -4946,7 +5348,7 @@
       <c r="F131" s="44"/>
       <c r="G131" s="44"/>
       <c r="H131" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I131" s="23" t="str">
@@ -4954,7 +5356,7 @@
         <v/>
       </c>
       <c r="J131" s="23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4965,7 +5367,7 @@
       <c r="F132" s="44"/>
       <c r="G132" s="44"/>
       <c r="H132" s="22" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I132" s="23" t="str">
@@ -4973,7 +5375,7 @@
         <v/>
       </c>
       <c r="J132" s="23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -4984,7 +5386,7 @@
       <c r="F133" s="44"/>
       <c r="G133" s="44"/>
       <c r="H133" s="22" t="str">
-        <f t="shared" ref="H133:H196" si="4">IF($A133="","",CHOOSE(WEEKDAY($A133,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="I133" s="23" t="str">
@@ -4992,7 +5394,7 @@
         <v/>
       </c>
       <c r="J133" s="23" t="str">
-        <f t="shared" ref="J133:J196" si="5">IF($A133="","",IF($B133="","",$B133&amp;"  ")&amp;$C133&amp;IF($E133="","","  ("&amp;$E133&amp;")"))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
@@ -6143,7 +6545,7 @@
       <c r="F194" s="44"/>
       <c r="G194" s="44"/>
       <c r="H194" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="H194:H257" si="6">IF($A194="","",CHOOSE(WEEKDAY($A194,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I194" s="23" t="str">
@@ -6151,7 +6553,7 @@
         <v/>
       </c>
       <c r="J194" s="23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J194:J257" si="7">IF($A194="","",IF($B194="","",$B194&amp;"  ")&amp;$C194&amp;IF($E194="","","  ("&amp;$E194&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -6162,7 +6564,7 @@
       <c r="F195" s="44"/>
       <c r="G195" s="44"/>
       <c r="H195" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I195" s="23" t="str">
@@ -6170,7 +6572,7 @@
         <v/>
       </c>
       <c r="J195" s="23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6181,7 +6583,7 @@
       <c r="F196" s="44"/>
       <c r="G196" s="44"/>
       <c r="H196" s="22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I196" s="23" t="str">
@@ -6189,7 +6591,7 @@
         <v/>
       </c>
       <c r="J196" s="23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -6200,7 +6602,7 @@
       <c r="F197" s="44"/>
       <c r="G197" s="44"/>
       <c r="H197" s="22" t="str">
-        <f t="shared" ref="H197:H260" si="6">IF($A197="","",CHOOSE(WEEKDAY($A197,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="I197" s="23" t="str">
@@ -6208,7 +6610,7 @@
         <v/>
       </c>
       <c r="J197" s="23" t="str">
-        <f t="shared" ref="J197:J260" si="7">IF($A197="","",IF($B197="","",$B197&amp;"  ")&amp;$C197&amp;IF($E197="","","  ("&amp;$E197&amp;")"))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -7359,7 +7761,7 @@
       <c r="F258" s="44"/>
       <c r="G258" s="44"/>
       <c r="H258" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="H258:H321" si="8">IF($A258="","",CHOOSE(WEEKDAY($A258,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I258" s="23" t="str">
@@ -7367,7 +7769,7 @@
         <v/>
       </c>
       <c r="J258" s="23" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J258:J321" si="9">IF($A258="","",IF($B258="","",$B258&amp;"  ")&amp;$C258&amp;IF($E258="","","  ("&amp;$E258&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -7378,7 +7780,7 @@
       <c r="F259" s="44"/>
       <c r="G259" s="44"/>
       <c r="H259" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I259" s="23" t="str">
@@ -7386,7 +7788,7 @@
         <v/>
       </c>
       <c r="J259" s="23" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7397,7 +7799,7 @@
       <c r="F260" s="44"/>
       <c r="G260" s="44"/>
       <c r="H260" s="22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I260" s="23" t="str">
@@ -7405,7 +7807,7 @@
         <v/>
       </c>
       <c r="J260" s="23" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -7416,7 +7818,7 @@
       <c r="F261" s="44"/>
       <c r="G261" s="44"/>
       <c r="H261" s="22" t="str">
-        <f t="shared" ref="H261:H324" si="8">IF($A261="","",CHOOSE(WEEKDAY($A261,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I261" s="23" t="str">
@@ -7424,7 +7826,7 @@
         <v/>
       </c>
       <c r="J261" s="23" t="str">
-        <f t="shared" ref="J261:J324" si="9">IF($A261="","",IF($B261="","",$B261&amp;"  ")&amp;$C261&amp;IF($E261="","","  ("&amp;$E261&amp;")"))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -8575,7 +8977,7 @@
       <c r="F322" s="44"/>
       <c r="G322" s="44"/>
       <c r="H322" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="H322:H385" si="10">IF($A322="","",CHOOSE(WEEKDAY($A322,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I322" s="23" t="str">
@@ -8583,7 +8985,7 @@
         <v/>
       </c>
       <c r="J322" s="23" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J322:J385" si="11">IF($A322="","",IF($B322="","",$B322&amp;"  ")&amp;$C322&amp;IF($E322="","","  ("&amp;$E322&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -8594,7 +8996,7 @@
       <c r="F323" s="44"/>
       <c r="G323" s="44"/>
       <c r="H323" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="I323" s="23" t="str">
@@ -8602,7 +9004,7 @@
         <v/>
       </c>
       <c r="J323" s="23" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8613,7 +9015,7 @@
       <c r="F324" s="44"/>
       <c r="G324" s="44"/>
       <c r="H324" s="22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="I324" s="23" t="str">
@@ -8621,7 +9023,7 @@
         <v/>
       </c>
       <c r="J324" s="23" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -8632,7 +9034,7 @@
       <c r="F325" s="44"/>
       <c r="G325" s="44"/>
       <c r="H325" s="22" t="str">
-        <f t="shared" ref="H325:H388" si="10">IF($A325="","",CHOOSE(WEEKDAY($A325,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="I325" s="23" t="str">
@@ -8640,7 +9042,7 @@
         <v/>
       </c>
       <c r="J325" s="23" t="str">
-        <f t="shared" ref="J325:J388" si="11">IF($A325="","",IF($B325="","",$B325&amp;"  ")&amp;$C325&amp;IF($E325="","","  ("&amp;$E325&amp;")"))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -9791,7 +10193,7 @@
       <c r="F386" s="44"/>
       <c r="G386" s="44"/>
       <c r="H386" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="H386:H399" si="12">IF($A386="","",CHOOSE(WEEKDAY($A386,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
         <v/>
       </c>
       <c r="I386" s="23" t="str">
@@ -9799,7 +10201,7 @@
         <v/>
       </c>
       <c r="J386" s="23" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J386:J399" si="13">IF($A386="","",IF($B386="","",$B386&amp;"  ")&amp;$C386&amp;IF($E386="","","  ("&amp;$E386&amp;")"))</f>
         <v/>
       </c>
     </row>
@@ -9810,7 +10212,7 @@
       <c r="F387" s="44"/>
       <c r="G387" s="44"/>
       <c r="H387" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="I387" s="23" t="str">
@@ -9818,7 +10220,7 @@
         <v/>
       </c>
       <c r="J387" s="23" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -9829,7 +10231,7 @@
       <c r="F388" s="44"/>
       <c r="G388" s="44"/>
       <c r="H388" s="22" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="I388" s="23" t="str">
@@ -9837,7 +10239,7 @@
         <v/>
       </c>
       <c r="J388" s="23" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -9848,7 +10250,7 @@
       <c r="F389" s="44"/>
       <c r="G389" s="44"/>
       <c r="H389" s="22" t="str">
-        <f t="shared" ref="H389:H402" si="12">IF($A389="","",CHOOSE(WEEKDAY($A389,2),"Δευ","Τρί","Τετ","Πέμ","Παρ","Σάβ","Κυρ"))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="I389" s="23" t="str">
@@ -9856,7 +10258,7 @@
         <v/>
       </c>
       <c r="J389" s="23" t="str">
-        <f t="shared" ref="J389:J402" si="13">IF($A389="","",IF($B389="","",$B389&amp;"  ")&amp;$C389&amp;IF($E389="","","  ("&amp;$E389&amp;")"))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -10050,118 +10452,46 @@
         <v/>
       </c>
     </row>
-    <row r="400" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C400" s="44"/>
-      <c r="D400" s="44"/>
-      <c r="E400" s="44"/>
-      <c r="F400" s="44"/>
-      <c r="G400" s="44"/>
-      <c r="H400" s="22" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="I400" s="23" t="str">
-        <f>IF($A400="","",$A400&amp;"#"&amp;COUNTIF($A$2:$A400,$A400))</f>
-        <v/>
-      </c>
-      <c r="J400" s="23" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="401" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C401" s="44"/>
-      <c r="D401" s="44"/>
-      <c r="E401" s="44"/>
-      <c r="F401" s="44"/>
-      <c r="G401" s="44"/>
-      <c r="H401" s="22" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="I401" s="23" t="str">
-        <f>IF($A401="","",$A401&amp;"#"&amp;COUNTIF($A$2:$A401,$A401))</f>
-        <v/>
-      </c>
-      <c r="J401" s="23" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="402" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C402" s="44"/>
-      <c r="D402" s="44"/>
-      <c r="E402" s="44"/>
-      <c r="F402" s="44"/>
-      <c r="G402" s="44"/>
-      <c r="H402" s="22" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="I402" s="23" t="str">
-        <f>IF($A402="","",$A402&amp;"#"&amp;COUNTIF($A$2:$A402,$A402))</f>
-        <v/>
-      </c>
-      <c r="J402" s="23" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J402" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J402">
-      <sortCondition ref="A1:A402"/>
+  <autoFilter ref="A1:J399" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J399">
+      <sortCondition ref="A1:A399"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="A2:G3 A5:G8 A10:G33 A42:G402 A35:G40">
-    <cfRule type="expression" dxfId="38" priority="10">
+  <conditionalFormatting sqref="A2:G399">
+    <cfRule type="expression" dxfId="44" priority="2">
+      <formula>$D2="Αργία / Διακοπές"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="3">
+      <formula>$D2="Εορτή / Εκκλησιασμός"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="4">
+      <formula>$D2="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="5">
+      <formula>$D2="Σύλλογος διδασκόντων"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="6">
+      <formula>$D2="Ενημέρωση γονέων / Έλεγχοι"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="7">
+      <formula>$D2="Ορόσημο / Εξετάσεις"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="8">
+      <formula>$D2="Επιμόρφωση εκπαιδευτικών"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="9">
+      <formula>$D2="Δράση / Πρόγραμμα / Όμιλος"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:G399">
+    <cfRule type="expression" dxfId="0" priority="11">
       <formula>AND($A2="",$A1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:G402">
-    <cfRule type="expression" dxfId="37" priority="2">
-      <formula>$D2="Αργία / Διακοπές"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="3">
-      <formula>$D2="Εορτή / Εκκλησιασμός"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="4">
-      <formula>$D2="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="5">
-      <formula>$D2="Σύλλογος διδασκόντων"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="6">
-      <formula>$D2="Ενημέρωση γονέων / Έλεγχοι"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="7">
-      <formula>$D2="Ορόσημο / Εξετάσεις"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="8">
-      <formula>$D2="Δράση"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="9">
-      <formula>$D2="Δράση / Πρόγραμμα / Όμιλος"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:G9">
-    <cfRule type="expression" dxfId="29" priority="20">
-      <formula>AND($A9="",#REF!&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A34:G34">
-    <cfRule type="expression" dxfId="28" priority="22">
-      <formula>AND($A34="",$A31&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A41:G41">
-    <cfRule type="expression" dxfId="27" priority="24">
-      <formula>AND($A41="",$A38&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Τίτλος δράσης" prompt="Σύντομος τίτλος. Ώρες στη στήλη Β, τμήματα στη στήλη Ε." sqref="C2:C402" xr:uid="{0CD0AE7B-36D6-492A-8412-0F46B1D4BF63}"/>
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Μη έγκυρη ημερομηνία" error="Γράψε πραγματική ημερομηνία στη μορφή 16/10/2026." promptTitle="Ημερομηνία" prompt="Γράψε την ημερομηνία, π.χ. 16/10/2026. Νέα δράση = πρώτη κενή (κίτρινη) γραμμή στο τέλος." sqref="A2:A402" xr:uid="{04C73EC8-C88D-4F69-A9AB-F63578E3CB50}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Τίτλος δράσης" prompt="Σύντομος τίτλος. Ώρες στη στήλη Β, τμήματα στη στήλη Ε." sqref="C2:C399" xr:uid="{0CD0AE7B-36D6-492A-8412-0F46B1D4BF63}"/>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Μη έγκυρη ημερομηνία" error="Γράψε πραγματική ημερομηνία στη μορφή 16/10/2026." promptTitle="Ημερομηνία" prompt="Γράψε την ημερομηνία, π.χ. 16/10/2026. Νέα δράση = πρώτη κενή (κίτρινη) γραμμή στο τέλος." sqref="A2:A399" xr:uid="{04C73EC8-C88D-4F69-A9AB-F63578E3CB50}">
       <formula1>OR($A2="",AND(ISNUMBER($A2),$A2&gt;36526))</formula1>
     </dataValidation>
   </dataValidations>
@@ -10177,7 +10507,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D2:D402</xm:sqref>
+          <xm:sqref>D2:D399</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10205,53 +10535,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
       <c r="K1" s="36" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="N1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61" t="str">
+      <c r="A2" s="95" t="str">
         <f>$L$2&amp;" "&amp;$L$6</f>
         <v>ΟΚΤΩΒΡΙΟΣ 2026</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="F2" s="61" t="str">
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="F2" s="95" t="str">
         <f>$L$3&amp;" "&amp;$L$8</f>
         <v>ΝΟΕΜΒΡΙΟΣ 2026</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
       <c r="K2" s="34" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="L2" s="38" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="N2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="O2">
         <v>9</v>
@@ -10262,37 +10592,37 @@
     </row>
     <row r="3" spans="1:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K3" s="35" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L3" s="37" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="N3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O3">
         <v>10</v>
@@ -10311,11 +10641,11 @@
         <v>46296</v>
       </c>
       <c r="C4" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="28" t="str">
-        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F4" s="25" t="str">
@@ -10327,16 +10657,16 @@
         <v>46327</v>
       </c>
       <c r="H4" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I4" s="28" t="str">
-        <f>IF($G4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="K4" s="34"/>
       <c r="N4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="O4">
         <v>11</v>
@@ -10355,11 +10685,11 @@
         <v>46297</v>
       </c>
       <c r="C5" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="28" t="str">
-        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F5" s="25" t="str">
@@ -10371,22 +10701,22 @@
         <v>46328</v>
       </c>
       <c r="H5" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I5" s="28" t="str">
-        <f>IF($G5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="K5" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L5">
         <f>INDEX($O$2:$O$11,MATCH($L$2,$N$2:$N$11,0))</f>
         <v>10</v>
       </c>
       <c r="N5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="O5">
         <v>12</v>
@@ -10405,11 +10735,11 @@
         <v>46298</v>
       </c>
       <c r="C6" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="28" t="str">
-        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F6" s="25" t="str">
@@ -10421,22 +10751,22 @@
         <v>46329</v>
       </c>
       <c r="H6" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I6" s="28" t="str">
-        <f>IF($G6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="K6" s="34" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L6">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($P$2:$P$11,MATCH($L$2,$N$2:$N$11,0))</f>
         <v>2026</v>
       </c>
       <c r="N6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O6">
         <v>1</v>
@@ -10445,7 +10775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Κυρ</v>
@@ -10455,11 +10785,11 @@
         <v>46299</v>
       </c>
       <c r="C7" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="28" t="str">
-        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F7" s="25" t="str">
@@ -10471,22 +10801,22 @@
         <v>46330</v>
       </c>
       <c r="H7" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
-        <v>Δράση</v>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <v>Δράση / Πρόγραμμα / Όμιλος</v>
       </c>
       <c r="I7" s="28" t="str">
-        <f>IF($G7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
-        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</v>
+        <f>IF($G7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives»</v>
       </c>
       <c r="K7" s="34" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="L7">
         <f>INDEX($O$2:$O$11,MATCH($L$3,$N$2:$N$11,0))</f>
         <v>11</v>
       </c>
       <c r="N7" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O7">
         <v>2</v>
@@ -10505,11 +10835,11 @@
         <v>46300</v>
       </c>
       <c r="C8" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="28" t="str">
-        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F8" s="25" t="str">
@@ -10521,22 +10851,22 @@
         <v>46331</v>
       </c>
       <c r="H8" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I8" s="28" t="str">
-        <f>IF($G8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="K8" s="34" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L8">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($P$2:$P$11,MATCH($L$3,$N$2:$N$11,0))</f>
         <v>2026</v>
       </c>
       <c r="N8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O8">
         <v>3</v>
@@ -10555,11 +10885,11 @@
         <v>46301</v>
       </c>
       <c r="C9" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="28" t="str">
-        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F9" s="25" t="str">
@@ -10571,15 +10901,15 @@
         <v>46332</v>
       </c>
       <c r="H9" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I9" s="28" t="str">
-        <f>IF($G9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="N9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="O9">
         <v>4</v>
@@ -10598,11 +10928,11 @@
         <v>46302</v>
       </c>
       <c r="C10" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="28" t="str">
-        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F10" s="25" t="str">
@@ -10614,15 +10944,15 @@
         <v>46333</v>
       </c>
       <c r="H10" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I10" s="28" t="str">
-        <f>IF($G10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="N10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="O10">
         <v>5</v>
@@ -10641,11 +10971,11 @@
         <v>46303</v>
       </c>
       <c r="C11" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="28" t="str">
-        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F11" s="25" t="str">
@@ -10657,15 +10987,15 @@
         <v>46334</v>
       </c>
       <c r="H11" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I11" s="28" t="str">
-        <f>IF($G11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="N11" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="O11">
         <v>6</v>
@@ -10684,11 +11014,11 @@
         <v>46304</v>
       </c>
       <c r="C12" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="28" t="str">
-        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F12" s="25" t="str">
@@ -10700,11 +11030,11 @@
         <v>46335</v>
       </c>
       <c r="H12" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I12" s="28" t="str">
-        <f>IF($G12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10718,11 +11048,11 @@
         <v>46305</v>
       </c>
       <c r="C13" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="28" t="str">
-        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F13" s="25" t="str">
@@ -10734,11 +11064,11 @@
         <v>46336</v>
       </c>
       <c r="H13" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I13" s="28" t="str">
-        <f>IF($G13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10752,11 +11082,11 @@
         <v>46306</v>
       </c>
       <c r="C14" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="28" t="str">
-        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F14" s="25" t="str">
@@ -10768,11 +11098,11 @@
         <v>46337</v>
       </c>
       <c r="H14" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I14" s="28" t="str">
-        <f>IF($G14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10786,11 +11116,11 @@
         <v>46307</v>
       </c>
       <c r="C15" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="28" t="str">
-        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F15" s="25" t="str">
@@ -10802,11 +11132,11 @@
         <v>46338</v>
       </c>
       <c r="H15" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I15" s="28" t="str">
-        <f>IF($G15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10820,11 +11150,11 @@
         <v>46308</v>
       </c>
       <c r="C16" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="28" t="str">
-        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F16" s="25" t="str">
@@ -10836,11 +11166,11 @@
         <v>46339</v>
       </c>
       <c r="H16" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I16" s="28" t="str">
-        <f>IF($G16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10854,11 +11184,11 @@
         <v>46309</v>
       </c>
       <c r="C17" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="28" t="str">
-        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F17" s="25" t="str">
@@ -10870,11 +11200,11 @@
         <v>46340</v>
       </c>
       <c r="H17" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I17" s="28" t="str">
-        <f>IF($G17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10888,11 +11218,11 @@
         <v>46310</v>
       </c>
       <c r="C18" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="28" t="str">
-        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F18" s="25" t="str">
@@ -10904,11 +11234,11 @@
         <v>46341</v>
       </c>
       <c r="H18" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I18" s="28" t="str">
-        <f>IF($G18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10922,11 +11252,11 @@
         <v>46311</v>
       </c>
       <c r="C19" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="28" t="str">
-        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F19" s="25" t="str">
@@ -10938,11 +11268,11 @@
         <v>46342</v>
       </c>
       <c r="H19" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I19" s="28" t="str">
-        <f>IF($G19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -10956,11 +11286,11 @@
         <v>46312</v>
       </c>
       <c r="C20" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="28" t="str">
-        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F20" s="25" t="str">
@@ -10972,11 +11302,11 @@
         <v>46343</v>
       </c>
       <c r="H20" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v>Εορτή / Εκκλησιασμός</v>
       </c>
       <c r="I20" s="28" t="str">
-        <f>IF($G20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</v>
       </c>
     </row>
@@ -10990,11 +11320,11 @@
         <v>46313</v>
       </c>
       <c r="C21" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="28" t="str">
-        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F21" s="25" t="str">
@@ -11006,11 +11336,11 @@
         <v>46344</v>
       </c>
       <c r="H21" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I21" s="28" t="str">
-        <f>IF($G21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11024,11 +11354,11 @@
         <v>46314</v>
       </c>
       <c r="C22" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="28" t="str">
-        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F22" s="25" t="str">
@@ -11040,11 +11370,11 @@
         <v>46345</v>
       </c>
       <c r="H22" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I22" s="28" t="str">
-        <f>IF($G22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11058,11 +11388,11 @@
         <v>46315</v>
       </c>
       <c r="C23" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F23" s="25" t="str">
@@ -11074,11 +11404,11 @@
         <v>46346</v>
       </c>
       <c r="H23" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I23" s="28" t="str">
-        <f>IF($G23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11092,11 +11422,11 @@
         <v>46316</v>
       </c>
       <c r="C24" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="28" t="str">
-        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F24" s="25" t="str">
@@ -11108,11 +11438,11 @@
         <v>46347</v>
       </c>
       <c r="H24" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I24" s="28" t="str">
-        <f>IF($G24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11126,11 +11456,11 @@
         <v>46317</v>
       </c>
       <c r="C25" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="28" t="str">
-        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F25" s="25" t="str">
@@ -11142,11 +11472,11 @@
         <v>46348</v>
       </c>
       <c r="H25" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I25" s="28" t="str">
-        <f>IF($G25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11160,11 +11490,11 @@
         <v>46318</v>
       </c>
       <c r="C26" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="28" t="str">
-        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F26" s="25" t="str">
@@ -11176,11 +11506,11 @@
         <v>46349</v>
       </c>
       <c r="H26" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I26" s="28" t="str">
-        <f>IF($G26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11194,11 +11524,11 @@
         <v>46319</v>
       </c>
       <c r="C27" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="28" t="str">
-        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F27" s="25" t="str">
@@ -11210,11 +11540,11 @@
         <v>46350</v>
       </c>
       <c r="H27" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I27" s="28" t="str">
-        <f>IF($G27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11228,11 +11558,11 @@
         <v>46320</v>
       </c>
       <c r="C28" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F28" s="25" t="str">
@@ -11244,15 +11574,15 @@
         <v>46351</v>
       </c>
       <c r="H28" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I28" s="28" t="str">
-        <f>IF($G28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <f>IF($G28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A29" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Δευ</v>
@@ -11262,12 +11592,12 @@
         <v>46321</v>
       </c>
       <c r="C29" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v>Αργία / Διακοπές</v>
       </c>
       <c r="D29" s="28" t="str">
-        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
-        <v>Αγίου Δημητρίου</v>
+        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v>Αγίου Δημητρίου – Ελευθέρια Θεσσαλονίκης (τοπική αργία)</v>
       </c>
       <c r="F29" s="25" t="str">
         <f t="shared" si="2"/>
@@ -11278,15 +11608,15 @@
         <v>46352</v>
       </c>
       <c r="H29" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I29" s="28" t="str">
-        <f>IF($G29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+        <f>IF($G29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Τρί</v>
@@ -11296,12 +11626,12 @@
         <v>46322</v>
       </c>
       <c r="C30" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v>Εορτή / Εκκλησιασμός</v>
       </c>
       <c r="D30" s="28" t="str">
-        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
-        <v>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου</v>
+        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου (χωρίς μάθημα)</v>
       </c>
       <c r="F30" s="25" t="str">
         <f t="shared" si="2"/>
@@ -11312,11 +11642,11 @@
         <v>46353</v>
       </c>
       <c r="H30" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I30" s="28" t="str">
-        <f>IF($G30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11330,11 +11660,11 @@
         <v>46323</v>
       </c>
       <c r="C31" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v>Αργία / Διακοπές</v>
       </c>
       <c r="D31" s="28" t="str">
-        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v>Εθνική επέτειος 28ης Οκτωβρίου – Αργία</v>
       </c>
       <c r="F31" s="25" t="str">
@@ -11346,11 +11676,11 @@
         <v>46354</v>
       </c>
       <c r="H31" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I31" s="28" t="str">
-        <f>IF($G31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11364,11 +11694,11 @@
         <v>46324</v>
       </c>
       <c r="C32" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="28" t="str">
-        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F32" s="25" t="str">
@@ -11380,15 +11710,15 @@
         <v>46355</v>
       </c>
       <c r="H32" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I32" s="28" t="str">
-        <f>IF($G32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <f>IF($G32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Παρ</v>
@@ -11398,11 +11728,11 @@
         <v>46325</v>
       </c>
       <c r="C33" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="28" t="str">
-        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F33" s="25" t="str">
@@ -11414,12 +11744,12 @@
         <v>46356</v>
       </c>
       <c r="H33" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
-        <v/>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <v>Δράση / Πρόγραμμα / Όμιλος</v>
       </c>
       <c r="I33" s="28" t="str">
-        <f>IF($G33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
-        <v/>
+        <f>IF($G33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v>09:00-12.30  Μουσείο Μακεδονικού Αγώνα</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -11432,11 +11762,11 @@
         <v>46326</v>
       </c>
       <c r="C34" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="28" t="str">
-        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F34" s="25" t="str">
@@ -11448,74 +11778,74 @@
         <v/>
       </c>
       <c r="H34" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="I34" s="28" t="str">
-        <f>IF($G34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($G34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($G34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($G34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
-      <c r="B37" s="59" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="59"/>
-      <c r="D37" s="59"/>
+      <c r="B37" s="93" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="93"/>
+      <c r="D37" s="93"/>
       <c r="F37" s="12"/>
-      <c r="G37" s="59" t="s">
-        <v>28</v>
-      </c>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
+      <c r="G37" s="93" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" s="93"/>
+      <c r="I37" s="93"/>
     </row>
     <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
-      <c r="B38" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="59"/>
-      <c r="D38" s="59"/>
+      <c r="B38" s="93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="93"/>
+      <c r="D38" s="93"/>
       <c r="F38" s="13"/>
-      <c r="G38" s="59" t="s">
-        <v>29</v>
-      </c>
-      <c r="H38" s="59"/>
-      <c r="I38" s="59"/>
+      <c r="G38" s="93" t="s">
+        <v>30</v>
+      </c>
+      <c r="H38" s="93"/>
+      <c r="I38" s="93"/>
     </row>
     <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
-      <c r="B39" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="59"/>
-      <c r="D39" s="59"/>
+      <c r="B39" s="93" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="93"/>
+      <c r="D39" s="93"/>
       <c r="F39" s="14"/>
-      <c r="G39" s="59" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="59"/>
-      <c r="I39" s="59"/>
+      <c r="G39" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="H39" s="93"/>
+      <c r="I39" s="93"/>
     </row>
     <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11"/>
-      <c r="B40" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
+      <c r="B40" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="93"/>
+      <c r="D40" s="93"/>
       <c r="F40" s="15"/>
-      <c r="G40" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="H40" s="59"/>
-      <c r="I40" s="59"/>
+      <c r="G40" s="93" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" s="93"/>
+      <c r="I40" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -11532,60 +11862,60 @@
     <mergeCell ref="G38:I38"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:D34">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>$C4="Αργία / Διακοπές"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="2">
+    <cfRule type="expression" dxfId="35" priority="2">
       <formula>$C4="Εορτή / Εκκλησιασμός"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="3">
+    <cfRule type="expression" dxfId="34" priority="3">
       <formula>$C4="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="4">
+    <cfRule type="expression" dxfId="33" priority="4">
       <formula>$C4="Σύλλογος διδασκόντων"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="5">
+    <cfRule type="expression" dxfId="32" priority="5">
       <formula>$C4="Ενημέρωση γονέων / Έλεγχοι"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="6">
+    <cfRule type="expression" dxfId="31" priority="6">
       <formula>$C4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="7">
-      <formula>$C4="Δράση"</formula>
+    <cfRule type="expression" dxfId="30" priority="7">
+      <formula>$C4="Επιμόρφωση εκπαιδευτικών"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="8">
+    <cfRule type="expression" dxfId="29" priority="8">
       <formula>$C4="Δράση / Πρόγραμμα / Όμιλος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="9">
+    <cfRule type="expression" dxfId="28" priority="9">
       <formula>IF($B4="",0,WEEKDAY($B4,2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:I34">
-    <cfRule type="expression" dxfId="17" priority="10">
+    <cfRule type="expression" dxfId="27" priority="10">
       <formula>$H4="Αργία / Διακοπές"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="11">
+    <cfRule type="expression" dxfId="26" priority="11">
       <formula>$H4="Εορτή / Εκκλησιασμός"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="12">
+    <cfRule type="expression" dxfId="25" priority="12">
       <formula>$H4="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="13">
+    <cfRule type="expression" dxfId="24" priority="13">
       <formula>$H4="Σύλλογος διδασκόντων"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="23" priority="14">
       <formula>$H4="Ενημέρωση γονέων / Έλεγχοι"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="15">
+    <cfRule type="expression" dxfId="22" priority="15">
       <formula>$H4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="16">
-      <formula>$H4="Δράση"</formula>
+    <cfRule type="expression" dxfId="21" priority="16">
+      <formula>$H4="Επιμόρφωση εκπαιδευτικών"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="17">
+    <cfRule type="expression" dxfId="20" priority="17">
       <formula>$H4="Δράση / Πρόγραμμα / Όμιλος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="18">
+    <cfRule type="expression" dxfId="19" priority="18">
       <formula>IF($G4="",0,WEEKDAY($G4,2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11608,6 +11938,2210 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:Z60"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="5" width="34.21875" customWidth="1"/>
+    <col min="6" max="7" width="20.33203125" customWidth="1"/>
+    <col min="8" max="10" width="3.6640625" customWidth="1"/>
+    <col min="11" max="11" width="20.33203125" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="89" t="str">
+        <f>ΟΔΗΓΙΕΣ!$A$1</f>
+        <v>3ο ΓΥΜΝΑΣΙΟ ΠΟΛΙΧΝΗΣ  ·  ΗΜΕΡΟΛΟΓΙΟ ΔΡΑΣΕΩΝ  ·  ΣΧΟΛΙΚΟ ΕΤΟΣ 2026-27</v>
+      </c>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="P1" s="58" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57"/>
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
+      <c r="Z1" s="57"/>
+    </row>
+    <row r="2" spans="1:26" ht="34.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="90" t="str">
+        <f>$L$2&amp;" "&amp;$L$6</f>
+        <v>ΝΟΕΜΒΡΙΟΣ 2026</v>
+      </c>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="L2" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" s="58">
+        <v>9</v>
+      </c>
+      <c r="P2" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
+      <c r="Y2" s="57"/>
+      <c r="Z2" s="57"/>
+    </row>
+    <row r="3" spans="1:26" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="69" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="69" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="69" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="69" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="70" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="70" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="O3" s="58">
+        <v>10</v>
+      </c>
+      <c r="P3" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="57"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="68" t="str">
+        <f>IF(MONTH($L$7+0)=$L$5,$L$7+0,"")</f>
+        <v/>
+      </c>
+      <c r="B4" s="68" t="str">
+        <f>IF(MONTH($L$7+1)=$L$5,$L$7+1,"")</f>
+        <v/>
+      </c>
+      <c r="C4" s="68" t="str">
+        <f>IF(MONTH($L$7+2)=$L$5,$L$7+2,"")</f>
+        <v/>
+      </c>
+      <c r="D4" s="68" t="str">
+        <f>IF(MONTH($L$7+3)=$L$5,$L$7+3,"")</f>
+        <v/>
+      </c>
+      <c r="E4" s="68" t="str">
+        <f>IF(MONTH($L$7+4)=$L$5,$L$7+4,"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="68" t="str">
+        <f>IF(MONTH($L$7+5)=$L$5,$L$7+5,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="68">
+        <f>IF(MONTH($L$7+6)=$L$5,$L$7+6,"")</f>
+        <v>46327</v>
+      </c>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="O4" s="58">
+        <v>11</v>
+      </c>
+      <c r="P4" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="57"/>
+      <c r="R4" s="57"/>
+      <c r="S4" s="57"/>
+      <c r="T4" s="57"/>
+      <c r="U4" s="57"/>
+      <c r="V4" s="57"/>
+      <c r="W4" s="57"/>
+      <c r="X4" s="57"/>
+      <c r="Y4" s="57"/>
+      <c r="Z4" s="57"/>
+    </row>
+    <row r="5" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="63" t="str">
+        <f>IF(A4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="B5" s="63" t="str">
+        <f>IF(B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C5" s="63" t="str">
+        <f>IF(C4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D5" s="63" t="str">
+        <f>IF(D4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E5" s="63" t="str">
+        <f>IF(E4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F5" s="63" t="str">
+        <f>IF(F4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G5" s="63" t="str">
+        <f>IF(G4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="L5" s="58">
+        <f>INDEX($O$2:$O$11,MATCH($L$2,$N$2:$N$11,0))</f>
+        <v>11</v>
+      </c>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="O5" s="58">
+        <v>12</v>
+      </c>
+      <c r="P5" s="58">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="57"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="57"/>
+      <c r="X5" s="57"/>
+      <c r="Y5" s="57"/>
+      <c r="Z5" s="57"/>
+    </row>
+    <row r="6" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="L6" s="58">
+        <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($P$2:$P$11,MATCH($L$2,$N$2:$N$11,0))</f>
+        <v>2026</v>
+      </c>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58" t="s">
+        <v>75</v>
+      </c>
+      <c r="O6" s="58">
+        <v>1</v>
+      </c>
+      <c r="P6" s="58">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="57"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="57"/>
+      <c r="U6" s="57"/>
+      <c r="V6" s="57"/>
+      <c r="W6" s="57"/>
+      <c r="X6" s="57"/>
+      <c r="Y6" s="57"/>
+      <c r="Z6" s="57"/>
+    </row>
+    <row r="7" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="65"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="L7" s="59">
+        <f>DATE($L$6,$L$5,1)-WEEKDAY(DATE($L$6,$L$5,1),2)+1</f>
+        <v>46321</v>
+      </c>
+      <c r="M7" s="58"/>
+      <c r="N7" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="O7" s="58">
+        <v>2</v>
+      </c>
+      <c r="P7" s="58">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="57"/>
+      <c r="R7" s="57"/>
+      <c r="S7" s="57"/>
+      <c r="T7" s="57"/>
+      <c r="U7" s="57"/>
+      <c r="V7" s="57"/>
+      <c r="W7" s="57"/>
+      <c r="X7" s="57"/>
+      <c r="Y7" s="57"/>
+      <c r="Z7" s="57"/>
+    </row>
+    <row r="8" spans="1:26" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="67"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="58"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="O8" s="58">
+        <v>3</v>
+      </c>
+      <c r="P8" s="58">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="57"/>
+      <c r="R8" s="57"/>
+      <c r="S8" s="57"/>
+      <c r="T8" s="57"/>
+      <c r="U8" s="57"/>
+      <c r="V8" s="57"/>
+      <c r="W8" s="57"/>
+      <c r="X8" s="57"/>
+      <c r="Y8" s="57"/>
+      <c r="Z8" s="57"/>
+    </row>
+    <row r="9" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="62">
+        <f>IF(MONTH($L$7+7)=$L$5,$L$7+7,"")</f>
+        <v>46328</v>
+      </c>
+      <c r="B9" s="62">
+        <f>IF(MONTH($L$7+8)=$L$5,$L$7+8,"")</f>
+        <v>46329</v>
+      </c>
+      <c r="C9" s="62">
+        <f>IF(MONTH($L$7+9)=$L$5,$L$7+9,"")</f>
+        <v>46330</v>
+      </c>
+      <c r="D9" s="62">
+        <f>IF(MONTH($L$7+10)=$L$5,$L$7+10,"")</f>
+        <v>46331</v>
+      </c>
+      <c r="E9" s="62">
+        <f>IF(MONTH($L$7+11)=$L$5,$L$7+11,"")</f>
+        <v>46332</v>
+      </c>
+      <c r="F9" s="62">
+        <f>IF(MONTH($L$7+12)=$L$5,$L$7+12,"")</f>
+        <v>46333</v>
+      </c>
+      <c r="G9" s="62">
+        <f>IF(MONTH($L$7+13)=$L$5,$L$7+13,"")</f>
+        <v>46334</v>
+      </c>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="58">
+        <v>4</v>
+      </c>
+      <c r="P9" s="58">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="57"/>
+      <c r="S9" s="57"/>
+      <c r="T9" s="57"/>
+      <c r="U9" s="57"/>
+      <c r="V9" s="57"/>
+      <c r="W9" s="57"/>
+      <c r="X9" s="57"/>
+      <c r="Y9" s="57"/>
+      <c r="Z9" s="57"/>
+    </row>
+    <row r="10" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="63" t="str">
+        <f>IF(A9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="B10" s="63" t="str">
+        <f>IF(B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C10" s="63" t="str">
+        <f>IF(C9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives»</v>
+      </c>
+      <c r="D10" s="63" t="str">
+        <f>IF(D9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E10" s="63" t="str">
+        <f>IF(E9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F10" s="63" t="str">
+        <f>IF(F9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G10" s="63" t="str">
+        <f>IF(G9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="58"/>
+      <c r="L10" s="58"/>
+      <c r="M10" s="58"/>
+      <c r="N10" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="O10" s="58">
+        <v>5</v>
+      </c>
+      <c r="P10" s="58">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="57"/>
+      <c r="R10" s="57"/>
+      <c r="S10" s="57"/>
+      <c r="T10" s="57"/>
+      <c r="U10" s="57"/>
+      <c r="V10" s="57"/>
+      <c r="W10" s="57"/>
+      <c r="X10" s="57"/>
+      <c r="Y10" s="57"/>
+      <c r="Z10" s="57"/>
+    </row>
+    <row r="11" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="64"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="58"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="58"/>
+      <c r="N11" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="O11" s="58">
+        <v>6</v>
+      </c>
+      <c r="P11" s="58">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="57"/>
+      <c r="S11" s="57"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="57"/>
+      <c r="V11" s="57"/>
+      <c r="W11" s="57"/>
+      <c r="X11" s="57"/>
+      <c r="Y11" s="57"/>
+      <c r="Z11" s="57"/>
+    </row>
+    <row r="12" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="65"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="57"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="57"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="57"/>
+      <c r="P12" s="57"/>
+      <c r="Q12" s="57"/>
+      <c r="R12" s="57"/>
+      <c r="S12" s="57"/>
+      <c r="T12" s="57"/>
+      <c r="U12" s="57"/>
+      <c r="V12" s="57"/>
+      <c r="W12" s="57"/>
+      <c r="X12" s="57"/>
+      <c r="Y12" s="57"/>
+      <c r="Z12" s="57"/>
+    </row>
+    <row r="13" spans="1:26" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="67"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="57"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="57"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="57"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="57"/>
+      <c r="U13" s="57"/>
+      <c r="V13" s="57"/>
+      <c r="W13" s="57"/>
+      <c r="X13" s="57"/>
+      <c r="Y13" s="57"/>
+      <c r="Z13" s="57"/>
+    </row>
+    <row r="14" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="62">
+        <f>IF(MONTH($L$7+14)=$L$5,$L$7+14,"")</f>
+        <v>46335</v>
+      </c>
+      <c r="B14" s="62">
+        <f>IF(MONTH($L$7+15)=$L$5,$L$7+15,"")</f>
+        <v>46336</v>
+      </c>
+      <c r="C14" s="62">
+        <f>IF(MONTH($L$7+16)=$L$5,$L$7+16,"")</f>
+        <v>46337</v>
+      </c>
+      <c r="D14" s="62">
+        <f>IF(MONTH($L$7+17)=$L$5,$L$7+17,"")</f>
+        <v>46338</v>
+      </c>
+      <c r="E14" s="62">
+        <f>IF(MONTH($L$7+18)=$L$5,$L$7+18,"")</f>
+        <v>46339</v>
+      </c>
+      <c r="F14" s="62">
+        <f>IF(MONTH($L$7+19)=$L$5,$L$7+19,"")</f>
+        <v>46340</v>
+      </c>
+      <c r="G14" s="62">
+        <f>IF(MONTH($L$7+20)=$L$5,$L$7+20,"")</f>
+        <v>46341</v>
+      </c>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="57"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="57"/>
+      <c r="N14" s="57"/>
+      <c r="O14" s="57"/>
+      <c r="P14" s="57"/>
+      <c r="Q14" s="57"/>
+      <c r="R14" s="57"/>
+      <c r="S14" s="57"/>
+      <c r="T14" s="57"/>
+      <c r="U14" s="57"/>
+      <c r="V14" s="57"/>
+      <c r="W14" s="57"/>
+      <c r="X14" s="57"/>
+      <c r="Y14" s="57"/>
+      <c r="Z14" s="57"/>
+    </row>
+    <row r="15" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="63" t="str">
+        <f>IF(A14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="B15" s="63" t="str">
+        <f>IF(B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C15" s="63" t="str">
+        <f>IF(C14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D15" s="63" t="str">
+        <f>IF(D14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E15" s="63" t="str">
+        <f>IF(E14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F15" s="63" t="str">
+        <f>IF(F14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G15" s="63" t="str">
+        <f>IF(G14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="57"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="57"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="57"/>
+      <c r="U15" s="57"/>
+      <c r="V15" s="57"/>
+      <c r="W15" s="57"/>
+      <c r="X15" s="57"/>
+      <c r="Y15" s="57"/>
+      <c r="Z15" s="57"/>
+    </row>
+    <row r="16" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="64"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="57"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="57"/>
+      <c r="P16" s="57"/>
+      <c r="Q16" s="57"/>
+      <c r="R16" s="57"/>
+      <c r="S16" s="57"/>
+      <c r="T16" s="57"/>
+      <c r="U16" s="57"/>
+      <c r="V16" s="57"/>
+      <c r="W16" s="57"/>
+      <c r="X16" s="57"/>
+      <c r="Y16" s="57"/>
+      <c r="Z16" s="57"/>
+    </row>
+    <row r="17" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="65"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="57"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="57"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="57"/>
+      <c r="W17" s="57"/>
+      <c r="X17" s="57"/>
+      <c r="Y17" s="57"/>
+      <c r="Z17" s="57"/>
+    </row>
+    <row r="18" spans="1:26" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="67"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="K18" s="57"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="57"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="57"/>
+      <c r="U18" s="57"/>
+      <c r="V18" s="57"/>
+      <c r="W18" s="57"/>
+      <c r="X18" s="57"/>
+      <c r="Y18" s="57"/>
+      <c r="Z18" s="57"/>
+    </row>
+    <row r="19" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="62">
+        <f>IF(MONTH($L$7+21)=$L$5,$L$7+21,"")</f>
+        <v>46342</v>
+      </c>
+      <c r="B19" s="62">
+        <f>IF(MONTH($L$7+22)=$L$5,$L$7+22,"")</f>
+        <v>46343</v>
+      </c>
+      <c r="C19" s="62">
+        <f>IF(MONTH($L$7+23)=$L$5,$L$7+23,"")</f>
+        <v>46344</v>
+      </c>
+      <c r="D19" s="62">
+        <f>IF(MONTH($L$7+24)=$L$5,$L$7+24,"")</f>
+        <v>46345</v>
+      </c>
+      <c r="E19" s="62">
+        <f>IF(MONTH($L$7+25)=$L$5,$L$7+25,"")</f>
+        <v>46346</v>
+      </c>
+      <c r="F19" s="62">
+        <f>IF(MONTH($L$7+26)=$L$5,$L$7+26,"")</f>
+        <v>46347</v>
+      </c>
+      <c r="G19" s="62">
+        <f>IF(MONTH($L$7+27)=$L$5,$L$7+27,"")</f>
+        <v>46348</v>
+      </c>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="57"/>
+      <c r="O19" s="57"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+      <c r="T19" s="57"/>
+      <c r="U19" s="57"/>
+      <c r="V19" s="57"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="57"/>
+      <c r="Y19" s="57"/>
+      <c r="Z19" s="57"/>
+    </row>
+    <row r="20" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="63" t="str">
+        <f>IF(A19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="B20" s="63" t="str">
+        <f>IF(B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</v>
+      </c>
+      <c r="C20" s="63" t="str">
+        <f>IF(C19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D20" s="63" t="str">
+        <f>IF(D19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E20" s="63" t="str">
+        <f>IF(E19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F20" s="63" t="str">
+        <f>IF(F19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G20" s="63" t="str">
+        <f>IF(G19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="57"/>
+      <c r="O20" s="57"/>
+      <c r="P20" s="57"/>
+      <c r="Q20" s="57"/>
+      <c r="R20" s="57"/>
+      <c r="S20" s="57"/>
+      <c r="T20" s="57"/>
+      <c r="U20" s="57"/>
+      <c r="V20" s="57"/>
+      <c r="W20" s="57"/>
+      <c r="X20" s="57"/>
+      <c r="Y20" s="57"/>
+      <c r="Z20" s="57"/>
+    </row>
+    <row r="21" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="64"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="57"/>
+      <c r="V21" s="57"/>
+      <c r="W21" s="57"/>
+      <c r="X21" s="57"/>
+      <c r="Y21" s="57"/>
+      <c r="Z21" s="57"/>
+    </row>
+    <row r="22" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="65"/>
+      <c r="B22" s="65"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="57"/>
+      <c r="O22" s="57"/>
+      <c r="P22" s="57"/>
+      <c r="Q22" s="57"/>
+      <c r="R22" s="57"/>
+      <c r="S22" s="57"/>
+      <c r="T22" s="57"/>
+      <c r="U22" s="57"/>
+      <c r="V22" s="57"/>
+      <c r="W22" s="57"/>
+      <c r="X22" s="57"/>
+      <c r="Y22" s="57"/>
+      <c r="Z22" s="57"/>
+    </row>
+    <row r="23" spans="1:26" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="67"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
+      <c r="O23" s="57"/>
+      <c r="P23" s="57"/>
+      <c r="Q23" s="57"/>
+      <c r="R23" s="57"/>
+      <c r="S23" s="57"/>
+      <c r="T23" s="57"/>
+      <c r="U23" s="57"/>
+      <c r="V23" s="57"/>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
+      <c r="Y23" s="57"/>
+      <c r="Z23" s="57"/>
+    </row>
+    <row r="24" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="62">
+        <f>IF(MONTH($L$7+28)=$L$5,$L$7+28,"")</f>
+        <v>46349</v>
+      </c>
+      <c r="B24" s="62">
+        <f>IF(MONTH($L$7+29)=$L$5,$L$7+29,"")</f>
+        <v>46350</v>
+      </c>
+      <c r="C24" s="62">
+        <f>IF(MONTH($L$7+30)=$L$5,$L$7+30,"")</f>
+        <v>46351</v>
+      </c>
+      <c r="D24" s="62">
+        <f>IF(MONTH($L$7+31)=$L$5,$L$7+31,"")</f>
+        <v>46352</v>
+      </c>
+      <c r="E24" s="62">
+        <f>IF(MONTH($L$7+32)=$L$5,$L$7+32,"")</f>
+        <v>46353</v>
+      </c>
+      <c r="F24" s="62">
+        <f>IF(MONTH($L$7+33)=$L$5,$L$7+33,"")</f>
+        <v>46354</v>
+      </c>
+      <c r="G24" s="62">
+        <f>IF(MONTH($L$7+34)=$L$5,$L$7+34,"")</f>
+        <v>46355</v>
+      </c>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="57"/>
+      <c r="P24" s="57"/>
+      <c r="Q24" s="57"/>
+      <c r="R24" s="57"/>
+      <c r="S24" s="57"/>
+      <c r="T24" s="57"/>
+      <c r="U24" s="57"/>
+      <c r="V24" s="57"/>
+      <c r="W24" s="57"/>
+      <c r="X24" s="57"/>
+      <c r="Y24" s="57"/>
+      <c r="Z24" s="57"/>
+    </row>
+    <row r="25" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="63" t="str">
+        <f>IF(A24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="B25" s="63" t="str">
+        <f>IF(B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C25" s="63" t="str">
+        <f>IF(C24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D25" s="63" t="str">
+        <f>IF(D24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E25" s="63" t="str">
+        <f>IF(E24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F25" s="63" t="str">
+        <f>IF(F24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G25" s="63" t="str">
+        <f>IF(G24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="57"/>
+      <c r="P25" s="57"/>
+      <c r="Q25" s="57"/>
+      <c r="R25" s="57"/>
+      <c r="S25" s="57"/>
+      <c r="T25" s="57"/>
+      <c r="U25" s="57"/>
+      <c r="V25" s="57"/>
+      <c r="W25" s="57"/>
+      <c r="X25" s="57"/>
+      <c r="Y25" s="57"/>
+      <c r="Z25" s="57"/>
+    </row>
+    <row r="26" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="64"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="57"/>
+      <c r="Q26" s="57"/>
+      <c r="R26" s="57"/>
+      <c r="S26" s="57"/>
+      <c r="T26" s="57"/>
+      <c r="U26" s="57"/>
+      <c r="V26" s="57"/>
+      <c r="W26" s="57"/>
+      <c r="X26" s="57"/>
+      <c r="Y26" s="57"/>
+      <c r="Z26" s="57"/>
+    </row>
+    <row r="27" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="65"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="72"/>
+      <c r="G27" s="72"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="57"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="57"/>
+      <c r="P27" s="57"/>
+      <c r="Q27" s="57"/>
+      <c r="R27" s="57"/>
+      <c r="S27" s="57"/>
+      <c r="T27" s="57"/>
+      <c r="U27" s="57"/>
+      <c r="V27" s="57"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="57"/>
+      <c r="Y27" s="57"/>
+      <c r="Z27" s="57"/>
+    </row>
+    <row r="28" spans="1:26" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="67"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="57"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="57"/>
+      <c r="P28" s="57"/>
+      <c r="Q28" s="57"/>
+      <c r="R28" s="57"/>
+      <c r="S28" s="57"/>
+      <c r="T28" s="57"/>
+      <c r="U28" s="57"/>
+      <c r="V28" s="57"/>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
+      <c r="Y28" s="57"/>
+      <c r="Z28" s="57"/>
+    </row>
+    <row r="29" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="62">
+        <f>IF(MONTH($L$7+35)=$L$5,$L$7+35,"")</f>
+        <v>46356</v>
+      </c>
+      <c r="B29" s="62" t="str">
+        <f>IF(MONTH($L$7+36)=$L$5,$L$7+36,"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="62" t="str">
+        <f>IF(MONTH($L$7+37)=$L$5,$L$7+37,"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="62" t="str">
+        <f>IF(MONTH($L$7+38)=$L$5,$L$7+38,"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="62" t="str">
+        <f>IF(MONTH($L$7+39)=$L$5,$L$7+39,"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="62" t="str">
+        <f>IF(MONTH($L$7+40)=$L$5,$L$7+40,"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="62" t="str">
+        <f>IF(MONTH($L$7+41)=$L$5,$L$7+41,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="57"/>
+      <c r="Q29" s="57"/>
+      <c r="R29" s="57"/>
+      <c r="S29" s="57"/>
+      <c r="T29" s="57"/>
+      <c r="U29" s="57"/>
+      <c r="V29" s="57"/>
+      <c r="W29" s="57"/>
+      <c r="X29" s="57"/>
+      <c r="Y29" s="57"/>
+      <c r="Z29" s="57"/>
+    </row>
+    <row r="30" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="63" t="str">
+        <f>IF(A29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(A29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v>09:00-12.30  Μουσείο Μακεδονικού Αγώνα</v>
+      </c>
+      <c r="B30" s="63" t="str">
+        <f>IF(B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C30" s="63" t="str">
+        <f>IF(C29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(C29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D30" s="63" t="str">
+        <f>IF(D29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(D29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E30" s="63" t="str">
+        <f>IF(E29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(E29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F30" s="63" t="str">
+        <f>IF(F29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(F29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G30" s="63" t="str">
+        <f>IF(G29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH(G29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="57"/>
+      <c r="V30" s="57"/>
+      <c r="W30" s="57"/>
+      <c r="X30" s="57"/>
+      <c r="Y30" s="57"/>
+      <c r="Z30" s="57"/>
+    </row>
+    <row r="31" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="64"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="64"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="57"/>
+      <c r="L31" s="57"/>
+      <c r="M31" s="57"/>
+      <c r="N31" s="57"/>
+      <c r="O31" s="57"/>
+      <c r="P31" s="57"/>
+      <c r="Q31" s="57"/>
+      <c r="R31" s="57"/>
+      <c r="S31" s="57"/>
+      <c r="T31" s="57"/>
+      <c r="U31" s="57"/>
+      <c r="V31" s="57"/>
+      <c r="W31" s="57"/>
+      <c r="X31" s="57"/>
+      <c r="Y31" s="57"/>
+      <c r="Z31" s="57"/>
+    </row>
+    <row r="32" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="65"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="57"/>
+      <c r="L32" s="57"/>
+      <c r="M32" s="57"/>
+      <c r="N32" s="57"/>
+      <c r="O32" s="57"/>
+      <c r="P32" s="57"/>
+      <c r="Q32" s="57"/>
+      <c r="R32" s="57"/>
+      <c r="S32" s="57"/>
+      <c r="T32" s="57"/>
+      <c r="U32" s="57"/>
+      <c r="V32" s="57"/>
+      <c r="W32" s="57"/>
+      <c r="X32" s="57"/>
+      <c r="Y32" s="57"/>
+      <c r="Z32" s="57"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="66"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="74"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="57"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="57"/>
+      <c r="N33" s="57"/>
+      <c r="O33" s="57"/>
+      <c r="P33" s="57"/>
+      <c r="Q33" s="57"/>
+      <c r="R33" s="57"/>
+      <c r="S33" s="57"/>
+      <c r="T33" s="57"/>
+      <c r="U33" s="57"/>
+      <c r="V33" s="57"/>
+      <c r="W33" s="57"/>
+      <c r="X33" s="57"/>
+      <c r="Y33" s="57"/>
+      <c r="Z33" s="57"/>
+    </row>
+    <row r="34" spans="1:26" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="57"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="57"/>
+      <c r="N34" s="57"/>
+      <c r="O34" s="57"/>
+      <c r="P34" s="57"/>
+      <c r="Q34" s="57"/>
+      <c r="R34" s="57"/>
+      <c r="S34" s="57"/>
+      <c r="T34" s="57"/>
+      <c r="U34" s="57"/>
+      <c r="V34" s="57"/>
+      <c r="W34" s="57"/>
+      <c r="X34" s="57"/>
+      <c r="Y34" s="57"/>
+      <c r="Z34" s="57"/>
+    </row>
+    <row r="35" spans="1:26" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="57"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="57"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="57"/>
+      <c r="N35" s="57"/>
+      <c r="O35" s="57"/>
+      <c r="P35" s="57"/>
+      <c r="Q35" s="57"/>
+      <c r="R35" s="57"/>
+      <c r="S35" s="57"/>
+      <c r="T35" s="57"/>
+      <c r="U35" s="57"/>
+      <c r="V35" s="57"/>
+      <c r="W35" s="57"/>
+      <c r="X35" s="57"/>
+      <c r="Y35" s="57"/>
+      <c r="Z35" s="57"/>
+    </row>
+    <row r="36" spans="1:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="75" t="str">
+        <f>ΚΑΤΗΓΟΡΙΕΣ!$A$2</f>
+        <v>Αργία / Διακοπές</v>
+      </c>
+      <c r="B36" s="76" t="str">
+        <f>ΚΑΤΗΓΟΡΙΕΣ!$A$3</f>
+        <v>Εορτή / Εκκλησιασμός</v>
+      </c>
+      <c r="C36" s="77" t="str">
+        <f>ΚΑΤΗΓΟΡΙΕΣ!$A$4</f>
+        <v>Εκδρομή / Επίσκεψη / Περίπατος</v>
+      </c>
+      <c r="D36" s="81" t="str">
+        <f>ΚΑΤΗΓΟΡΙΕΣ!$A$5</f>
+        <v>Σύλλογος διδασκόντων</v>
+      </c>
+      <c r="E36" s="83"/>
+      <c r="F36" s="84"/>
+      <c r="G36" s="85"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="57"/>
+      <c r="O36" s="57"/>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="57"/>
+      <c r="R36" s="57"/>
+      <c r="S36" s="57"/>
+      <c r="T36" s="57"/>
+      <c r="U36" s="57"/>
+      <c r="V36" s="57"/>
+      <c r="W36" s="57"/>
+      <c r="X36" s="57"/>
+      <c r="Y36" s="57"/>
+      <c r="Z36" s="57"/>
+    </row>
+    <row r="37" spans="1:26" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="78" t="str">
+        <f>ΚΑΤΗΓΟΡΙΕΣ!$A$6</f>
+        <v>Ενημέρωση γονέων / Έλεγχοι</v>
+      </c>
+      <c r="B37" s="79" t="str">
+        <f>ΚΑΤΗΓΟΡΙΕΣ!$A$7</f>
+        <v>Ορόσημο / Εξετάσεις</v>
+      </c>
+      <c r="C37" s="80" t="str">
+        <f>ΚΑΤΗΓΟΡΙΕΣ!$A$8</f>
+        <v>Επιμόρφωση εκπαιδευτικών</v>
+      </c>
+      <c r="D37" s="82" t="str">
+        <f>ΚΑΤΗΓΟΡΙΕΣ!$A$9</f>
+        <v>Δράση / Πρόγραμμα / Όμιλος</v>
+      </c>
+      <c r="E37" s="86"/>
+      <c r="F37" s="87"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="57"/>
+      <c r="W37" s="57"/>
+      <c r="X37" s="57"/>
+      <c r="Y37" s="57"/>
+      <c r="Z37" s="57"/>
+    </row>
+    <row r="38" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="57"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="57"/>
+      <c r="S38" s="57"/>
+      <c r="T38" s="57"/>
+      <c r="U38" s="57"/>
+      <c r="V38" s="57"/>
+      <c r="W38" s="57"/>
+      <c r="X38" s="57"/>
+      <c r="Y38" s="57"/>
+      <c r="Z38" s="57"/>
+    </row>
+    <row r="39" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="57"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="57"/>
+      <c r="S39" s="57"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="57"/>
+      <c r="V39" s="57"/>
+      <c r="W39" s="57"/>
+      <c r="X39" s="57"/>
+      <c r="Y39" s="57"/>
+      <c r="Z39" s="57"/>
+    </row>
+    <row r="40" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="57"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="57"/>
+      <c r="P40" s="57"/>
+      <c r="Q40" s="57"/>
+      <c r="R40" s="57"/>
+      <c r="S40" s="57"/>
+      <c r="T40" s="57"/>
+      <c r="U40" s="57"/>
+      <c r="V40" s="57"/>
+      <c r="W40" s="57"/>
+      <c r="X40" s="57"/>
+      <c r="Y40" s="57"/>
+      <c r="Z40" s="57"/>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="57"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="57"/>
+      <c r="O41" s="57"/>
+      <c r="P41" s="57"/>
+      <c r="Q41" s="57"/>
+      <c r="R41" s="57"/>
+      <c r="S41" s="57"/>
+      <c r="T41" s="57"/>
+      <c r="U41" s="57"/>
+      <c r="V41" s="57"/>
+      <c r="W41" s="57"/>
+      <c r="X41" s="57"/>
+      <c r="Y41" s="57"/>
+      <c r="Z41" s="57"/>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="57"/>
+      <c r="O42" s="57"/>
+      <c r="P42" s="57"/>
+      <c r="Q42" s="57"/>
+      <c r="R42" s="57"/>
+      <c r="S42" s="57"/>
+      <c r="T42" s="57"/>
+      <c r="U42" s="57"/>
+      <c r="V42" s="57"/>
+      <c r="W42" s="57"/>
+      <c r="X42" s="57"/>
+      <c r="Y42" s="57"/>
+      <c r="Z42" s="57"/>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A43" s="57"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="57"/>
+      <c r="P43" s="57"/>
+      <c r="Q43" s="57"/>
+      <c r="R43" s="57"/>
+      <c r="S43" s="57"/>
+      <c r="T43" s="57"/>
+      <c r="U43" s="57"/>
+      <c r="V43" s="57"/>
+      <c r="W43" s="57"/>
+      <c r="X43" s="57"/>
+      <c r="Y43" s="57"/>
+      <c r="Z43" s="57"/>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A44" s="57"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="57"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="57"/>
+      <c r="O44" s="57"/>
+      <c r="P44" s="57"/>
+      <c r="Q44" s="57"/>
+      <c r="R44" s="57"/>
+      <c r="S44" s="57"/>
+      <c r="T44" s="57"/>
+      <c r="U44" s="57"/>
+      <c r="V44" s="57"/>
+      <c r="W44" s="57"/>
+      <c r="X44" s="57"/>
+      <c r="Y44" s="57"/>
+      <c r="Z44" s="57"/>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="57"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="57"/>
+      <c r="P45" s="57"/>
+      <c r="Q45" s="57"/>
+      <c r="R45" s="57"/>
+      <c r="S45" s="57"/>
+      <c r="T45" s="57"/>
+      <c r="U45" s="57"/>
+      <c r="V45" s="57"/>
+      <c r="W45" s="57"/>
+      <c r="X45" s="57"/>
+      <c r="Y45" s="57"/>
+      <c r="Z45" s="57"/>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="57"/>
+      <c r="L46" s="57"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="57"/>
+      <c r="O46" s="57"/>
+      <c r="P46" s="57"/>
+      <c r="Q46" s="57"/>
+      <c r="R46" s="57"/>
+      <c r="S46" s="57"/>
+      <c r="T46" s="57"/>
+      <c r="U46" s="57"/>
+      <c r="V46" s="57"/>
+      <c r="W46" s="57"/>
+      <c r="X46" s="57"/>
+      <c r="Y46" s="57"/>
+      <c r="Z46" s="57"/>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="57"/>
+      <c r="L47" s="57"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="57"/>
+      <c r="O47" s="57"/>
+      <c r="P47" s="57"/>
+      <c r="Q47" s="57"/>
+      <c r="R47" s="57"/>
+      <c r="S47" s="57"/>
+      <c r="T47" s="57"/>
+      <c r="U47" s="57"/>
+      <c r="V47" s="57"/>
+      <c r="W47" s="57"/>
+      <c r="X47" s="57"/>
+      <c r="Y47" s="57"/>
+      <c r="Z47" s="57"/>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="57"/>
+      <c r="L48" s="57"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="57"/>
+      <c r="O48" s="57"/>
+      <c r="P48" s="57"/>
+      <c r="Q48" s="57"/>
+      <c r="R48" s="57"/>
+      <c r="S48" s="57"/>
+      <c r="T48" s="57"/>
+      <c r="U48" s="57"/>
+      <c r="V48" s="57"/>
+      <c r="W48" s="57"/>
+      <c r="X48" s="57"/>
+      <c r="Y48" s="57"/>
+      <c r="Z48" s="57"/>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A49" s="57"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="57"/>
+      <c r="K49" s="57"/>
+      <c r="L49" s="57"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="57"/>
+      <c r="O49" s="57"/>
+      <c r="P49" s="57"/>
+      <c r="Q49" s="57"/>
+      <c r="R49" s="57"/>
+      <c r="S49" s="57"/>
+      <c r="T49" s="57"/>
+      <c r="U49" s="57"/>
+      <c r="V49" s="57"/>
+      <c r="W49" s="57"/>
+      <c r="X49" s="57"/>
+      <c r="Y49" s="57"/>
+      <c r="Z49" s="57"/>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A50" s="57"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="57"/>
+      <c r="J50" s="57"/>
+      <c r="K50" s="57"/>
+      <c r="L50" s="57"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="57"/>
+      <c r="O50" s="57"/>
+      <c r="P50" s="57"/>
+      <c r="Q50" s="57"/>
+      <c r="R50" s="57"/>
+      <c r="S50" s="57"/>
+      <c r="T50" s="57"/>
+      <c r="U50" s="57"/>
+      <c r="V50" s="57"/>
+      <c r="W50" s="57"/>
+      <c r="X50" s="57"/>
+      <c r="Y50" s="57"/>
+      <c r="Z50" s="57"/>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A51" s="57"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="57"/>
+      <c r="L51" s="57"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="57"/>
+      <c r="O51" s="57"/>
+      <c r="P51" s="57"/>
+      <c r="Q51" s="57"/>
+      <c r="R51" s="57"/>
+      <c r="S51" s="57"/>
+      <c r="T51" s="57"/>
+      <c r="U51" s="57"/>
+      <c r="V51" s="57"/>
+      <c r="W51" s="57"/>
+      <c r="X51" s="57"/>
+      <c r="Y51" s="57"/>
+      <c r="Z51" s="57"/>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A52" s="57"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="57"/>
+      <c r="K52" s="57"/>
+      <c r="L52" s="57"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="57"/>
+      <c r="O52" s="57"/>
+      <c r="P52" s="57"/>
+      <c r="Q52" s="57"/>
+      <c r="R52" s="57"/>
+      <c r="S52" s="57"/>
+      <c r="T52" s="57"/>
+      <c r="U52" s="57"/>
+      <c r="V52" s="57"/>
+      <c r="W52" s="57"/>
+      <c r="X52" s="57"/>
+      <c r="Y52" s="57"/>
+      <c r="Z52" s="57"/>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A53" s="57"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="57"/>
+      <c r="K53" s="57"/>
+      <c r="L53" s="57"/>
+      <c r="M53" s="57"/>
+      <c r="N53" s="57"/>
+      <c r="O53" s="57"/>
+      <c r="P53" s="57"/>
+      <c r="Q53" s="57"/>
+      <c r="R53" s="57"/>
+      <c r="S53" s="57"/>
+      <c r="T53" s="57"/>
+      <c r="U53" s="57"/>
+      <c r="V53" s="57"/>
+      <c r="W53" s="57"/>
+      <c r="X53" s="57"/>
+      <c r="Y53" s="57"/>
+      <c r="Z53" s="57"/>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A54" s="57"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="57"/>
+      <c r="I54" s="57"/>
+      <c r="J54" s="57"/>
+      <c r="K54" s="57"/>
+      <c r="L54" s="57"/>
+      <c r="M54" s="57"/>
+      <c r="N54" s="57"/>
+      <c r="O54" s="57"/>
+      <c r="P54" s="57"/>
+      <c r="Q54" s="57"/>
+      <c r="R54" s="57"/>
+      <c r="S54" s="57"/>
+      <c r="T54" s="57"/>
+      <c r="U54" s="57"/>
+      <c r="V54" s="57"/>
+      <c r="W54" s="57"/>
+      <c r="X54" s="57"/>
+      <c r="Y54" s="57"/>
+      <c r="Z54" s="57"/>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A55" s="57"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="57"/>
+      <c r="L55" s="57"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="57"/>
+      <c r="O55" s="57"/>
+      <c r="P55" s="57"/>
+      <c r="Q55" s="57"/>
+      <c r="R55" s="57"/>
+      <c r="S55" s="57"/>
+      <c r="T55" s="57"/>
+      <c r="U55" s="57"/>
+      <c r="V55" s="57"/>
+      <c r="W55" s="57"/>
+      <c r="X55" s="57"/>
+      <c r="Y55" s="57"/>
+      <c r="Z55" s="57"/>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A56" s="57"/>
+      <c r="B56" s="57"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="57"/>
+      <c r="J56" s="57"/>
+      <c r="K56" s="57"/>
+      <c r="L56" s="57"/>
+      <c r="M56" s="57"/>
+      <c r="N56" s="57"/>
+      <c r="O56" s="57"/>
+      <c r="P56" s="57"/>
+      <c r="Q56" s="57"/>
+      <c r="R56" s="57"/>
+      <c r="S56" s="57"/>
+      <c r="T56" s="57"/>
+      <c r="U56" s="57"/>
+      <c r="V56" s="57"/>
+      <c r="W56" s="57"/>
+      <c r="X56" s="57"/>
+      <c r="Y56" s="57"/>
+      <c r="Z56" s="57"/>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A57" s="57"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57"/>
+      <c r="I57" s="57"/>
+      <c r="J57" s="57"/>
+      <c r="K57" s="57"/>
+      <c r="L57" s="57"/>
+      <c r="M57" s="57"/>
+      <c r="N57" s="57"/>
+      <c r="O57" s="57"/>
+      <c r="P57" s="57"/>
+      <c r="Q57" s="57"/>
+      <c r="R57" s="57"/>
+      <c r="S57" s="57"/>
+      <c r="T57" s="57"/>
+      <c r="U57" s="57"/>
+      <c r="V57" s="57"/>
+      <c r="W57" s="57"/>
+      <c r="X57" s="57"/>
+      <c r="Y57" s="57"/>
+      <c r="Z57" s="57"/>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A58" s="57"/>
+      <c r="B58" s="57"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="57"/>
+      <c r="J58" s="57"/>
+      <c r="K58" s="57"/>
+      <c r="L58" s="57"/>
+      <c r="M58" s="57"/>
+      <c r="N58" s="57"/>
+      <c r="O58" s="57"/>
+      <c r="P58" s="57"/>
+      <c r="Q58" s="57"/>
+      <c r="R58" s="57"/>
+      <c r="S58" s="57"/>
+      <c r="T58" s="57"/>
+      <c r="U58" s="57"/>
+      <c r="V58" s="57"/>
+      <c r="W58" s="57"/>
+      <c r="X58" s="57"/>
+      <c r="Y58" s="57"/>
+      <c r="Z58" s="57"/>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A59" s="57"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="57"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="57"/>
+      <c r="I59" s="57"/>
+      <c r="J59" s="57"/>
+      <c r="K59" s="57"/>
+      <c r="L59" s="57"/>
+      <c r="M59" s="57"/>
+      <c r="N59" s="57"/>
+      <c r="O59" s="57"/>
+      <c r="P59" s="57"/>
+      <c r="Q59" s="57"/>
+      <c r="R59" s="57"/>
+      <c r="S59" s="57"/>
+      <c r="T59" s="57"/>
+      <c r="U59" s="57"/>
+      <c r="V59" s="57"/>
+      <c r="W59" s="57"/>
+      <c r="X59" s="57"/>
+      <c r="Y59" s="57"/>
+      <c r="Z59" s="57"/>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A60" s="57"/>
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="57"/>
+      <c r="K60" s="57"/>
+      <c r="L60" s="57"/>
+      <c r="M60" s="57"/>
+      <c r="N60" s="57"/>
+      <c r="O60" s="57"/>
+      <c r="P60" s="57"/>
+      <c r="Q60" s="57"/>
+      <c r="R60" s="57"/>
+      <c r="S60" s="57"/>
+      <c r="T60" s="57"/>
+      <c r="U60" s="57"/>
+      <c r="V60" s="57"/>
+      <c r="W60" s="57"/>
+      <c r="X60" s="57"/>
+      <c r="Y60" s="57"/>
+      <c r="Z60" s="57"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A4:G33">
+    <cfRule type="expression" dxfId="1" priority="48">
+      <formula>INDEX($A$1:$G$40,4+5*INT((ROW()-4)/5),COLUMN())=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2" xr:uid="{B636D5C0-CF2C-467A-B6BC-D854A78311B2}">
+      <formula1>$N$2:$N$11</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0.1388888888888889" footer="0.1388888888888889"/>
+  <pageSetup paperSize="8" scale="87" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;L3ο ΓΥΜΝΑΣΙΟ ΠΟΛΙΧΝΗΣ&amp;R&amp;D</oddFooter>
+  </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="40" id="{B3EF608C-E088-471A-A03D-4F1AAC7878B1}">
+            <xm:f>AND(MOD(ROW()-4,5)&lt;2,IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH(INDEX($A$1:$G$40,4+5*INT((ROW()-4)/5),COLUMN())&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")="Αργία / Διακοπές")</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="64"/>
+                  <bgColor rgb="FFF4B6B6"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="41" id="{C988E767-8D68-4263-8E7C-48CDEF0F61FA}">
+            <xm:f>AND(MOD(ROW()-4,5)&lt;2,IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH(INDEX($A$1:$G$40,4+5*INT((ROW()-4)/5),COLUMN())&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")="Εορτή / Εκκλησιασμός")</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="64"/>
+                  <bgColor rgb="FFFFE08A"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="42" id="{4B5095F0-BDBC-40B9-A1E4-3D37412393A3}">
+            <xm:f>AND(MOD(ROW()-4,5)&lt;2,IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH(INDEX($A$1:$G$40,4+5*INT((ROW()-4)/5),COLUMN())&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")="Εκδρομή / Επίσκεψη / Περίπατος")</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="64"/>
+                  <bgColor rgb="FFB7DE9C"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="43" id="{AECF0E27-2D69-465C-90ED-E3DED4919BA0}">
+            <xm:f>AND(MOD(ROW()-4,5)&lt;2,IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH(INDEX($A$1:$G$40,4+5*INT((ROW()-4)/5),COLUMN())&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")="Σύλλογος διδασκόντων")</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="64"/>
+                  <bgColor rgb="FFD0CECE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="44" id="{7D09B08E-1FEB-439D-81F9-55F8F11993C2}">
+            <xm:f>AND(MOD(ROW()-4,5)&lt;2,IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH(INDEX($A$1:$G$40,4+5*INT((ROW()-4)/5),COLUMN())&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")="Ενημέρωση γονέων / Έλεγχοι")</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="64"/>
+                  <bgColor rgb="FFF9C08A"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="45" id="{450C170E-AD0C-4D77-B6F9-CCB55D1C5AE2}">
+            <xm:f>AND(MOD(ROW()-4,5)&lt;2,IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH(INDEX($A$1:$G$40,4+5*INT((ROW()-4)/5),COLUMN())&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")="Ορόσημο / Εξετάσεις")</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="64"/>
+                  <bgColor rgb="FFA9CDEB"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="46" id="{14C7C226-D7F4-4EF2-85F7-55F6ABD09DDD}">
+            <xm:f>AND(MOD(ROW()-4,5)&lt;2,IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH(INDEX($A$1:$G$40,4+5*INT((ROW()-4)/5),COLUMN())&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")="Επιμόρφωση εκπαιδευτικών")</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="64"/>
+                  <bgColor rgb="FF9FD8CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="47" id="{8B64F24B-C07F-4B38-8884-DF72FDD4D37A}">
+            <xm:f>AND(MOD(ROW()-4,5)&lt;2,IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH(INDEX($A$1:$G$40,4+5*INT((ROW()-4)/5),COLUMN())&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")="Δράση / Πρόγραμμα / Όμιλος")</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor indexed="64"/>
+                  <bgColor rgb="FFC4B5DC"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A4:G33</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0914995-AB9B-4AD7-9331-7E6E9854CA91}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11618,42 +14152,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
       <c r="F1" s="36" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G1" s="34"/>
       <c r="I1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K1" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="65" t="str">
+      <c r="A2" s="97" t="str">
         <f>$G$2&amp;" "&amp;$G$6</f>
         <v>ΝΟΕΜΒΡΙΟΣ 2026</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
       <c r="F2" s="34" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G2" s="39" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J2">
         <v>9</v>
@@ -11664,21 +14198,21 @@
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F3" s="34"/>
       <c r="G3" s="34"/>
       <c r="I3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J3">
         <v>10</v>
@@ -11697,17 +14231,17 @@
         <v>46327</v>
       </c>
       <c r="C4" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="28" t="str">
-        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B4="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B4&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F4" s="34"/>
       <c r="G4" s="34"/>
       <c r="I4" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J4">
         <v>11</v>
@@ -11726,22 +14260,22 @@
         <v>46328</v>
       </c>
       <c r="C5" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="28" t="str">
-        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B5="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B5&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F5" s="34" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G5" s="34">
         <f>INDEX($J$2:$J$11,MATCH($G$2,$I$2:$I$11,0))</f>
         <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="J5">
         <v>12</v>
@@ -11760,22 +14294,22 @@
         <v>46329</v>
       </c>
       <c r="C6" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="28" t="str">
-        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B6="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B6&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F6" s="34" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G6" s="34">
         <f>ΟΔΗΓΙΕΣ!$B$3+INDEX($K$2:$K$11,MATCH($G$2,$I$2:$I$11,0))</f>
         <v>2026</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -11784,7 +14318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Τετ</v>
@@ -11794,17 +14328,17 @@
         <v>46330</v>
       </c>
       <c r="C7" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
-        <v>Δράση</v>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <v>Δράση / Πρόγραμμα / Όμιλος</v>
       </c>
       <c r="D7" s="28" t="str">
-        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
-        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</v>
+        <f>IF($B7="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B7&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v>08:45-11:15  Διαδικτυακή εκπαίδευση «Kids Save Lives»</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="34"/>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -11823,17 +14357,17 @@
         <v>46331</v>
       </c>
       <c r="C8" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="28" t="str">
-        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B8="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B8&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
       <c r="I8" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J8">
         <v>3</v>
@@ -11852,15 +14386,15 @@
         <v>46332</v>
       </c>
       <c r="C9" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="28" t="str">
-        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B9="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B9&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="I9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -11879,15 +14413,15 @@
         <v>46333</v>
       </c>
       <c r="C10" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="28" t="str">
-        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B10="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B10&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="I10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -11906,15 +14440,15 @@
         <v>46334</v>
       </c>
       <c r="C11" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="28" t="str">
-        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B11="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B11&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
       <c r="I11" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -11933,11 +14467,11 @@
         <v>46335</v>
       </c>
       <c r="C12" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="28" t="str">
-        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B12="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B12&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11951,11 +14485,11 @@
         <v>46336</v>
       </c>
       <c r="C13" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="28" t="str">
-        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B13="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B13&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11969,11 +14503,11 @@
         <v>46337</v>
       </c>
       <c r="C14" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="28" t="str">
-        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B14="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B14&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -11987,11 +14521,11 @@
         <v>46338</v>
       </c>
       <c r="C15" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="28" t="str">
-        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B15="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B15&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12005,11 +14539,11 @@
         <v>46339</v>
       </c>
       <c r="C16" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="28" t="str">
-        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B16="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B16&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12023,11 +14557,11 @@
         <v>46340</v>
       </c>
       <c r="C17" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="28" t="str">
-        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B17="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B17&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12041,11 +14575,11 @@
         <v>46341</v>
       </c>
       <c r="C18" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="28" t="str">
-        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B18="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B18&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12059,11 +14593,11 @@
         <v>46342</v>
       </c>
       <c r="C19" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="28" t="str">
-        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B19="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B19&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12077,11 +14611,11 @@
         <v>46343</v>
       </c>
       <c r="C20" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v>Εορτή / Εκκλησιασμός</v>
       </c>
       <c r="D20" s="28" t="str">
-        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B20="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B20&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</v>
       </c>
     </row>
@@ -12095,11 +14629,11 @@
         <v>46344</v>
       </c>
       <c r="C21" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="28" t="str">
-        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B21="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B21&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12113,11 +14647,11 @@
         <v>46345</v>
       </c>
       <c r="C22" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="28" t="str">
-        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B22="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B22&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12131,11 +14665,11 @@
         <v>46346</v>
       </c>
       <c r="C23" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="28" t="str">
-        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B23="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B23&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12149,11 +14683,11 @@
         <v>46347</v>
       </c>
       <c r="C24" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="28" t="str">
-        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B24="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B24&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12167,11 +14701,11 @@
         <v>46348</v>
       </c>
       <c r="C25" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="28" t="str">
-        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B25="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B25&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12185,11 +14719,11 @@
         <v>46349</v>
       </c>
       <c r="C26" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="28" t="str">
-        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B26="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B26&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12203,11 +14737,11 @@
         <v>46350</v>
       </c>
       <c r="C27" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="28" t="str">
-        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B27="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B27&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12221,11 +14755,11 @@
         <v>46351</v>
       </c>
       <c r="C28" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B28="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B28&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12239,11 +14773,11 @@
         <v>46352</v>
       </c>
       <c r="C29" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="28" t="str">
-        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12257,11 +14791,11 @@
         <v>46353</v>
       </c>
       <c r="C30" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="28" t="str">
-        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B30="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B30&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12275,11 +14809,11 @@
         <v>46354</v>
       </c>
       <c r="C31" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="28" t="str">
-        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B31="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B31&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
@@ -12293,15 +14827,15 @@
         <v>46355</v>
       </c>
       <c r="C32" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="28" t="str">
-        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+        <f>IF($B32="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B32&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A33" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Δευ</v>
@@ -12311,12 +14845,12 @@
         <v>46356</v>
       </c>
       <c r="C33" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
-        <v/>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
+        <v>Δράση / Πρόγραμμα / Όμιλος</v>
       </c>
       <c r="D33" s="28" t="str">
-        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
-        <v/>
+        <f>IF($B33="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B33&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
+        <v>09:00-12.30  Μουσείο Μακεδονικού Αγώνα</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -12329,115 +14863,115 @@
         <v/>
       </c>
       <c r="C34" s="27" t="str">
-        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$402,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")</f>
+        <f>IFERROR(INDEX(ΔΡΑΣΕΙΣ!$D$2:$D$399,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="28" t="str">
-        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$402,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$402,0)),""))</f>
+        <f>IF($B34="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B34&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="32"/>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="30"/>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="42"/>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="43"/>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="40"/>
-      <c r="B41" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" s="63"/>
-      <c r="D41" s="63"/>
+      <c r="B41" s="98" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="99"/>
+      <c r="D41" s="99"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="31"/>
-      <c r="B42" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42" s="63"/>
-      <c r="D42" s="63"/>
+      <c r="B42" s="98" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="99"/>
+      <c r="D42" s="99"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="33"/>
-      <c r="B43" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="C43" s="63"/>
-      <c r="D43" s="63"/>
+      <c r="B43" s="98" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="41"/>
-      <c r="B44" s="62" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="62"/>
-      <c r="D44" s="62"/>
+      <c r="B44" s="98" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="98"/>
+      <c r="D44" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B43:D43"/>
     <mergeCell ref="B44:D44"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B42:D42"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B43:D43"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:D34">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>$C4="Αργία / Διακοπές"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>$C4="Εορτή / Εκκλησιασμός"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="16" priority="3">
       <formula>$C4="Εκδρομή / Επίσκεψη / Περίπατος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="15" priority="4">
       <formula>$C4="Σύλλογος διδασκόντων"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="14" priority="5">
       <formula>$C4="Ενημέρωση γονέων / Έλεγχοι"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="13" priority="6">
       <formula>$C4="Ορόσημο / Εξετάσεις"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="7">
-      <formula>$C4="Δράση"</formula>
+    <cfRule type="expression" dxfId="12" priority="7">
+      <formula>$C4="Επιμόρφωση εκπαιδευτικών"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="8">
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>$C4="Δράση / Πρόγραμμα / Όμιλος"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="10" priority="9">
       <formula>IF($B4="",0,WEEKDAY($B4,2)&gt;5)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{9C67FBB8-4BA3-4044-8B9B-0EEB3BDA6399}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{A3E60828-E491-422A-872C-58E61D2442A3}">
       <formula1>$I$2:$I$11</formula1>
     </dataValidation>
   </dataValidations>

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">ΑΦΙΣΑ_ΕΠΙΛΟΓΗΣ!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">ΔΡΑΣΕΙΣ!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -207,7 +207,7 @@
     <t>08:45-11:15</t>
   </si>
   <si>
-    <t>Διαδικτυακή εκπαίδευση «Kids Save Lives»</t>
+    <t>Διαδικτυακή εκπαίδευση «Kids Save Lives» – επιμορφωτική δράση για μαθητές και εκπαιδευτικούς</t>
   </si>
   <si>
     <t>Εκδηλώσεις για την επέτειο του Πολυτεχνείου</t>
@@ -2618,7 +2618,7 @@
         <v>139</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E9" s="21"/>
       <c r="F9" s="21"/>

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="145">
   <si>
     <t>3ο ΓΥΜΝΑΣΙΟ ΠΟΛΙΧΝΗΣ  ·  ΗΜΕΡΟΛΟΓΙΟ ΔΡΑΣΕΩΝ  ·  ΣΧΟΛΙΚΟ ΕΤΟΣ 2026-27</t>
   </si>
@@ -472,6 +472,21 @@
   </si>
   <si>
     <t>Μουσείο Μακεδονικού Αγώνα</t>
+  </si>
+  <si>
+    <t>2η–3η ώρα</t>
+  </si>
+  <si>
+    <t>Επιμορφωτική δράση από «Το Χαμόγελο του Παιδιού»</t>
+  </si>
+  <si>
+    <t>Α1, Α2</t>
+  </si>
+  <si>
+    <t>4η–5η ώρα</t>
+  </si>
+  <si>
+    <t>Α3</t>
   </si>
 </sst>
 </file>
@@ -3124,61 +3139,69 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="19">
-        <v>46503</v>
-      </c>
-      <c r="B28" s="20"/>
+        <v>46493</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>140</v>
+      </c>
       <c r="C28" s="21" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="21"/>
+        <v>32</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>142</v>
+      </c>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
       <c r="H28" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Παρ</v>
       </c>
       <c r="I28" s="23" t="str">
         <f>IF($A28="","",$A28&amp;"#"&amp;COUNTIF($A$2:$A28,$A28))</f>
-        <v>46503#1</v>
+        <v>46493#1</v>
       </c>
       <c r="J28" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Διακοπές Πάσχα</v>
+        <v>2η–3η ώρα  Επιμορφωτική δράση από «Το Χαμόγελο του Παιδιού»  (Α1, Α2)</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="19">
-        <v>46504</v>
-      </c>
-      <c r="B29" s="20"/>
+        <v>46493</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>143</v>
+      </c>
       <c r="C29" s="21" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="21"/>
+        <v>32</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>144</v>
+      </c>
       <c r="F29" s="21"/>
       <c r="G29" s="21"/>
       <c r="H29" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Παρ</v>
       </c>
       <c r="I29" s="23" t="str">
         <f>IF($A29="","",$A29&amp;"#"&amp;COUNTIF($A$2:$A29,$A29))</f>
-        <v>46504#1</v>
+        <v>46493#2</v>
       </c>
       <c r="J29" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Διακοπές Πάσχα</v>
+        <v>4η–5η ώρα  Επιμορφωτική δράση από «Το Χαμόγελο του Παιδιού»  (Α3)</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="19">
-        <v>46505</v>
+        <v>46503</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="21" t="s">
@@ -3192,11 +3215,11 @@
       <c r="G30" s="21"/>
       <c r="H30" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Δευ</v>
       </c>
       <c r="I30" s="23" t="str">
         <f>IF($A30="","",$A30&amp;"#"&amp;COUNTIF($A$2:$A30,$A30))</f>
-        <v>46505#1</v>
+        <v>46503#1</v>
       </c>
       <c r="J30" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3205,7 +3228,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="19">
-        <v>46506</v>
+        <v>46504</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="21" t="s">
@@ -3219,11 +3242,11 @@
       <c r="G31" s="21"/>
       <c r="H31" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Τρί</v>
       </c>
       <c r="I31" s="23" t="str">
         <f>IF($A31="","",$A31&amp;"#"&amp;COUNTIF($A$2:$A31,$A31))</f>
-        <v>46506#1</v>
+        <v>46504#1</v>
       </c>
       <c r="J31" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3232,7 +3255,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="19">
-        <v>46507</v>
+        <v>46505</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="21" t="s">
@@ -3246,11 +3269,11 @@
       <c r="G32" s="21"/>
       <c r="H32" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Τετ</v>
       </c>
       <c r="I32" s="23" t="str">
         <f>IF($A32="","",$A32&amp;"#"&amp;COUNTIF($A$2:$A32,$A32))</f>
-        <v>46507#1</v>
+        <v>46505#1</v>
       </c>
       <c r="J32" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3259,7 +3282,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="19">
-        <v>46510</v>
+        <v>46506</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="21" t="s">
@@ -3273,11 +3296,11 @@
       <c r="G33" s="21"/>
       <c r="H33" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I33" s="23" t="str">
         <f>IF($A33="","",$A33&amp;"#"&amp;COUNTIF($A$2:$A33,$A33))</f>
-        <v>46510#1</v>
+        <v>46506#1</v>
       </c>
       <c r="J33" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3286,7 +3309,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="19">
-        <v>46511</v>
+        <v>46507</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="21" t="s">
@@ -3300,11 +3323,11 @@
       <c r="G34" s="21"/>
       <c r="H34" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Παρ</v>
       </c>
       <c r="I34" s="23" t="str">
         <f>IF($A34="","",$A34&amp;"#"&amp;COUNTIF($A$2:$A34,$A34))</f>
-        <v>46511#1</v>
+        <v>46507#1</v>
       </c>
       <c r="J34" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3313,7 +3336,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="19">
-        <v>46512</v>
+        <v>46510</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="21" t="s">
@@ -3327,11 +3350,11 @@
       <c r="G35" s="21"/>
       <c r="H35" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Δευ</v>
       </c>
       <c r="I35" s="23" t="str">
         <f>IF($A35="","",$A35&amp;"#"&amp;COUNTIF($A$2:$A35,$A35))</f>
-        <v>46512#1</v>
+        <v>46510#1</v>
       </c>
       <c r="J35" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3340,7 +3363,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="19">
-        <v>46513</v>
+        <v>46511</v>
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="21" t="s">
@@ -3354,11 +3377,11 @@
       <c r="G36" s="21"/>
       <c r="H36" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Τρί</v>
       </c>
       <c r="I36" s="23" t="str">
         <f>IF($A36="","",$A36&amp;"#"&amp;COUNTIF($A$2:$A36,$A36))</f>
-        <v>46513#1</v>
+        <v>46511#1</v>
       </c>
       <c r="J36" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3367,7 +3390,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
-        <v>46514</v>
+        <v>46512</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="21" t="s">
@@ -3381,11 +3404,11 @@
       <c r="G37" s="21"/>
       <c r="H37" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Τετ</v>
       </c>
       <c r="I37" s="23" t="str">
         <f>IF($A37="","",$A37&amp;"#"&amp;COUNTIF($A$2:$A37,$A37))</f>
-        <v>46514#1</v>
+        <v>46512#1</v>
       </c>
       <c r="J37" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3394,38 +3417,38 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="19">
-        <v>46517</v>
+        <v>46513</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
       <c r="H38" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I38" s="23" t="str">
         <f>IF($A38="","",$A38&amp;"#"&amp;COUNTIF($A$2:$A38,$A38))</f>
-        <v>46517#1</v>
+        <v>46513#1</v>
       </c>
       <c r="J38" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Επαναλειτουργία σχολείου μετά το Πάσχα (εκτίμηση)</v>
+        <v>Διακοπές Πάσχα</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="19">
-        <v>46559</v>
+        <v>46514</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D39" s="21" t="s">
         <v>25</v>
@@ -3435,24 +3458,24 @@
       <c r="G39" s="21"/>
       <c r="H39" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Παρ</v>
       </c>
       <c r="I39" s="23" t="str">
         <f>IF($A39="","",$A39&amp;"#"&amp;COUNTIF($A$2:$A39,$A39))</f>
-        <v>46559#1</v>
+        <v>46514#1</v>
       </c>
       <c r="J39" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Αγίου Πνεύματος – Αργία</v>
+        <v>Διακοπές Πάσχα</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="19">
-        <v>46568</v>
+        <v>46517</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D40" s="21" t="s">
         <v>30</v>
@@ -3462,57 +3485,69 @@
       <c r="G40" s="21"/>
       <c r="H40" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Δευ</v>
       </c>
       <c r="I40" s="23" t="str">
         <f>IF($A40="","",$A40&amp;"#"&amp;COUNTIF($A$2:$A40,$A40))</f>
-        <v>46568#1</v>
+        <v>46517#1</v>
       </c>
       <c r="J40" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Λήξη διδακτικού έτους</v>
+        <v>Επαναλειτουργία σχολείου μετά το Πάσχα (εκτίμηση)</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
+      <c r="A41" s="19">
+        <v>46559</v>
+      </c>
       <c r="B41" s="20"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
+      <c r="C41" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>25</v>
+      </c>
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="22" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Δευ</v>
       </c>
       <c r="I41" s="23" t="str">
         <f>IF($A41="","",$A41&amp;"#"&amp;COUNTIF($A$2:$A41,$A41))</f>
-        <v/>
+        <v>46559#1</v>
       </c>
       <c r="J41" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Αγίου Πνεύματος – Αργία</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="19"/>
+      <c r="A42" s="19">
+        <v>46568</v>
+      </c>
       <c r="B42" s="20"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
+      <c r="C42" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>30</v>
+      </c>
       <c r="E42" s="21"/>
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
       <c r="H42" s="22" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Τετ</v>
       </c>
       <c r="I42" s="23" t="str">
         <f>IF($A42="","",$A42&amp;"#"&amp;COUNTIF($A$2:$A42,$A42))</f>
-        <v/>
+        <v>46568#1</v>
       </c>
       <c r="J42" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>Λήξη διδακτικού έτους</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="143">
   <si>
     <t>3ο ΓΥΜΝΑΣΙΟ ΠΟΛΙΧΝΗΣ  ·  ΗΜΕΡΟΛΟΓΙΟ ΔΡΑΣΕΩΝ  ·  ΣΧΟΛΙΚΟ ΕΤΟΣ 2026-27</t>
   </si>
@@ -474,19 +474,13 @@
     <t>Μουσείο Μακεδονικού Αγώνα</t>
   </si>
   <si>
-    <t>2η–3η ώρα</t>
+    <t>2η–5η ώρα</t>
   </si>
   <si>
     <t>Επιμορφωτική δράση από «Το Χαμόγελο του Παιδιού»</t>
   </si>
   <si>
-    <t>Α1, Α2</t>
-  </si>
-  <si>
-    <t>4η–5η ώρα</t>
-  </si>
-  <si>
-    <t>Α3</t>
+    <t>Α1, Α2: 2η–3η ώρα · Α3: 4η–5η ώρα</t>
   </si>
 </sst>
 </file>
@@ -3165,43 +3159,39 @@
       </c>
       <c r="J28" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>2η–3η ώρα  Επιμορφωτική δράση από «Το Χαμόγελο του Παιδιού»  (Α1, Α2)</v>
+        <v>2η–5η ώρα  Επιμορφωτική δράση από «Το Χαμόγελο του Παιδιού»  (Α1, Α2: 2η–3η ώρα · Α3: 4η–5η ώρα)</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="19">
-        <v>46493</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>143</v>
-      </c>
+        <v>46503</v>
+      </c>
+      <c r="B29" s="20"/>
       <c r="C29" s="21" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>144</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E29" s="21"/>
       <c r="F29" s="21"/>
       <c r="G29" s="21"/>
       <c r="H29" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Δευ</v>
       </c>
       <c r="I29" s="23" t="str">
         <f>IF($A29="","",$A29&amp;"#"&amp;COUNTIF($A$2:$A29,$A29))</f>
-        <v>46493#2</v>
+        <v>46503#1</v>
       </c>
       <c r="J29" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>4η–5η ώρα  Επιμορφωτική δράση από «Το Χαμόγελο του Παιδιού»  (Α3)</v>
+        <v>Διακοπές Πάσχα</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="19">
-        <v>46503</v>
+        <v>46504</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="21" t="s">
@@ -3215,11 +3205,11 @@
       <c r="G30" s="21"/>
       <c r="H30" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Τρί</v>
       </c>
       <c r="I30" s="23" t="str">
         <f>IF($A30="","",$A30&amp;"#"&amp;COUNTIF($A$2:$A30,$A30))</f>
-        <v>46503#1</v>
+        <v>46504#1</v>
       </c>
       <c r="J30" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3228,7 +3218,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="19">
-        <v>46504</v>
+        <v>46505</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="21" t="s">
@@ -3242,11 +3232,11 @@
       <c r="G31" s="21"/>
       <c r="H31" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Τετ</v>
       </c>
       <c r="I31" s="23" t="str">
         <f>IF($A31="","",$A31&amp;"#"&amp;COUNTIF($A$2:$A31,$A31))</f>
-        <v>46504#1</v>
+        <v>46505#1</v>
       </c>
       <c r="J31" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3255,7 +3245,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="19">
-        <v>46505</v>
+        <v>46506</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="21" t="s">
@@ -3269,11 +3259,11 @@
       <c r="G32" s="21"/>
       <c r="H32" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I32" s="23" t="str">
         <f>IF($A32="","",$A32&amp;"#"&amp;COUNTIF($A$2:$A32,$A32))</f>
-        <v>46505#1</v>
+        <v>46506#1</v>
       </c>
       <c r="J32" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3282,7 +3272,7 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="19">
-        <v>46506</v>
+        <v>46507</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="21" t="s">
@@ -3296,11 +3286,11 @@
       <c r="G33" s="21"/>
       <c r="H33" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Παρ</v>
       </c>
       <c r="I33" s="23" t="str">
         <f>IF($A33="","",$A33&amp;"#"&amp;COUNTIF($A$2:$A33,$A33))</f>
-        <v>46506#1</v>
+        <v>46507#1</v>
       </c>
       <c r="J33" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3309,7 +3299,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="19">
-        <v>46507</v>
+        <v>46510</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="21" t="s">
@@ -3323,11 +3313,11 @@
       <c r="G34" s="21"/>
       <c r="H34" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Δευ</v>
       </c>
       <c r="I34" s="23" t="str">
         <f>IF($A34="","",$A34&amp;"#"&amp;COUNTIF($A$2:$A34,$A34))</f>
-        <v>46507#1</v>
+        <v>46510#1</v>
       </c>
       <c r="J34" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3336,7 +3326,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="19">
-        <v>46510</v>
+        <v>46511</v>
       </c>
       <c r="B35" s="20"/>
       <c r="C35" s="21" t="s">
@@ -3350,11 +3340,11 @@
       <c r="G35" s="21"/>
       <c r="H35" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Τρί</v>
       </c>
       <c r="I35" s="23" t="str">
         <f>IF($A35="","",$A35&amp;"#"&amp;COUNTIF($A$2:$A35,$A35))</f>
-        <v>46510#1</v>
+        <v>46511#1</v>
       </c>
       <c r="J35" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3363,7 +3353,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="19">
-        <v>46511</v>
+        <v>46512</v>
       </c>
       <c r="B36" s="20"/>
       <c r="C36" s="21" t="s">
@@ -3377,11 +3367,11 @@
       <c r="G36" s="21"/>
       <c r="H36" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τρί</v>
+        <v>Τετ</v>
       </c>
       <c r="I36" s="23" t="str">
         <f>IF($A36="","",$A36&amp;"#"&amp;COUNTIF($A$2:$A36,$A36))</f>
-        <v>46511#1</v>
+        <v>46512#1</v>
       </c>
       <c r="J36" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3390,7 +3380,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
-        <v>46512</v>
+        <v>46513</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="21" t="s">
@@ -3404,11 +3394,11 @@
       <c r="G37" s="21"/>
       <c r="H37" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v>Πέμ</v>
       </c>
       <c r="I37" s="23" t="str">
         <f>IF($A37="","",$A37&amp;"#"&amp;COUNTIF($A$2:$A37,$A37))</f>
-        <v>46512#1</v>
+        <v>46513#1</v>
       </c>
       <c r="J37" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3417,7 +3407,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="19">
-        <v>46513</v>
+        <v>46514</v>
       </c>
       <c r="B38" s="20"/>
       <c r="C38" s="21" t="s">
@@ -3431,11 +3421,11 @@
       <c r="G38" s="21"/>
       <c r="H38" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Πέμ</v>
+        <v>Παρ</v>
       </c>
       <c r="I38" s="23" t="str">
         <f>IF($A38="","",$A38&amp;"#"&amp;COUNTIF($A$2:$A38,$A38))</f>
-        <v>46513#1</v>
+        <v>46514#1</v>
       </c>
       <c r="J38" s="23" t="str">
         <f t="shared" si="1"/>
@@ -3444,41 +3434,41 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="19">
-        <v>46514</v>
+        <v>46517</v>
       </c>
       <c r="B39" s="20"/>
       <c r="C39" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E39" s="21"/>
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
       <c r="H39" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Παρ</v>
+        <v>Δευ</v>
       </c>
       <c r="I39" s="23" t="str">
         <f>IF($A39="","",$A39&amp;"#"&amp;COUNTIF($A$2:$A39,$A39))</f>
-        <v>46514#1</v>
+        <v>46517#1</v>
       </c>
       <c r="J39" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Διακοπές Πάσχα</v>
+        <v>Επαναλειτουργία σχολείου μετά το Πάσχα (εκτίμηση)</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="19">
-        <v>46517</v>
+        <v>46559</v>
       </c>
       <c r="B40" s="20"/>
       <c r="C40" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E40" s="21"/>
       <c r="F40" s="21"/>
@@ -3489,65 +3479,59 @@
       </c>
       <c r="I40" s="23" t="str">
         <f>IF($A40="","",$A40&amp;"#"&amp;COUNTIF($A$2:$A40,$A40))</f>
-        <v>46517#1</v>
+        <v>46559#1</v>
       </c>
       <c r="J40" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Επαναλειτουργία σχολείου μετά το Πάσχα (εκτίμηση)</v>
+        <v>Αγίου Πνεύματος – Αργία</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="19">
-        <v>46559</v>
+        <v>46568</v>
       </c>
       <c r="B41" s="20"/>
       <c r="C41" s="21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E41" s="21"/>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Δευ</v>
+        <v>Τετ</v>
       </c>
       <c r="I41" s="23" t="str">
         <f>IF($A41="","",$A41&amp;"#"&amp;COUNTIF($A$2:$A41,$A41))</f>
-        <v>46559#1</v>
+        <v>46568#1</v>
       </c>
       <c r="J41" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Αγίου Πνεύματος – Αργία</v>
+        <v>Λήξη διδακτικού έτους</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="19">
-        <v>46568</v>
-      </c>
+      <c r="A42" s="19"/>
       <c r="B42" s="20"/>
-      <c r="C42" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>30</v>
-      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="21"/>
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
       <c r="H42" s="22" t="str">
         <f t="shared" si="0"/>
-        <v>Τετ</v>
+        <v/>
       </c>
       <c r="I42" s="23" t="str">
         <f>IF($A42="","",$A42&amp;"#"&amp;COUNTIF($A$2:$A42,$A42))</f>
-        <v>46568#1</v>
+        <v/>
       </c>
       <c r="J42" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Λήξη διδακτικού έτους</v>
+        <v/>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -393,7 +393,7 @@
     <t>E · ΤΑΞΕΙΣ / ΤΜΗΜΑΤΑ  (προαιρετικό)</t>
   </si>
   <si>
-    <t>Π.χ. «Α1, Α2» ή «Β΄ τάξη» ή «όλο το σχολείο». Μπαίνει σε παρένθεση μετά τον τίτλο στην αφίσα.</t>
+    <t>Π.χ. «Α1, Α2» ή «Β΄ τάξη» ή «όλο το σχολείο». Μπαίνει σε παρένθεση μετά τον τίτλο στην αφίσα. Αν μια δράση έχει διαφορετικά τμήματα σε διαφορετικές ώρες, χώρισέ τα με « / » και στις δύο στήλες με την ίδια σειρά, π.χ. ΩΡΕΣ «2η–3η ώρα / 4η–5η ώρα» και ΤΜΗΜΑΤΑ «Α1, Α2 / Α3».</t>
   </si>
   <si>
     <t>F · ΥΠΕΥΘΥΝΟΣ  (προαιρετικό)</t>
@@ -474,13 +474,13 @@
     <t>Μουσείο Μακεδονικού Αγώνα</t>
   </si>
   <si>
-    <t>2η–5η ώρα</t>
+    <t>2η–3η ώρα / 4η–5η ώρα</t>
   </si>
   <si>
-    <t>Επιμορφωτική δράση από «Το Χαμόγελο του Παιδιού»</t>
+    <t>Α΄ τάξη: Επιμορφωτική δράση από «Το Χαμόγελο του Παιδιού»</t>
   </si>
   <si>
-    <t>Α1, Α2: 2η–3η ώρα · Α3: 4η–5η ώρα</t>
+    <t>Α1, Α2 / Α3</t>
   </si>
 </sst>
 </file>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="J28" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>2η–5η ώρα  Επιμορφωτική δράση από «Το Χαμόγελο του Παιδιού»  (Α1, Α2: 2η–3η ώρα · Α3: 4η–5η ώρα)</v>
+        <v>2η–3η ώρα / 4η–5η ώρα  Α΄ τάξη: Επιμορφωτική δράση από «Το Χαμόγελο του Παιδιού»  (Α1, Α2 / Α3)</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -471,7 +471,7 @@
     <t>09:00-12.30</t>
   </si>
   <si>
-    <t>Μουσείο Μακεδονικού Αγώνα</t>
+    <t>Μουσείο Μακεδονικού Αγώνα και διαδραστική έκθεση Van Gogh – The Immersive Experience (ΔΕΘ Helexpo)</t>
   </si>
   <si>
     <t>2η–3η ώρα / 4η–5η ώρα</t>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="J9" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>09:00-12.30  Μουσείο Μακεδονικού Αγώνα</v>
+        <v>09:00-12.30  Μουσείο Μακεδονικού Αγώνα και διαδραστική έκθεση Van Gogh – The Immersive Experience (ΔΕΘ Helexpo)</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="145">
   <si>
     <t>3ο ΓΥΜΝΑΣΙΟ ΠΟΛΙΧΝΗΣ  ·  ΗΜΕΡΟΛΟΓΙΟ ΔΡΑΣΕΩΝ  ·  ΣΧΟΛΙΚΟ ΕΤΟΣ 2026-27</t>
   </si>
@@ -481,6 +481,12 @@
   </si>
   <si>
     <t>Α1, Α2 / Α3</t>
+  </si>
+  <si>
+    <t>08:00-14:10</t>
+  </si>
+  <si>
+    <t>Επίσκεψη στο Σπήλαιο Αλιστράτης και στο ΚΠΕ Ποροΐων</t>
   </si>
 </sst>
 </file>
@@ -3514,24 +3520,32 @@
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="19"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
+      <c r="A42" s="19">
+        <v>46349</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>27</v>
+      </c>
       <c r="E42" s="21"/>
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
       <c r="H42" s="22" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>Δευ</v>
       </c>
       <c r="I42" s="23" t="str">
         <f>IF($A42="","",$A42&amp;"#"&amp;COUNTIF($A$2:$A42,$A42))</f>
-        <v/>
+        <v>46349#1</v>
       </c>
       <c r="J42" s="23" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>08:00-14:10  Επίσκεψη στο Σπήλαιο Αλιστράτης και στο ΚΠΕ Ποροΐων</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -2579,7 +2579,11 @@
       <c r="D7" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="21"/>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Α΄ τάξη</t>
+        </is>
+      </c>
       <c r="F7" s="21"/>
       <c r="G7" s="21"/>
       <c r="H7" s="22" t="str">
@@ -2626,8 +2630,10 @@
       <c r="A9" s="19">
         <v>46356</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>138</v>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>09:00-12:30</t>
+        </is>
       </c>
       <c r="C9" s="21" t="s">
         <v>139</v>
@@ -2635,7 +2641,11 @@
       <c r="D9" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="21"/>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>Γ΄ τάξη</t>
+        </is>
+      </c>
       <c r="F9" s="21"/>
       <c r="G9" s="21"/>
       <c r="H9" s="22" t="str">
@@ -3532,7 +3542,11 @@
       <c r="D42" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="21"/>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>Γ2, Γ3</t>
+        </is>
+      </c>
       <c r="F42" s="21"/>
       <c r="G42" s="21"/>
       <c r="H42" s="22" t="str">

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>Γ΄ τάξη</t>
+          <t>Γ1, Γ4</t>
         </is>
       </c>
       <c r="F9" s="21"/>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="J9" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>09:00-12.30  Μουσείο Μακεδονικού Αγώνα και διαδραστική έκθεση Van Gogh – The Immersive Experience (ΔΕΘ Helexpo)</v>
+        <v>09:00-12.30  Μουσείο Μακεδονικού Αγώνα και διαδραστική έκθεση Van Gogh – The Immersive Experience (ΔΕΘ Helexpo)  (Γ1, Γ4)</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>Γ1, Γ4</t>
+          <t>Γ΄ τάξη</t>
         </is>
       </c>
       <c r="F9" s="21"/>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="J9" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>09:00-12.30  Μουσείο Μακεδονικού Αγώνα και διαδραστική έκθεση Van Gogh – The Immersive Experience (ΔΕΘ Helexpo)  (Γ1, Γ4)</v>
+        <v>09:00-12.30  Μουσείο Μακεδονικού Αγώνα και διαδραστική έκθεση Van Gogh – The Immersive Experience (ΔΕΘ Helexpo)</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -3563,12 +3563,34 @@
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
+      <c r="A43" s="19">
+        <v>46311</v>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:50-10:55</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Παγκόσμια Ημέρα Επανεκκίνησης Καρδιάς – «Kids Save Lives»</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Δράση / Πρόγραμμα / Όμιλος</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ομάδες μαθητών από διάφορα τμήματα</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Βασιλακοπούλου, Κανοπούλου</t>
+        </is>
+      </c>
       <c r="G43" s="21"/>
       <c r="H43" s="22" t="str">
         <f t="shared" si="0"/>

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -195,7 +195,7 @@
     <t>Έναρξη μαθημάτων</t>
   </si>
   <si>
-    <t>Αγίου Δημητρίου – Ελευθέρια Θεσσαλονίκης (τοπική αργία)</t>
+    <t>Αγίου Δημητρίου – τοπική αργία</t>
   </si>
   <si>
     <t>Εορταστικές εκδηλώσεις για την 28η Οκτωβρίου (χωρίς μάθημα)</t>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J4" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>Αγίου Δημητρίου – Ελευθέρια Θεσσαλονίκης (τοπική αργία)</v>
+        <v>Αγίου Δημητρίου – τοπική αργία</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="D29" s="28" t="str">
         <f>IF($B29="","",IFERROR(INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#1",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#2",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),"")&amp;IFERROR(CHAR(10)&amp;INDEX(ΔΡΑΣΕΙΣ!$J$2:$J$399,MATCH($B29&amp;"#3",ΔΡΑΣΕΙΣ!$I$2:$I$399,0)),""))</f>
-        <v>Αγίου Δημητρίου – Ελευθέρια Θεσσαλονίκης (τοπική αργία)</v>
+        <v>Αγίου Δημητρίου – τοπική αργία</v>
       </c>
       <c r="F29" s="25" t="str">
         <f t="shared" si="2"/>

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -3606,13 +3606,35 @@
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="19"/>
+      <c r="A44" s="19">
+        <v>46327</v>
+      </c>
       <c r="B44" s="20"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Momus – Λαδάδικα – Μοδιάνο (όμιλος «Ψηφιακή Ταυτότητα με Τεχνητή Νοημοσύνη»)</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ομάδα του ομίλου</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Πασσαλίδης Αλέξανδρος</t>
+        </is>
+      </c>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ενδεικτικά: Νοέμβριος – Δεκέμβριος 2026 · η ακριβής ημερομηνία θα ανακοινωθεί</t>
+        </is>
+      </c>
       <c r="H44" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3627,13 +3649,31 @@
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
+      <c r="A45" s="19">
+        <v>46357</v>
+      </c>
       <c r="B45" s="20"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Επίσκεψη στο Συσσίτιο / Κοινωνικό Παντοπωλείο</t>
+        </is>
+      </c>
+      <c r="D45" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 τμήμα Γ΄ τάξης</t>
+        </is>
+      </c>
       <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
+      <c r="G45" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ενδεικτικά: Δεκέμβριος 2026 · η ακριβής ημερομηνία θα ανακοινωθεί · Με αστική συγκοινωνία ή πεζή</t>
+        </is>
+      </c>
       <c r="H45" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3648,13 +3688,31 @@
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="19"/>
+      <c r="A46" s="19">
+        <v>46388</v>
+      </c>
       <c r="B46" s="20"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Επίσκεψη στο ΚΔΑΠ ΜΕΑ Πολίχνης (1ο τμήμα)</t>
+        </is>
+      </c>
+      <c r="D46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 τμήμα Γ΄ τάξης</t>
+        </is>
+      </c>
       <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ενδεικτικά: Ιανουάριος 2027 · η ακριβής ημερομηνία θα ανακοινωθεί · Με αστική συγκοινωνία ή πεζή</t>
+        </is>
+      </c>
       <c r="H46" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3669,13 +3727,31 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="19"/>
+      <c r="A47" s="19">
+        <v>46388</v>
+      </c>
       <c r="B47" s="20"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Επίσκεψη στο ΚΔΑΠ ΜΕΑ Πολίχνης (2ο τμήμα)</t>
+        </is>
+      </c>
+      <c r="D47" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 τμήμα Γ΄ τάξης</t>
+        </is>
+      </c>
       <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ενδεικτικά: Ιανουάριος 2027, άλλη μέρα από το 1ο τμήμα · η ακριβής ημερομηνία θα ανακοινωθεί · Με αστική συγκοινωνία ή πεζή</t>
+        </is>
+      </c>
       <c r="H47" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3690,13 +3766,31 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="19"/>
+      <c r="A48" s="19">
+        <v>46421</v>
+      </c>
       <c r="B48" s="20"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Επίσκεψη στο Γ.Ν. Παπαγεωργίου – Σύλλογος Αντηρίδα</t>
+        </is>
+      </c>
+      <c r="D48" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 τμήμα</t>
+        </is>
+      </c>
       <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
+      <c r="G48" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Με αστική συγκοινωνία ή πεζή</t>
+        </is>
+      </c>
       <c r="H48" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3711,13 +3805,31 @@
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="19"/>
+      <c r="A49" s="19">
+        <v>46428</v>
+      </c>
       <c r="B49" s="20"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Επίσκεψη στο Γ.Ν. Παπαγεωργίου – Σύλλογος Αντηρίδα</t>
+        </is>
+      </c>
+      <c r="D49" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 τμήμα</t>
+        </is>
+      </c>
       <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
+      <c r="G49" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Με αστική συγκοινωνία ή πεζή</t>
+        </is>
+      </c>
       <c r="H49" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3732,13 +3844,35 @@
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="19"/>
+      <c r="A50" s="19">
+        <v>46419</v>
+      </c>
       <c r="B50" s="20"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">«Οδύσσεια» – θεατρική ομάδα «Μικρός Βορράς»</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Α΄ τάξη</t>
+        </is>
+      </c>
+      <c r="F50" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Σωτηριάδου Ελπίς</t>
+        </is>
+      </c>
+      <c r="G50" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ενδεικτικά: Φεβρουάριος – Μάρτιος 2027 · η ακριβής ημερομηνία θα ανακοινωθεί</t>
+        </is>
+      </c>
       <c r="H50" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3753,13 +3887,31 @@
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="19"/>
+      <c r="A51" s="19">
+        <v>46447</v>
+      </c>
       <c r="B51" s="20"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Επίσκεψη στο ΚΗΦΗ Δήμου Παύλου Μελά</t>
+        </is>
+      </c>
+      <c r="D51" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 τμήμα</t>
+        </is>
+      </c>
       <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
+      <c r="G51" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ενδεικτικά: Μάρτιος 2027 · η ακριβής ημερομηνία θα ανακοινωθεί · Με αστική συγκοινωνία ή πεζή</t>
+        </is>
+      </c>
       <c r="H51" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3774,13 +3926,27 @@
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="19"/>
+      <c r="A52" s="19">
+        <v>46447</v>
+      </c>
       <c r="B52" s="20"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Επίσκεψη στο ΚΕΠΕΑ Αρναίας</t>
+        </is>
+      </c>
+      <c r="D52" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
       <c r="E52" s="21"/>
       <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
+      <c r="G52" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ενδεικτικά: τέλος Μαρτίου 2027 · η ακριβής ημερομηνία και τα τμήματα θα ανακοινωθούν</t>
+        </is>
+      </c>
       <c r="H52" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3795,13 +3961,35 @@
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="19"/>
+      <c r="A53" s="19">
+        <v>46447</v>
+      </c>
       <c r="B53" s="20"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Φεστιβάλ θεάτρου</t>
+        </is>
+      </c>
+      <c r="D53" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Θεατρική ομάδα + Γ1</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Καραγιάννη Αγγελική</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ενδεικτικά: τέλος Μαρτίου 2027 · η ακριβής ημερομηνία θα ανακοινωθεί</t>
+        </is>
+      </c>
       <c r="H53" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3816,13 +4004,35 @@
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="19"/>
+      <c r="A54" s="19">
+        <v>46447</v>
+      </c>
       <c r="B54" s="20"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Επίσκεψη στην Αμερικανική Γεωργική Σχολή</t>
+        </is>
+      </c>
+      <c r="D54" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Α΄ τάξη</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Κιτσάτης Νικόλαος</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ενδεικτικά: Μάρτιος – Απρίλιος 2027 · η ακριβής ημερομηνία θα ανακοινωθεί</t>
+        </is>
+      </c>
       <c r="H54" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3837,12 +4047,30 @@
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="19"/>
+      <c r="A55" s="19">
+        <v>46492</v>
+      </c>
       <c r="B55" s="20"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Οχυρό Ρούπελ – Λίμνη Κερκίνη</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Γ1, Γ3</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Βασιλακοπούλου Σταυρούλα</t>
+        </is>
+      </c>
       <c r="G55" s="21"/>
       <c r="H55" s="22" t="str">
         <f t="shared" si="0"/>
@@ -3858,13 +4086,31 @@
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="19"/>
+      <c r="A56" s="19">
+        <v>46508</v>
+      </c>
       <c r="B56" s="20"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
+      <c r="C56" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Προσομοίωση Συνεδρίασης Δημοτικού Συμβουλίου (Δημαρχείο – Αθ. Τσακίρη)</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Εκδρομή / Επίσκεψη / Περίπατος</t>
+        </is>
+      </c>
+      <c r="E56" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Γ΄ τάξη</t>
+        </is>
+      </c>
       <c r="F56" s="21"/>
-      <c r="G56" s="21"/>
+      <c r="G56" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ενδεικτικά: Μάιος 2027 · η ακριβής ημερομηνία θα ανακοινωθεί · Με αστική συγκοινωνία ή πεζή</t>
+        </is>
+      </c>
       <c r="H56" s="22" t="str">
         <f t="shared" si="0"/>
         <v/>

--- a/draseis.xlsx
+++ b/draseis.xlsx
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>Γ΄ τάξη</t>
+          <t>Γ1, Γ4</t>
         </is>
       </c>
       <c r="F9" s="21"/>
